--- a/emails_output/emails.xlsx
+++ b/emails_output/emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>UID</t>
   </si>
@@ -25,10 +25,88 @@
     <t>Attachments</t>
   </si>
   <si>
-    <t>9871</t>
-  </si>
-  <si>
-    <t>9872</t>
+    <t>9873</t>
+  </si>
+  <si>
+    <t>9874</t>
+  </si>
+  <si>
+    <t>9875</t>
+  </si>
+  <si>
+    <t>9876</t>
+  </si>
+  <si>
+    <t>9877</t>
+  </si>
+  <si>
+    <t>9878</t>
+  </si>
+  <si>
+    <t>9879</t>
+  </si>
+  <si>
+    <t>9880</t>
+  </si>
+  <si>
+    <t>9881</t>
+  </si>
+  <si>
+    <t>9882</t>
+  </si>
+  <si>
+    <t>9883</t>
+  </si>
+  <si>
+    <t>9884</t>
+  </si>
+  <si>
+    <t>9885</t>
+  </si>
+  <si>
+    <t>9886</t>
+  </si>
+  <si>
+    <t>9887</t>
+  </si>
+  <si>
+    <t>9888</t>
+  </si>
+  <si>
+    <t>9889</t>
+  </si>
+  <si>
+    <t>9890</t>
+  </si>
+  <si>
+    <t>9891</t>
+  </si>
+  <si>
+    <t>9892</t>
+  </si>
+  <si>
+    <t>9893</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>9895</t>
+  </si>
+  <si>
+    <t>9896</t>
+  </si>
+  <si>
+    <t>9897</t>
+  </si>
+  <si>
+    <t>9898</t>
+  </si>
+  <si>
+    <t>9899</t>
+  </si>
+  <si>
+    <t>9900</t>
   </si>
   <si>
     <t>hello taraweeh time mi amigo</t>
@@ -54,50 +132,2720 @@
   </si>
   <si>
     <t>Rayen gargouri &lt;gargourirayen@gmail.com&gt;
-Je me permets de vous contacter afin de faire une demande d’installation_x000D_
-d’un nouvel équipement dans nos locaux._x000D_
-_x000D_
-Nous souhaitons mettre en place une solution supplémentaire pour améliorer_x000D_
-la qualité de notre connexion. Idéalement, l’intervention pourrait avoir_x000D_
-lieu en début de semaine prochaine, de préférence le matin. Toutefois, si_x000D_
-cela n’est pas possible, nous restons flexibles selon vos disponibilités._x000D_
-_x000D_
-Nous vous serions reconnaissants de bien vouloir nous transmettre un devis_x000D_
-détaillé avant toute intervention. Si le coût reste raisonnable, nous_x000D_
-pourrons valider rapidement la demande._x000D_
-_x000D_
-Merci également de prévoir tout le matériel nécessaire afin d’éviter_x000D_
-plusieurs déplacements._x000D_
-_x000D_
-N’hésitez pas à me contacter pour toute information complémentaire._x000D_
-_x000D_
-Dans l’attente de votre retour._x000D_
-_x000D_
-Cordialement,_x000D_
+Je me permets de vous contacter afin de faire une demande d’installation_x005F_x000D_
+d’un nouvel équipement dans nos locaux._x005F_x000D_
+_x005F_x000D_
+Nous souhaitons mettre en place une solution supplémentaire pour améliorer_x005F_x000D_
+la qualité de notre connexion. Idéalement, l’intervention pourrait avoir_x005F_x000D_
+lieu en début de semaine prochaine, de préférence le matin. Toutefois, si_x005F_x000D_
+cela n’est pas possible, nous restons flexibles selon vos disponibilités._x005F_x000D_
+_x005F_x000D_
+Nous vous serions reconnaissants de bien vouloir nous transmettre un devis_x005F_x000D_
+détaillé avant toute intervention. Si le coût reste raisonnable, nous_x005F_x000D_
+pourrons valider rapidement la demande._x005F_x000D_
+_x005F_x000D_
+Merci également de prévoir tout le matériel nécessaire afin d’éviter_x005F_x000D_
+plusieurs déplacements._x005F_x000D_
+_x005F_x000D_
+N’hésitez pas à me contacter pour toute information complémentaire._x005F_x000D_
+_x005F_x000D_
+Dans l’attente de votre retour._x005F_x000D_
+_x005F_x000D_
+Cordialement,_x005F_x000D_
 Téléphone : 25318351</t>
   </si>
   <si>
     <t>"H't yessine" &lt;ye20042004@gmail.com&gt;
-Bonjour,_x000D_
-_x000D_
-Je vous écris afin de vous demander une vérification de notre réseau, car_x000D_
-nous rencontrons des coupures intermittentes depuis quelques jours._x000D_
-_x000D_
-Le problème n’est pas constant, mais il impacte régulièrement notre_x000D_
-travail, surtout en fin de journée. Nous souhaiterions donc qu’un_x000D_
-technicien puisse intervenir pour diagnostiquer la situation et proposer_x000D_
-une solution adaptée._x000D_
-_x000D_
-Si possible, nous préférerions une intervention en milieu de semaine,_x000D_
-plutôt le matin. Merci également de nous informer à l’avance du coût de_x000D_
-l’intervention avant toute validation._x000D_
-_x000D_
-Vous pouvez me contacter directement pour organiser cela._x000D_
-_x000D_
-Merci d’avance pour votre aide._x000D_
-_x000D_
-Cordialement,_x000D_
+Bonjour,_x005F_x000D_
+_x005F_x000D_
+Je vous écris afin de vous demander une vérification de notre réseau, car_x005F_x000D_
+nous rencontrons des coupures intermittentes depuis quelques jours._x005F_x000D_
+_x005F_x000D_
+Le problème n’est pas constant, mais il impacte régulièrement notre_x005F_x000D_
+travail, surtout en fin de journée. Nous souhaiterions donc qu’un_x005F_x000D_
+technicien puisse intervenir pour diagnostiquer la situation et proposer_x005F_x000D_
+une solution adaptée._x005F_x000D_
+_x005F_x000D_
+Si possible, nous préférerions une intervention en milieu de semaine,_x005F_x000D_
+plutôt le matin. Merci également de nous informer à l’avance du coût de_x005F_x000D_
+l’intervention avant toute validation._x005F_x000D_
+_x005F_x000D_
+Vous pouvez me contacter directement pour organiser cela._x005F_x000D_
+_x005F_x000D_
+Merci d’avance pour votre aide._x005F_x000D_
+_x005F_x000D_
+Cordialement,_x005F_x000D_
 Téléphone : 28456712</t>
+  </si>
+  <si>
+    <t>"LinkedIn" &lt;linkedin@em.linkedin.com&gt;
+_x000D_
+_x000D_
+  _x000D_
+    _x000D_
+    _x000D_
+    _x000D_
+    _x000D_
+    _x000D_
+    LinkedIn_x000D_
+    .ExternalClass { width:100%; }_x000D_
+.ExternalClass, .ExternalClass p, .ExternalClass span, .ExternalClass font, .ExternalClass td, .ExternalClass div { line-height: 100%; }_x000D_
+table td p { border-collapse: collapse; mso-table-lspace: 0pt; mso-table-rspace: 0pt; }_x000D_
+h1, h2, h3, h4, h5, h6 { font-size: inherit; padding: 0; margin: 0; color: black; line-height: 100%; }_x000D_
+.applelinks a { text-decoration: none; color: inherit !important; }_x000D_
+a { color: black; text-decoration: none; }_x000D_
+a, a:link, a:visited { color: inherit; text-decoration: none; }_x000D_
+span.MsoHyperlink { mso-style-priority: 99; color: inherit; }_x000D_
+span.MsoHyperlinkFollowed { mso-style-priority: 99; color: inherit; }_x000D_
+img { border: 0px !important; }_x000D_
+_x000D_
+body { font-family: Segoe UI, Arial, sans-serif; font-size: 14px; -webkit-text-size-adjust: none; -ms-text-size-adjust: none; -webkit-font-smoothing: antialiased; margin: 0; padding: 0; width: 100% !important; }_x000D_
+_x000D_
+.linkopacity:hover { opacity: 0.8 !important; }_x000D_
+_x000D_
+.button { -webkit-border-radius: 50px; -moz-border-radius: 50px; border-radius: 50px; overflow: hidden; }_x000D_
+_x000D_
+_x000D_
+@media only screen and (max-width: 480px) {_x000D_
+.w100m, .column50, .column33, .column25, .column75, .column66 { width: 100% !important; }_x000D_
+.banner { font-size: 22px !important;}_x000D_
+.w90m { width: 90% !important;}_x000D_
+.expandm { width: 100% !important; display: block !important; }_x000D_
+.resizem { width: 100% !important; height: auto !important; }_x000D_
+.hidem { display: none !important; }_x000D_
+.h1m { font-size: 22px !important;}_x000D_
+.h2m { font-size: 15px !important;}_x000D_
+.h3m { font-size: 13px !important;}_x000D_
+.tcenterm { text-align: center !important; }_x000D_
+.tleftm { text-align: left !important; }_x000D_
+.trightm { text-align: right !important; }_x000D_
+.height0m { height: 0 !important; }_x000D_
+.showm { display: block !important; max-height: 1000px !important; width: 100% !important; overflow: visible !important; align: center !important; }  _x000D_
+_x000D_
+.logo { width: 150px !important; height: auto !important; }  _x000D_
+_x000D_
+.border0m { border: 0px !important; }_x000D_
+.borderlr0m { border-left: 0px !important; border-right: 0px !important; }  _x000D_
+.pad0m { padding: 0px !important; }_x000D_
+.padlr0m { padding-left: 0px !important; padding-right: 0px !important; }  _x000D_
+.padt0m { padding-top: 0px !important; }_x000D_
+.padt5m { padding-top: 5px !important; }_x000D_
+.padt10m { padding-top: 10px !important; }_x000D_
+.padt20m { padding-top: 20px !important; }_x000D_
+.padt30m { padding-top: 30px !important; }_x000D_
+.padb0m { padding-bottom: 0px !important;}_x000D_
+.padb5m { padding-bottom: 5px !important;}_x000D_
+.padb10m { padding-bottom: 10px !important;}_x000D_
+.padb20m { padding-bottom: 20px !important;}_x000D_
+.padb30m { padding-bottom: 30px !important;}_x000D_
+}_x000D_
+_x000D_
+@media only screen and (max-width: 512px) {_x000D_
+.ow100 { width: 100% !important; }_x000D_
+.w100 { width: 100% !important; }_x000D_
+.w90 { width: 90% !important; }_x000D_
+.hide { display: none !important; }_x000D_
+.resize { width: 100% !important; height: auto !important; }_x000D_
+.resize img { max-width: 100% !important; height: auto !important; }_x000D_
+.resize a { width: auto !important; height: auto !important; }_x000D_
+.expand { width: 100% !important; display: block !important; }_x000D_
+.height0 { height: 0 !important; }_x000D_
+.column50 { width: 50%; }_x000D_
+.column50a { width: 50%; }_x000D_
+.column33 { width: 33.33%; }_x000D_
+.column25 { width: 25%; }_x000D_
+.column75 { width: 75%; }_x000D_
+.column66 { width: 66%; }_x000D_
+.tcenter { text-align: center !important; }_x000D_
+.show { display: block !important; max-height: 1000px !important; width: 100% !important; overflow: visible !important; align: center !important; }_x000D_
+_x000D_
+.bannerside { padding-top: 105px !important; }_x000D_
+_x000D_
+.border0 { border: 0px !important; }_x000D_
+.borderlr0 { border-left: 0px !important; border-right: 0px !important; }  _x000D_
+.pad0 { padding: 0px !important; }_x000D_
+.padlr0 { padding-left: 0px !important; padding-right: 0px !important; }  _x000D_
+.padt0 { padding-top: 0px !important; }_x000D_
+.padt5 { padding-top: 5px !important; }_x000D_
+.padt10 { padding-top: 10px !important; }_x000D_
+.padt20 { padding-top: 20px !important; }_x000D_
+.padt30 { padding-top: 30px !important; }_x000D_
+.padb0 { padding-bottom: 0px !important; }_x000D_
+.padb5 { padding-bottom: 5px !important; }_x000D_
+.padb10 { padding-bottom: 10px !important; }_x000D_
+.padb20 { padding-bottom: 20px !important; }_x000D_
+.padb30 { padding-bottom: 30px !important; }_x000D_
+}_x000D_
+   _x000D_
+    _x000D_
+_x000D_
+body { margin: 0 !important; padding: 0 !important; font-family: Segoe UI, Arial, sans-serif; }_x000D_
+table, td, div, p { font-family: Segoe UI, Arial, sans-serif; line-height: normal; }_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+96_x000D_
+_x000D_
+_x000D_
+_x000D_
+  _x000D_
+  _x000D_
+    _x000D_
+    _x000D_
+    _x000D_
+      Update your job preferences to get better recommendations._x000D_
+    _x000D_
+    _x000D_
+    &amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp; &amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;_x000D_
+_x000D_
+    _x000D_
+    _x000D_
+    _x000D_
+      _x000D_
+        _x000D_
+          _x000D_
+            _x000D_
+              _x000D_
+                _x000D_
+                  _x000D_
+                    _x000D_
+                      _x000D_
+                      _x000D_
+                        _x000D_
+                          _x000D_
+                          _x000D_
+                          _x000D_
+                        _x000D_
+                        _x000D_
+                        _x000D_
+                        _x000D_
+                          _x000D_
+                            _x000D_
+                              _x000D_
+                                _x000D_
+                                  _x000D_
+                                  _x000D_
+                                    _x000D_
+                                    _x000D_
+                                  _x000D_
+                                  _x000D_
+                                  _x000D_
+                                  _x000D_
+                  _x000D_
+                  _x000D_
+                                    _x000D_
+                                    _x000D_
+                                    _x000D_
+                                  _x000D_
+                                  _x000D_
+                                _x000D_
+                              _x000D_
+                            _x000D_
+                          _x000D_
+                        _x000D_
+                        _x000D_
+                        _x000D_
+                        _x000D_
+                        _x000D_
+                          _x000D_
+                            _x000D_
+                              _x000D_
+                                _x000D_
+                                  _x000D_
+                                    _x000D_
+                                      _x000D_
+                                      _x000D_
+                                        _x000D_
+                                          Completing your profile_x000D_
+                                             is quick and&amp;nbsp;easy._x000D_
+                                        _x000D_
+                                        _x000D_
+                                        _x000D_
+                                        _x000D_
+                                          _x000D_
+                                        _x000D_
+                                        _x000D_
+                                        _x000D_
+                                        _x000D_
+                                          _x000D_
+                                            _x000D_
+                                              _x000D_
+                                                _x000D_
+                                                  _x000D_
+                                                    Add job preferences_x000D_
+                                                    _x000D_
+                                                  _x000D_
+                                                _x000D_
+                                              _x000D_
+                                            _x000D_
+                                          _x000D_
+                                        _x000D_
+                                        _x000D_
+                                      _x000D_
+                                    _x000D_
+                                  _x000D_
+                                _x000D_
+                              _x000D_
+                            _x000D_
+                          _x000D_
+                        _x000D_
+                        _x000D_
+                        _x000D_
+                          _x000D_
+                            _x000D_
+                            _x000D_
+                          _x000D_
+                        _x000D_
+                        _x000D_
+                        _x000D_
+                          _x000D_
+                            _x000D_
+                              _x000D_
+                              _x000D_
+                                _x000D_
+                                  _x000D_
+                                    Help recruiters find&amp;nbsp;you._x000D_
+                                  _x000D_
+                                _x000D_
+                                _x000D_
+                                _x000D_
+                                _x000D_
+                                  Update your job preferences to let them know&amp;nbsp;what roles you're interested&amp;nbsp;in._x000D_
+                                _x000D_
+                                _x000D_
+                                _x000D_
+                                _x000D_
+                                  _x000D_
+                                    _x000D_
+                                      _x000D_
+                                        _x000D_
+                                          _x000D_
+                                            Complete your profile_x000D_
+                                            _x000D_
+                                          _x000D_
+                                        _x000D_
+                                      _x000D_
+                                    _x000D_
+                                  _x000D_
+                                _x000D_
+                                _x000D_
+                              _x000D_
+                            _x000D_
+                          _x000D_
+                        _x000D_
+                        _x000D_
+                        _x000D_
+                        _x000D_
+                        _x000D_
+                          _x000D_
+                            _x000D_
+_x000D_
+Footer Mercado English_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+This email was intended for Yessine Hadj Taieb (IT Student) Learn why we includedthis. This is an occasional email to help you get the most outofLinkedIn. UnsubscribeHelp_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+2026,_x000D_
+_x000D_
+LinkedIn Ireland Unlimited Company._x000D_
+_x000D_
+All rights reserved. _x000D_
+_x000D_
+LinkedIn Ireland Unlimited Company, Gardner House, Wilton Plaza, Wilton Place, Dublin 2, Ireland._x000D_
+_x000D_
+LinkedIn and the LinkedIn logo are registered trademarks of LinkedIn.</t>
+  </si>
+  <si>
+    <t>LinkedIn &lt;messages-noreply@linkedin.com&gt;
+Your profile is looking great_x000D_
+_x000D_
+Your work and accomplishments are being recognized_x000D_
+_x000D_
+2 profile views_x000D_
+  _x000D_
+          https://www.linkedin.com/comm/me/profile-views?lipi=urn%3Ali%3Apage%3Aemail_b2_professional_identity_digest_02%3B62vgDD%2FtSUiKBJjco8N2nQ%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=39Vv6kzbeN7sc1&amp;trk=eml-b2_professional_identity_digest_02-email~professional~identity~digest-0-profile~views&amp;trkEmail=eml-b2_professional_identity_digest_02-email~professional~identity~digest-0-profile~views-null-m8w88x~mmweiv0w~x9-null-null&amp;eid=m8w88x-mmweiv0w-x9&amp;otpToken=MTMwNjFhZTUxMzI3Y2ZjMGJjMmYwZmViNDExOWU0YmM4OWNlZDI0Njk4YTc4YTY5N2JjZTAxNjg0OTVkNThmYmYyZDJkMGU5N2FkYWVhZDk1ZTgzZWI4MDg5MDE4YzgxNjVkMjYxZjYzY2EwMWVkM2YxYzllZDE3LDEsMQ%3D%3D      _x000D_
+_x000D_
+----------------------------------------_x000D_
+_x000D_
+This email was intended for Yessine Hadj Taieb (IT Student)_x000D_
+Learn why we included this: https://www.linkedin.com/help/linkedin/answer/4788?lang=en&amp;lipi=urn%3Ali%3Apage%3Aemail_b2_professional_identity_digest_02%3B62vgDD%2FtSUiKBJjco8N2nQ%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=39Vv6kzbeN7sc1&amp;trk=eml-b2_professional_identity_digest_02-SecurityHelp-0-textfooterglimmer&amp;trkEmail=eml-b2_professional_identity_digest_02-SecurityHelp-0-textfooterglimmer-null-m8w88x~mmweiv0w~x9-null-null&amp;eid=m8w88x-mmweiv0w-x9&amp;otpToken=MTMwNjFhZTUxMzI3Y2ZjMGJjMmYwZmViNDExOWU0YmM4OWNlZDI0Njk4YTc4YTY5N2JjZTAxNjg0OTVkNThmYmYyZDJkMGU5N2FkYWVhZDk1ZTgzZWI4MDg5MDE4YzgxNjVkMjYxZjYzY2EwMWVkM2YxYzllZDE3LDEsMQ%3D%3D_x000D_
+You are receiving LinkedIn notification emails._x000D_
+_x000D_
+_x000D_
+Unsubscribe: https://www.linkedin.com/comm/psettings/email-unsubscribe?lipi=urn%3Ali%3Apage%3Aemail_b2_professional_identity_digest_02%3B62vgDD%2FtSUiKBJjco8N2nQ%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=39Vv6kzbeN7sc1&amp;trk=eml-b2_professional_identity_digest_02-unsubscribe-0-textfooterglimmer&amp;trkEmail=eml-b2_professional_identity_digest_02-unsubscribe-0-textfooterglimmer-null-m8w88x~mmweiv0w~x9-null-null&amp;eid=m8w88x-mmweiv0w-x9&amp;loid=AQG3BVUtl__J4gAAAZ0CT7c5JLAdWHA_u6Unebauj_iogGJ29o4YhdZVWbfjdRnWk-9-0SE_2f6eL9-icNx7oSA9qK_gEZRg80cQ4HlvDg4_x000D_
+Help: https://www.linkedin.com/help/linkedin/answer/67?lang=en&amp;lipi=urn%3Ali%3Apage%3Aemail_b2_professional_identity_digest_02%3B62vgDD%2FtSUiKBJjco8N2nQ%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=39Vv6kzbeN7sc1&amp;trk=eml-b2_professional_identity_digest_02-help-0-textfooterglimmer&amp;trkEmail=eml-b2_professional_identity_digest_02-help-0-textfooterglimmer-null-m8w88x~mmweiv0w~x9-null-null&amp;eid=m8w88x-mmweiv0w-x9&amp;otpToken=MTMwNjFhZTUxMzI3Y2ZjMGJjMmYwZmViNDExOWU0YmM4OWNlZDI0Njk4YTc4YTY5N2JjZTAxNjg0OTVkNThmYmYyZDJkMGU5N2FkYWVhZDk1ZTgzZWI4MDg5MDE4YzgxNjVkMjYxZjYzY2EwMWVkM2YxYzllZDE3LDEsMQ%3D%3D_x000D_
+_x000D_
+© 2026 LinkedIn Corporation, 1zwnj000 West Maude Avenue, Sunnyvale, CA 94085._x000D_
+LinkedIn and the LinkedIn logo are registered trademarks of LinkedIn.</t>
+  </si>
+  <si>
+    <t>"DeepLearning.AI" &lt;hello@deeplearning.ai&gt;
+New course with Oracle! Agent Memory: Building Memory-Aware Agents_x000D_
+_x000D_
+View in browser (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VW4pvt46Fv9TW8-wlmh7KLMCPVmLt1V5LPSpvN2sc1y45m_5PW7lCGcx6lZ3l_VCSCGD4VMlvTVRKVY27PW4ZCW2D99PD92nRnzW46QGLV1L9wZvW5Nf4v_4wdvWBW6WwhVt7ZGHHHW2LQwHJ3y7_21W2LDH4z3DpzKFW24QZQ03R-DHLW6vtKG-6qFK1-W2SzGXp40v3sFW6Mwf332FLGkLN3VwG1wSPmPnW9bfhw05PrXD2W5XBfwm4ycx_fW6fcBT58259zTW43TFMQ2qX5_yW487dps3sGjg4W2p1_C_66J9y-W2fH6Qb3MKrXbW6lPC-k5qVFY3W5SSWP01VzyHGW3Jl4-t4ZgghFN9gVtL5rV9FgW1_58N66csWWJW93JbJx9bBbj-W61rz4s6qTsPfW8cy42J1p90XKW3HKHt-6-DN5HVhLzbv4v9cKMW4-7NTJ8Hs9GdW62svnw2JfcnRW5n2hkx65pLhxN8qLH_H-4NPzW7ydPwn5NnXMZW7jjj0V5ml-bBW4D96Rv1BsB-TW5qKmw64NGfCcW5cBL7B43NsdDN5JxtyljQ902f7nWK3K04 )_x000D_
+_x000D_
+Was this email forwarded to you? Subscribe here_x000D_
+_x000D_
+DeepLearning.AI coral logo next to the word "Courses" in all caps and teal color (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VW4pvt46Fv9TW8-wlmh7KLMCPVmLt1V5LPSpvN2sc1wW5m_5PW50kH_H6lZ3mZW3ltX3q4XjB-nW2P5F363NfshxW1XZL5v1wVy9HW4pV9D24tHrC6W1hxkxp1xMzqVN1W12fR9hgjbW2b1j267BGZ5LN8sLVsYWSrmLW7jJHTc6PLzjgN1KB6w5r2mtHW4zVxJr3k1NXBW2cCt6B4Z1x_zW6fVzmr5pHZT5W5sV2vN8bFhs-W2d8y0w1J27TVW8p2-5v4Y8cQ_W1Zk5rf4NWNLZW5tYmNv7X2yb8W5H57yq8r16zgW2n0VQy5zpLMMW7d5znJ7VykW9W621Gf_67tky8N7YMR9qkQq-LVZMVJv31SkH4W5T9Jhb2B-3SVW5rfD3D2rlPgnVhGKzf1F4-jyVh12NM4-KQh0W93DptL1RGtRcN8rcqrnjz6nZW5g5v8N7TWswKW2ppB8n8vF77_f2_5GNK04 )_x000D_
+_x000D_
+Agent Memory: Building Memory-Aware Agents promotional banner with an Enroll Now CTA (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VW4pvt46Fv9TW8-wlmh7KLMCPVmLt1V5LPSpvN2sc1wW5m_5PW50kH_H6lZ3mZW3ltX3q4XjB-nW2P5F363NfshxW1XZL5v1wVy9HW4pV9D24tHrC6W1hxkxp1xMzqVN1W12fR9hgjbW2b1j267BGZ5LN8sLVsYWSrmLW7jJHTc6PLzjgN1KB6w5r2mtHW4zVxJr3k1NXBW2cCt6B4Z1x_zW6fVzmr5pHZT5W5sV2vN8bFhs-W2d8y0w1J27TVW8p2-5v4Y8cQ_W1Zk5rf4NWNLZW5tYmNv7X2yb8W5H57yq8r16zgW2n0VQy5zpLMMW7d5znJ7VykW9W621Gf_67tky8N7YMR9qkQq-LVZMVJv31SkH4W5T9Jhb2B-3SVW5rfD3D2rlPgnVhGKzf1F4-jyVh12NM4-KQh0W93DptL1RGtRcN8rcqrnjz6nZW5g5v8N7TWswKW2ppB8n8vF77_f2_5GNK04 )_x000D_
+_x000D_
+Dear learner,_x000D_
+_x000D_
+Today we’re launching a new short course built in collaboration with Oracle: Agent Memory: Building Memory-Aware Agents (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VW4pvt46Fv9TW8-wlmh7KLMCPVmLt1V5LPSpvN2sc1wW5m_5PW50kH_H6lZ3mZW3ltX3q4XjB-nW2P5F363NfshxW1XZL5v1wVy9HW4pV9D24tHrC6W1hxkxp1xMzqVN1W12fR9hgjbW2b1j267BGZ5LN8sLVsYWSrmLW7jJHTc6PLzjgN1KB6w5r2mtHW4zVxJr3k1NXBW2cCt6B4Z1x_zW6fVzmr5pHZT5W5sV2vN8bFhs-W2d8y0w1J27TVW8p2-5v4Y8cQ_W1Zk5rf4NWNLZW5tYmNv7X2yb8W5H57yq8r16zgW2n0VQy5zpLMMW7d5znJ7VykW9W621Gf_67tky8N7YMR9qkQq-LVZMVJv31SkH4W5T9Jhb2B-3SVW5rfD3D2rlPgnVhGKzf1F4-jyVh12NM4-KQh0W93DptL1RGtRcN8rcqrnjz6nZW5g5v8N7TWswKW2ppB8n8vF77_f2_5GNK04 ) ._x000D_
+_x000D_
+Many AI agents work well within a single session but lose everything when the session ends. In this course, you’ll learn how to build a memory-first architecture that allows agents to persist knowledge, retrieve relevant context, and update what they know across sessions._x000D_
+_x000D_
+Using Oracle AI Database, LangChain, and LLM-powered pipelines, you’ll build a complete agent memory system that turns a stateless agent into one that can learn and improve over time._x000D_
+_x000D_
+Enroll Now_x000D_
+(https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VW4pvt46Fv9TW8-wlmh7KLMCPVmLt1V5LPSpvN2sc1wW5m_5PW50kH_H6lZ3mZW3ltX3q4XjB-nW2P5F363NfshxW1XZL5v1wVy9HW4pV9D24tHrC6W1hxkxp1xMzqVN1W12fR9hgjbW2b1j267BGZ5LN8sLVsYWSrmLW7jJHTc6PLzjgN1KB6w5r2mtHW4zVxJr3k1NXBW2cCt6B4Z1x_zW6fVzmr5pHZT5W5sV2vN8bFhs-W2d8y0w1J27TVW8p2-5v4Y8cQ_W1Zk5rf4NWNLZW5tYmNv7X2yb8W5H57yq8r16zgW2n0VQy5zpLMMW7d5znJ7VykW9W621Gf_67tky8N7YMR9qkQq-LVZMVJv31SkH4W5T9Jhb2B-3SVW5rfD3D2rlPgnVhGKzf1F4-jyVh12NM4-KQh0W93DptL1RGtRcN8rcqrnjz6nZW5g5v8N7TWswKW2ppB8n8vF77_f2_5GNK04 )_x000D_
+_x000D_
+In this course, you’ll learn to:_x000D_
+_x000D_
+- Build persistent memory stores and implement a Memory Manager that orchestrates how agents read and write memory_x000D_
+- Scale tool use by treating tools as procedural memory and retrieving them with semantic search_x000D_
+- Implement memory extraction, consolidation, and write-back pipelines so agents can update what they know_x000D_
+_x000D_
+The course is taught by Oracle’s Richmond Alake, Director of AI Developer Experience, and Nacho Martínez, Data Science Advocate at Oracle._x000D_
+_x000D_
+👉 Enroll Now_x000D_
+(https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VW4pvt46Fv9TW8-wlmh7KLMCPVmLt1V5LPSpvN2sc1wW5m_5PW50kH_H6lZ3mZW3ltX3q4XjB-nW2P5F363NfshxW1XZL5v1wVy9HW4pV9D24tHrC6W1hxkxp1xMzqVN1W12fR9hgjbW2b1j267BGZ5LN8sLVsYWSrmLW7jJHTc6PLzjgN1KB6w5r2mtHW4zVxJr3k1NXBW2cCt6B4Z1x_zW6fVzmr5pHZT5W5sV2vN8bFhs-W2d8y0w1J27TVW8p2-5v4Y8cQ_W1Zk5rf4NWNLZW5tYmNv7X2yb8W5H57yq8r16zgW2n0VQy5zpLMMW7d5znJ7VykW9W621Gf_67tky8N7YMR9qkQq-LVZMVJv31SkH4W5T9Jhb2B-3SVW5rfD3D2rlPgnVhGKzf1F4-jyVh12NM4-KQh0W93DptL1RGtRcN8rcqrnjz6nZW5g5v8N7TWswKW2ppB8n8vF77_f2_5GNK04 )_x000D_
+_x000D_
+Launch email GIFs - 2026-03-17T184511.291 (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VW4pvt46Fv9TW8-wlmh7KLMCPVmLt1V5LPSpvN2sc1wW5m_5PW50kH_H6lZ3mZW3ltX3q4XjB-nW2P5F363NfshxW1XZL5v1wVy9HW4pV9D24tHrC6W1hxkxp1xMzqVN1W12fR9hgjbW2b1j267BGZ5LN8sLVsYWSrmLW7jJHTc6PLzjgN1KB6w5r2mtHW4zVxJr3k1NXBW2cCt6B4Z1x_zW6fVzmr5pHZT5W5sV2vN8bFhs-W2d8y0w1J27TVW8p2-5v4Y8cQ_W1Zk5rf4NWNLZW5tYmNv7X2yb8W5H57yq8r16zgW2n0VQy5zpLMMW7d5znJ7VykW9W621Gf_67tky8N7YMR9qkQq-LVZMVJv31SkH4W5T9Jhb2B-3SVW5rfD3D2rlPgnVhGKzf1F4-jyVh12NM4-KQh0W93DptL1RGtRcN8rcqrnjz6nZW5g5v8N7TWswKW2ppB8n8vF77_f2_5GNK04 )_x000D_
+_x000D_
+Keep learning,_x000D_
+_x000D_
+The DeepLearning.AI team_x000D_
+_x000D_
+Facebook (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VW4pvt46Fv9TW8-wlmh7KLMCPVmLt1V5LPSpvN2sc1y43prCCW7lCdLW6lZ3mzW7gS4G85RlYpsW2MMVJ01fKk7FN6PH6jgb7PQWW4x3csp7wPfpcW27Ls3P6fmjWkW7CRwnm76d7rBW92DP-l5SkyrzW5b2c9894JnzCW913QZ78jsWGGW76ZQB28J9fxMW4DbMfB3sWYhQN14j8-4qc29DW708v226stT3DW607YRv4HhL9yW5GPmrW6qCSNpW7GSzQb68ptx6W18w8Y91PF4d1W644nlq2J-pCkW1JLtrd2nRDKnW4sFBZw66Nt59W7_M1zY67Gm5HW5S0Jpz6ttPGfW8T7TdM75KktFW3S2LTk1t9FwZf3P7Kwg04 )_x000D_
+_x000D_
+LinkedIn (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VW4pvt46Fv9TW8-wlmh7KLMCPVmLt1V5LPSpvN2sc1y43prCCW7lCdLW6lZ3mwW3gLvcV6yDfkqVMVP5C5xrfxKN1kmKC-hSgTcW76xjSr4wWvKcW7f9RWv4M8NKjW5CTBg88qNxQtF2mBmndqfRgVPL3Z-6Ts3LCW4MgdQr6k1jPmW3vltRS8DH9c-N3sNhBDMBjGJW2xXhfz64wshVVTF-gY1hQYRnW8gVrR79dgjQqW7l8hJX9jp7TqW3GqthP1q8FtwW62_rhb3_Tl9yW4ZVCpM8G078XW30KtXT5zlfJqW3Y5nPB5QlWRnW3k2p2R8P2v0cW17VmmQ8C32XmW5g3dfs46msLyW61D72c3pkmsdf5W1WyP04 )_x000D_
+_x000D_
+X (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VW4pvt46Fv9TW8-wlmh7KLMCPVmLt1V5LPSpvN2sc1y43prCCW7lCdLW6lZ3mjVpy3NN9lchsJW3HPsP68PLQ26W4qphHJ8L5j74W1lTKWr6T-ygWVfj1LW2PTS-xVK45J_2t9Qf7N4DN_-zCH7Q7W13Vkz84kX_vLW14GrmX5zbY1BW7JNChN5ndv0vW1tJ1-G1mx-fxN8p4ybNlKT-RW799LVw1-VLMzW237-VR5_0_MlW6Vd9-k46PyNFW1sWYw11VrLpfW8KGZgc8dcFd3W92N4KJ2pWtQyVbxs005DjgrGW4M1G_R5d15QHW4TRjc37ptNbBW8qQbT31y-PD3W6x2qRB5lm1yTF53Gb6NZCjbf65yqDP04 )_x000D_
+_x000D_
+Instagram (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VW4pvt46Fv9TW8-wlmh7KLMCPVmLt1V5LPSpvN2sc1y43prCCW7lCdLW6lZ3lzW21vDgz7mC59zW7LgdcT3PNXZkW3Xdtwk6XcD4FW1q72pC6TXSvnW5vSM9r5gjBJSN1d6nQjjRb0BN7fNpdrGM6cGW76lbzR7QZb9SN3K1lhWz_c3nW7ZmpbK97ryllW29vDJd1njqH9W1g3gg47_Wj41W7vGfDd1vQ-DwVcY8S82lxHk-W1Z6gVT9jN16FW2xQv6N6zvDPVW99DJMc6F0kbvW91hnvk2wXr7HW7BnpRv5qyZxPW4NySVY6jK_8mW787LXx3y4TKzW4XTgd37Z_mpvN9k86MX-mfQnW6WN5qG14XqCkf8XXZGb04 )_x000D_
+_x000D_
+YouTube (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VW4pvt46Fv9TW8-wlmh7KLMCPVmLt1V5LPSpvN2sc1yn3prCCW7Y8-PT6lZ3kyW8wRSzt1bMfc1W3LHjxD21lSt1W7_T_Sl2g9ZbPN51Vv72JB8CGW6C0vny7mqsBMW5f_smt3hSXgxW71NYdn97WPbCW49LKcw6s5CzLW6MBNmV6cD6x8W4GwBYp5SsgZYN8NX1WD3dp7gW62pflC5c084PMnKHH6RxC9rN7X5Jjt2dg3TW4W_6qR931nlFW6JSpg887qb1nW43Q0395K3fp6W3r1ctf98_mRsW3nfw1Y115gwGW79Qq4c8xrpTsW5s0VgT7ym5xkW6mwPpZ7QLgKCW4htd6H12Y-lRW70KPHG3bSFzPW15LQ2386fVtBW2nTZQ323gr42f8dmqTR04 )_x000D_
+_x000D_
+White Circle Profile Photo Instagram Post (3) (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VW4pvt46Fv9TW8-wlmh7KLMCPVmLt1V5LPSpvN2sc1y43prCCW7lCdLW6lZ3nbW2vsLJ_2jmsftW6YzTLh2LszZmW3vv3S54M0ZkpW38hnP34dpt18N7BF5DZrHGPmW2bTXBQ28CxT_W11mvgd8jWCv8W2gb_q05q2js3W3w0c8X2K_5Z7W2yCtJg8Hf38bW1bKny_5YY-ySW4lwDb-5qS_F4W81C3h84Psz60W4WCfjQ2rlHG7W5Pf12r35XxnbW3cyVg78N4nCYVY0tQh8bFxSbW6J6JqB3TFvntW8Zw3Xm4r800SN5Q617K6CvgXN7t3XpH9pYBSW8THykf1ylpprW5rttvZ82PYCdW1GsJvM2h5dKwf67Jk_604 )_x000D_
+_x000D_
+Copyright © 2026 deeplearning.ai, All rights reserved._x000D_
+_x000D_
+You are receiving this because you opted in to receive emails from deeplearning.ai._x000D_
+_x000D_
+DeepLearning.AI, 400 Castro St., Suite 600, Mountain View, CA 94041, United States_x000D_
+_x000D_
+Manage preferences (https://info.deeplearning.ai/hs/preferences-center/en/page?data=W2nXS-N30h-LWW2Mmw8m2Hs42ZW3_Djjx1V00W3W4thCc44pmjGhW3gt0Dw4cs2h9W2-kpGz2MqPSWW1_bblw1V0PHKW2qMVVW3XQ8rXW3W3Z511BdWgTW3NLWKt4002KNW2vzXs14htNj_W3Sy2942TRdJ_W3d2HxG2vS4DRW4tl86M49M8WKW3R2KWP41tYYZW3b1HjN1ZpBkzW2vZPfP3SZvp4W3VzY9K3XHxTwW3jvt9p4hwWGBW1LB6LF3BYxN0W36CQK31Z5sJFW4rjd_K3T5v7qW1QgZD31Ndfb3W2PvPKs4rnkJ2W4fgnND3Syv76W4hy5z13DKHG2W4tzDM01VdYzbW4hPn9Y32jc0PW3FdZ4W2CVRPkW3zcDp02zKQcMW3F4Cy72zG48wW3jmPlW3d3xQfW2xxCf82FzBjdW41Vbjl2Kqb5zW3C2lg72-tRNbW4psKpG4p8wKHW1L95k74mdRsDW49jm142TkhDPW2zDPKS1LkvNCW4cB_Gz2569_7W3M2Pry3_L47mW3C8C9L343X7RW3F7w4p2WMngQW2xwkSc3ZMZWNW2zHn_-1XgJW4W3H8yZg36dYgmW3XKFtF3bw3NtW4myXrn2-B8_hW38vTF_3f_CP2W4ryV_w43WbLnW3g1G7h4m9zVyW2HSfyj36FzDhW2HC1NP30nCCSW2Pl4Tq25dwkmW45mlBT2HpZh-f2nSJ2J04&amp;_hsenc=p2ANqtz-9vkOdTYc6osbgwMPuoX-3SAS89EryMVMHRlhvcBipq1tUMATg_HOG4KH539cUMSI2k0alVTks6mS0M0po088-JETGvTA&amp;_hsmi=409399070 )</t>
+  </si>
+  <si>
+    <t>daily.dev &lt;informer@daily.dev&gt;
+We picked posts from your topics based on what the community found useful  _x000D_
+_x000D_
+*******_x000D_
+For you_x000D_
+*******_x000D_
+_x000D_
+​Mar 19, 2026_x000D_
+_x000D_
+Logo ( https://app.daily.dev/ )_x000D_
+_x000D_
+Fireship ( https://app.daily.dev/posts/rI6zUABsr?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+The rise and fall of famo.us... ( https://app.daily.dev/posts/rI6zUABsr?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+--------------------------------------------------------------------------------------------------------------------------------------_x000D_
+_x000D_
+Read_x000D_
+article → ( https://app.daily.dev/posts/rI6zUABsr?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+Fast-track your growth. Upgrade to plus ( https://app.daily.dev/plus )_x000D_
+_x000D_
+Try daily.dev on mobile (if you haven’t yet)_x000D_
+_x000D_
+( https://apps.apple.com/app/daily-dev/id6740634400 )_x000D_
+daily.dev for iOS ( https://apps.apple.com/app/daily-dev/id6740634400 )_x000D_
+_x000D_
+( https://play.google.com/store/apps/details?id=dev.daily )_x000D_
+daily.dev for Android ( https://play.google.com/store/apps/details?id=dev.daily )_x000D_
+_x000D_
+Explore ( https://app.daily.dev/posts )   |   Discussions ( https://app.daily.dev/discussed )   |   Tags ( https://app.daily.dev/tags )   |   Sources ( https://app.daily.dev/sources )   |   Leaderboard ( https://app.daily.dev/users )_x000D_
+_x000D_
+X ( https://twitter.com/dailydotdev ) Yt ( https://www.youtube.com/c/dailydev )_x000D_
+Inst ( https://www.instagram.com/dailydotdev/ ) Tt ( https://www.tiktok.com/@dailydotdev )_x000D_
+GitHub ( https://github.com/dailydotdev/daily )_x000D_
+This email was intended for Yessine Ht (yessineht@gmail.com)_x000D_
+Settings notifications ( https://app.daily.dev/account/notifications ), account details ( https://app.daily.dev/account/profile ) or unsubscribe ( https://track.customer.io/manage_subscription_preferences/RLnCCQUAAZ0EexPe8pWgDm_9_8Z5Yw== ) _x000D_
+_x000D_
+( https://app.daily.dev )Daily Dev Ltd., 9 Derech HaTikva Ganei Tikva, Israel_x000D_
+5591252</t>
+  </si>
+  <si>
+    <t>LinkedIn &lt;messages-noreply@linkedin.com&gt;
+Do you know Mejdi Bel Hadj Youssef?1 mutual connection_x000D_
+_x000D_
+Yes, connect: https://www.linkedin.com/comm/mynetwork/send-invite/mejdi-bel-hadj-youssef-80b42b242/?lipi=urn%3Ali%3Apage%3Aemail_email_pymk_02%3BbNusqx7lTwSaPL6624s%2Fzw%3D%3D&amp;midSig=1xG41dxj3T8cc1&amp;midToken=AQFDdUEz6WQ9Uw&amp;trkEmail=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A1010319563-null-m8w88x%7Emmx8j3bw%7Ehu-null-null&amp;trk=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A1010319563&amp;_sig=138SBs787T8cc1_x000D_
+_x000D_
+_x000D_
+More people you may know_x000D_
+            _x000D_
+    eya jaoua_x000D_
+computer science student||Microsoft learn student ambassador_x000D_
+https://www.linkedin.com/comm/mynetwork/send-invite/eya-jaoua/?lipi=urn%3Ali%3Apage%3Aemail_email_pymk_02%3BbNusqx7lTwSaPL6624s%2Fzw%3D%3D&amp;midSig=1xG41dxj3T8cc1&amp;midToken=AQFDdUEz6WQ9Uw&amp;trkEmail=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A949657185-null-m8w88x%7Emmx8j3bw%7Ehu-null-null&amp;trk=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A949657185&amp;_sig=2gja66m8TT8cc14 mutual connections_x000D_
+            _x000D_
+    Mohamed Manaa_x000D_
+Enseignant universitaire chez ISET Sfax_x000D_
+https://www.linkedin.com/comm/mynetwork/send-invite/mohamed-manaa-62a776158/?lipi=urn%3Ali%3Apage%3Aemail_email_pymk_02%3BbNusqx7lTwSaPL6624s%2Fzw%3D%3D&amp;midSig=1xG41dxj3T8cc1&amp;midToken=AQFDdUEz6WQ9Uw&amp;trkEmail=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A634926850-null-m8w88x%7Emmx8j3bw%7Ehu-null-null&amp;trk=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A634926850&amp;_sig=2SgX7a2xnT8cc16 mutual connections_x000D_
+            _x000D_
+    Mansouri Haider_x000D_
+IT et Réseaux &amp; Télécommunication ( TEK-UP )_x000D_
+https://www.linkedin.com/comm/mynetwork/send-invite/mansouri-haider-a13261105/?lipi=urn%3Ali%3Apage%3Aemail_email_pymk_02%3BbNusqx7lTwSaPL6624s%2Fzw%3D%3D&amp;midSig=1xG41dxj3T8cc1&amp;midToken=AQFDdUEz6WQ9Uw&amp;trkEmail=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A445536879-null-m8w88x%7Emmx8j3bw%7Ehu-null-null&amp;trk=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A445536879&amp;_sig=37cgVfq0XT8cc11 mutual connection_x000D_
+            _x000D_
+    Thamer El Heni_x000D_
+Researcher in Industrial Engineering | Industrial &amp; Logistics Systems | AI &amp; Deep Learning_x000D_
+https://www.linkedin.com/comm/mynetwork/send-invite/thamer-el-heni-332851379/?lipi=urn%3Ali%3Apage%3Aemail_email_pymk_02%3BbNusqx7lTwSaPL6624s%2Fzw%3D%3D&amp;midSig=1xG41dxj3T8cc1&amp;midToken=AQFDdUEz6WQ9Uw&amp;trkEmail=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A1569738134-null-m8w88x%7Emmx8j3bw%7Ehu-null-null&amp;trk=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A1569738134&amp;_sig=2ndzgKO4vT8cc12 mutual connections_x000D_
+            _x000D_
+    Yosr Bouhlel_x000D_
+IT student | Software Development_x000D_
+https://www.linkedin.com/comm/mynetwork/send-invite/yosr-bouhlel/?lipi=urn%3Ali%3Apage%3Aemail_email_pymk_02%3BbNusqx7lTwSaPL6624s%2Fzw%3D%3D&amp;midSig=1xG41dxj3T8cc1&amp;midToken=AQFDdUEz6WQ9Uw&amp;trkEmail=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A1425864474-null-m8w88x%7Emmx8j3bw%7Ehu-null-null&amp;trk=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A1425864474&amp;_sig=06kvZGV47T8cc12 mutual connections_x000D_
+_x000D_
+See more people you might know:https://www.linkedin.com/comm/mynetwork/add-connections/?lipi=urn%3Ali%3Apage%3Aemail_email_pymk_02%3BbNusqx7lTwSaPL6624s%2Fzw%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=1xG41dxj3T8cc1&amp;trk=eml-email_pymk_02-see_more-0-cta~text&amp;trkEmail=eml-email_pymk_02-see_more-0-cta~text-null-m8w88x~mmx8j3bw~hu-null-null&amp;eid=m8w88x-mmx8j3bw-hu&amp;otpToken=MTMwNjFhZTUxMzI3Y2ZjMGJjMmYwZmViNDExOWU0YmQ4ZWNlZDU0NTlhYWI4OTYzN2JjZTAxNjg0OTVkNThmYmYyZDJkMGU5NjliNmQ4ZWIwNzg1ZWRhNDIyOGRmN2ZkMmU3YjkzNTI1MzZkY2ZjMWQ4NTVkMWJlLDEsMQ%3D%3D_x000D_
+      _x000D_
+_x000D_
+----------------------------------------_x000D_
+_x000D_
+This email was intended for Yessine Hadj Taieb (IT Student)_x000D_
+Learn why we included this: https://www.linkedin.com/help/linkedin/answer/4788?lang=en&amp;lipi=urn%3Ali%3Apage%3Aemail_email_pymk_02%3BbNusqx7lTwSaPL6624s%2Fzw%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=1xG41dxj3T8cc1&amp;trk=eml-email_pymk_02-SecurityHelp-0-textfooterglimmer&amp;trkEmail=eml-email_pymk_02-SecurityHelp-0-textfooterglimmer-null-m8w88x~mmx8j3bw~hu-null-null&amp;eid=m8w88x-mmx8j3bw-hu&amp;otpToken=MTMwNjFhZTUxMzI3Y2ZjMGJjMmYwZmViNDExOWU0YmQ4ZWNlZDU0NTlhYWI4OTYzN2JjZTAxNjg0OTVkNThmYmYyZDJkMGU5NjliNmQ4ZWIwNzg1ZWRhNDIyOGRmN2ZkMmU3YjkzNTI1MzZkY2ZjMWQ4NTVkMWJlLDEsMQ%3D%3D_x000D_
+You are receiving People You May Know notification emails._x000D_
+_x000D_
+_x000D_
+Unsubscribe: https://www.linkedin.com/comm/psettings/email-unsubscribe?lipi=urn%3Ali%3Apage%3Aemail_email_pymk_02%3BbNusqx7lTwSaPL6624s%2Fzw%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=1xG41dxj3T8cc1&amp;trk=eml-email_pymk_02-unsubscribe-0-textfooterglimmer&amp;trkEmail=eml-email_pymk_02-unsubscribe-0-textfooterglimmer-null-m8w88x~mmx8j3bw~hu-null-null&amp;eid=m8w88x-mmx8j3bw-hu&amp;loid=AQEmCipYgnYUJAAAAZ0FTsy34kpdbXbSzJzEdD-SWIOPlTNV7wPKwPiUW0lYLUTlfdvnuzx79pGSOqiBJWvhCH_-72pHWrtEA1Asx5_sPQ_x000D_
+Help: https://www.linkedin.com/help/linkedin/answer/67?lang=en&amp;lipi=urn%3Ali%3Apage%3Aemail_email_pymk_02%3BbNusqx7lTwSaPL6624s%2Fzw%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=1xG41dxj3T8cc1&amp;trk=eml-email_pymk_02-help-0-textfooterglimmer&amp;trkEmail=eml-email_pymk_02-help-0-textfooterglimmer-null-m8w88x~mmx8j3bw~hu-null-null&amp;eid=m8w88x-mmx8j3bw-hu&amp;otpToken=MTMwNjFhZTUxMzI3Y2ZjMGJjMmYwZmViNDExOWU0YmQ4ZWNlZDU0NTlhYWI4OTYzN2JjZTAxNjg0OTVkNThmYmYyZDJkMGU5NjliNmQ4ZWIwNzg1ZWRhNDIyOGRmN2ZkMmU3YjkzNTI1MzZkY2ZjMWQ4NTVkMWJlLDEsMQ%3D%3D_x000D_
+_x000D_
+© 2026 LinkedIn Corporation, 1zwnj000 West Maude Avenue, Sunnyvale, CA 94085._x000D_
+LinkedIn and the LinkedIn logo are registered trademarks of LinkedIn.</t>
+  </si>
+  <si>
+    <t>Ollama &lt;hello@ollama.com&gt;
+_x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+MiniMax-M2.7 is now available to run via Ollama's cloud. This new model is designed to excel at completing end-to-end tasks in_x000D_
+software engineering and office productivity while improving its character and emotional intelligence._x000D_
+ _x000D_
+M2.7 is also good at self-improvement using data from the web. This allows assistants like OpenClaw to do research and learn new_x000D_
+skills._x000D_
+ _x000D_
+To get started, download Ollama:_x000D_
+ _x000D_
+_x000D_
+Download Ollama [https://ollama.com/download]_x000D_
+_x000D_
+ _x000D_
+Next, launch OpenClaw with MiniMax-M2.7:_x000D_
+ _x000D_
+ollama launch openclaw --model minimax-m2.7:cloud_x000D_
+ _x000D_
+If you already have OpenClaw running with Ollama, switch to MiniMax-M2.7 cloud by using the /model command:_x000D_
+ _x000D_
+/model ollama/minimax-m2.7:cloud_x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+Self-improvement &amp; research_x000D_
+_x000D_
+OpenClaw can now perform deep research tasks and use up-to-date web information to teach itself skills and best practices._x000D_
+ _x000D_
+Example: financial reporting_x000D_
+ _x000D_
+Teach yourself how to write financial research reports by studying examples from top analysts. Write a PPT presentation and Word_x000D_
+document report on TSMC based on their latest earnings. Save your research framework as a skill so future reports follow the same_x000D_
+process._x000D_
+ _x000D_
+_x000D_
+_x000D_
+Launch agents in non-interactive mode_x000D_
+_x000D_
+Ollama can now launch non-interactive agents using the new --yes flag._x000D_
+ _x000D_
+This enables running OpenClaw and other agents in the background without interruption on servers, scripts, and other environments_x000D_
+that do not support the OpenClaw gateway._x000D_
+ _x000D_
+To launch a non-interactive OpenClaw agent, run:_x000D_
+ _x000D_
+ollama launch openclaw \_x000D_
+--model minimax-m2.7:cloud \_x000D_
+--yes -- agent \_x000D_
+--agent main \_x000D_
+--local \_x000D_
+--message "Prepare a pre-read for my next meeting"_x000D_
+ _x000D_
+ _x000D_
+If you have any feedback, reply directly to this email or join Ollama's Discord channel [https://discord.gg/ollama]._x000D_
+ _x000D_
+❤️ Ollama_x000D_
+ _x000D_
+You are receiving this email because you opted-in to receive updates from Ollama_x000D_
+Ollama, 744 High Street, Palo Alto, CA 94301_x000D_
+Unsubscribe [https://app.loops.so/unsubscribe/cmmxhgs6303dm013ngna84jus/499521766e101b0c025b73bfd52c281472f937354753c009cada275d4d1bdfc29a49fcd2f675180c7de51707de78b4c3b770fc3c6dea959168cd0a50]</t>
+  </si>
+  <si>
+    <t>Vercel &lt;notifications@vercel.com&gt;
+Vercel_x000D_
+Hi t0ny-iv,_x000D_
+_x000D_
+We're updating our Terms of Service (https://vercel.com/terms)_x000D_
+and Privacy Policy (https://vercel.com/privacy) to reflect how_x000D_
+Vercel uses data to support agentic features, improve our_x000D_
+platform, and contribute to the AI ecosystem._x000D_
+_x000D_
+----------------_x000D_
+_x000D_
+What is changing_x000D_
+----------------_x000D_
+_x000D_
+Agentic infrastructure capabilities_x000D_
+_x000D_
+We are developing features that allow Vercel to do more to keep_x000D_
+your apps running efficiently, including:_x000D_
+_x000D_
+*_x000D_
+Proactively investigating and mitigating incidents_x000D_
+*_x000D_
+Analyzing web app performance data and suggesting improvements_x000D_
+*_x000D_
+Identifying where your spend is going and creating PRs to_x000D_
+optimize usage_x000D_
+Optional AI model training_x000D_
+_x000D_
+You may choose whether Vercel can:_x000D_
+_x000D_
+*_x000D_
+Use your code and Vercel agent chats to improve Vercel models_x000D_
+*_x000D_
+Share your code and Vercel agent chats with AI model providers_x000D_
+_x000D_
+Vercel will not share personal data, account details, or_x000D_
+sensitive information like environment variables, and any_x000D_
+information of this nature will be removed from data you make_x000D_
+available for AI training._x000D_
+_x000D_
+----------------_x000D_
+_x000D_
+Defaults by plan_x000D_
+----------------_x000D_
+_x000D_
+* Hobby and Trial Pro: Opted in to AI model training by default,_x000D_
+can opt out at any time_x000D_
+* Pro: Opted out of AI model training by default, can opt in at_x000D_
+any time_x000D_
+You can manage your preferences in Team Settings → Data_x000D_
+Preferences_x000D_
+(https://vercel.com/d?to=%2F%5Bteam%5D%2F%7E%2Fsettings%23data-preferences&amp;title=Go+to+Data+Preferences)._x000D_
+_x000D_
+If you choose to opt out by March 31, 2026, no data will be used_x000D_
+by Vercel to train AI or shared with third parties. If you choose_x000D_
+to opt out after March 31, 2026, your data will not be used or_x000D_
+shared starting from the time of your opt-out._x000D_
+_x000D_
+Other changes to our Terms of Service include updated dispute_x000D_
+resolution processes, billing practices, and provisions to_x000D_
+reflect compliance with the latest data protection laws. While_x000D_
+arbitration has always been our method of resolving disputes with_x000D_
+international and Enterprise customers, it now also applies to_x000D_
+U.S.-based customers. The opt-out process described in Section 21_x000D_
+of our Terms of Service is unchanged._x000D_
+_x000D_
+For more detailed FAQs, visit our Changelog_x000D_
+(https://vercel.com/changelog/updates-to-terms-of-service-march-2026?utm_campaign=tos&amp;utm_source=email)._x000D_
+_x000D_
+-----------------------------------------------------------------_x000D_
+_x000D_
+Copyright © 2026 Vercel Inc._x000D_
+(https://vercel.com?utm_medium=email&amp;utm_source=notifications&gt;)_x000D_
+All rights reserved._x000D_
+440 N Barranca Ave #4133 Covina, CA 91723_x000D_
+_x000D_
+Manage your notification settings_x000D_
+(https://vercel.com/d?to=%2F%5Bteam%5D%2F%7E%2Fsettings%2Fnotifications&amp;title=Notification+Settings)_x000D_
+_x000D_
+p {_x000D_
+color:#000;_x000D_
+font-family:_x000D_
+Geist,-apple-system,system-ui,BlinkMacSystemFont,"Segoe UI"_x000D_
+,"Roboto","Oxygen","Ubuntu","Cantarell","Fira Sans","Droid_x000D_
+Sans","Helvetica Neue",sans-serif;_x000D_
+font-size: 14px;_x000D_
+line-height: 24px;_x000D_
+overflow-wrap: anywhere;_x000D_
+}_x000D_
+.break-all {_x000D_
+color:#000;_x000D_
+font-family:_x000D_
+Geist,-apple-system,system-ui,BlinkMacSystemFont,"Segoe UI"_x000D_
+,"Roboto","Oxygen","Ubuntu","Cantarell","Fira Sans","Droid_x000D_
+Sans","Helvetica Neue",sans-serif;_x000D_
+font-size: 14px;_x000D_
+line-height: 24px;_x000D_
+word-break: break-all_x000D_
+}_x000D_
+h1 {_x000D_
+color: #000;_x000D_
+font-family: Geist,-apple-system, BlinkMacSystemFont, "Segoe UI",_x000D_
+"Roboto","Oxygen","Ubuntu","Cantarell","Fira Sans","Droid_x000D_
+Sans","Helvetica Neue",sans-serif;_x000D_
+font-size: 24px;_x000D_
+font-weight: normal;_x000D_
+margin: 30px 0;_x000D_
+padding: 0;_x000D_
+}_x000D_
+h2 {_x000D_
+font-size: 18px;_x000D_
+}_x000D_
+h3 {_x000D_
+font-size: 16px;_x000D_
+}_x000D_
+pre {_x000D_
+font-family: "Geist_x000D_
+Mono",ui-monospace,SFMono-Regular,Menlo,Monaco,Consolas,"Liberation_x000D_
+Mono","Courier New",monospace_x000D_
+width: 100%;_x000D_
+max-width: 465px;_x000D_
+overflow: hidden;_x000D_
+text-overflow: ellipsis;_x000D_
+color: #171717;_x000D_
+border: 1px solid #e5e5e5;_x000D_
+padding: 20px;_x000D_
+border-radius: 6px;_x000D_
+}_x000D_
+.block-button.block-button--solid.block-button--sm {_x000D_
+background-color:#000;_x000D_
+border-radius:5px;_x000D_
+color: #fff;_x000D_
+display: inline-block;_x000D_
+font-family: -apple-system,system-ui,BlinkMacSystemFont,"Segoe_x000D_
+UI" ,"Roboto","Oxygen","Ubuntu","Cantarell","Fira Sans","Droid_x000D_
+Sans","Helvetica Neue",sans-serif;_x000D_
+font-size:14px;_x000D_
+font-weight:500;_x000D_
+line-height:50px;_x000D_
+text-align:center;_x000D_
+text-decoration:none;_x000D_
+width:200px;_x000D_
+}_x000D_
+strong {_x000D_
+color:#000;_x000D_
+font-weight:bold;_x000D_
+}_x000D_
+a {_x000D_
+color:#067df7;_x000D_
+text-decoration:none;_x000D_
+}_x000D_
+code.inline {_x000D_
+color:rgb(189,16,224);_x000D_
+text-decoration:none;_x000D_
+font-family:Menlo,Monaco,"Lucida Console","Liberation_x000D_
+Mono","DejaVu Sans Mono","Bitstream Vera Sans Mono","Courier_x000D_
+New",monospace,serif;_x000D_
+font-size:0.9em;_x000D_
+}_x000D_
+ul {_x000D_
+padding-left: 20px;_x000D_
+}_x000D_
+li, .usage {_x000D_
+font-family: -apple-system, BlinkMacSystemFont, "Segoe UI",_x000D_
+"Roboto","Oxygen","Ubuntu","Cantarell","Fira Sans","Droid_x000D_
+Sans","Helvetica Neue",sans-serif;_x000D_
+font-size:14px;_x000D_
+line-height: 2em;_x000D_
+color:#000;_x000D_
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Microsoft" &lt;Microsoft@infomail.microsoft.com&gt;
+_x000D_
+_x000D_
+_x000D_
+    _x000D_
+_x000D_
+    _x000D_
+      _x000D_
+         _x000D_
+            96_x000D_
+         _x000D_
+      _x000D_
+    _x000D_
+      _x000D_
+    _x000D_
+    _x000D_
+    _x000D_
+    _x000D_
+	Attention : Vos photos et vos fichiers ne sont plus synchronisés_x000D_
+	_x000D_
+	_x000D_
+	_x000D_
+	_x000D_
+	_x000D_
+	_x000D_
+	_x000D_
+    _x000D_
+    _x000D_
+    _x000D_
+_x000D_
+    _x000D_
+_x000D_
+    _x000D_
+    _x000D_
+        _x000D_
+    _x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+     _x000D_
+    _x000D_
+    _x000D_
+    _x000D_
+    _x000D_
+    _x000D_
+    _x000D_
+_x000D_
+    _x000D_
+    _x000D_
+_x000D_
+    _x000D_
+    _x000D_
+_x000D_
+    _x000D_
+    _x000D_
+    	@-ms-viewport { width: device-width;}_x000D_
+    _x000D_
+    _x000D_
+    	.xf-content-height { margin:0 !important; }_x000D_
+		.xf-content-height .newpar { margin: 0; height: 100% !important; }_x000D_
+		.desktop-block { display:block; }_x000D_
+	    .rtl-template,  .rtl-template td { direction: rtl !important; text-align: right !important; } _x000D_
+		.rtl-template .text-rtl-center td, .rtl-template .hero-text-center{text-align:center !important}_x000D_
+		.rtl-template .btn-rtl th { direction: rtl !important; }_x000D_
+        .rtl-template ul { margin: 0 !important; padding-right: 22px !important;text-align: right !important;direction: rtl !important; }_x000D_
+        .rtl-template ol { margin-top: 0 !important;margin-bottom:0 !important; padding-right: 22px !important;text-align: right !important;}_x000D_
+        .rtl-template .social-icons { padding-left: 12px !important; padding-right: 0 !important; }_x000D_
+        .rtl-template .text-align-right th { text-align: right !important;padding-right:0px !important; padding-left:3px !important; }_x000D_
+		.rtl-template .txt-align-right, .rtl-template .block-text-align-right {text-align: right !important;}_x000D_
+		.rtl-template li { padding: 0 12px 8px 0 !important; }_x000D_
+		.rtl-template .rating-thumbs-up { padding-left: 30px; padding-right: 0; }_x000D_
+		.rtl-template .reward-tile-card {padding-left: 20px; padding-right: 0; }_x000D_
+        .rtl-template .ribbon-cta .block-max-width {text-align: left !important;}_x000D_
+		.rtl-template .block-max-width, .rtl-template .btn-block-right {text-align: right !important;}_x000D_
+		.rtl-template .block-max-width-center {text-align: center !important;}_x000D_
+		u+.rtl-template a { color:#0067B8 !important; }	_x000D_
+		.rtl-template .table-ruler td, .rtl-template .table-ruler th, .rtl-template .table-zebra td, .rtl-template .table-zebra th,	_x000D_
+		.rtl-template .table-hr-icon td, .rtl-template .table-zebra-icon td { padding: 20px 20px 20px 0 !important;	text-align: right !important; }_x000D_
+		.rtl-template .table-ruler-mobile th, .rtl-template .table-zebra-mobile th { text-align: right !important; 	}_x000D_
+		.rtl-template .text-rtl-center td {text-align: center !important;}_x000D_
+    	.rtl-template .text-rtl-center .img-wrapper img {display:block; margin:0 auto;}_x000D_
+		.email-table .text-center p,.email-table .text-center td {text-align:center !important;}_x000D_
+        .email-table .text-center img {Margin:0 auto;margin:0 auto;}  _x000D_
+        .email-table .text-left p,.email-table .text-left td {text-align:left !important;}_x000D_
+        .email-table .text-right p,.email-table .text-right td {text-align:right !important;}_x000D_
+        .rtl-template .email-table .text-center p,.rtl-template .email-table .text-center td {direction: rtl !important;text-align: center !important;}_x000D_
+		.rtl-template .btn-rtl th {direction: rtl !important;} _x000D_
+		.rtl-template .tile-headline, .rtl-template .tile-paragraph { padding: 0 20px 0 20px;}_x000D_
+		.rtl-template .small-tile-image { padding: 20px 20px 0px 20px;}_x000D_
+		.rtl-template .tile-button { padding: 0 20px 20px 20px; }_x000D_
+		.rtl-template .padd-left-right-40 { padding: 0 40px 0 40px !important;}_x000D_
+		.rtl-template .padd-left-20 { padding-left: 20px !important; padding-right: 0 !important;}_x000D_
+		.rtl-template .intro-tile-image {padding:10px 10px 10px 20px}_x000D_
+		.rtl-template .intro-tile-text {padding:0 0 0 10px}_x000D_
+        .rtl-template .image-tile-10 { padding:10px 10px 0px 0px !important;}_x000D_
+        .rtl-template .image-tile-20 {padding: 20px 20px 0px 0px !important;}_x000D_
+        .footer-address-center td,.footer-address-center td p,.footer-address-center td p a{text-align:center !important;direction:ltr !important;}_x000D_
+		 table.groupthree a {text-decoration: underline !important;}_x000D_
+		.txt-center ul li, .txt-center ol li{text-align: center !important; list-style-position: inside;}_x000D_
+         body {margin:0;padding:0;}_x000D_
+         table td {border-collapse:collapse;margin:0;padding:0;}_x000D_
+         table td p {margin:0;padding:0;}_x000D_
+		 table td p a {color:#0067B8;text-decoration:underline;font-weight: normal;}_x000D_
+		 table th {font-weight: normal !important;}_x000D_
+		 .table-width{width:200px!important;height:27px!important;}		_x000D_
+		 .mobile-social-padd-right{padding-right:40px;}_x000D_
+         .desktopHidden, .desktop-hidden, .autopreview, .spacer-desktop-hide, .table-ruler-mobile, .table-zebra-mobile {display: none !important;}_x000D_
+         .gutter {padding:0 30px;}_x000D_
+		 .tile-pad-large-4 {padding-left: 50px !important; padding-right: 50px !important;}        _x000D_
+         .tile-pad-large {padding-left: 30px !important; padding-right: 30px !important;}        _x000D_
+         .tile-pad-small-v1 {padding-left: 50px !important; padding-right: 50px !important;}        _x000D_
+         .tile-pad-small-v2 {padding-left: 84px !important; padding-right: 84px !important;}        _x000D_
+         .tile-pad-small-v3 {padding-left: 119px !important; padding-right: 119px !important;}        _x000D_
+         .tile-pad-small-v5 {padding-left: 154px !important; padding-right: 154px !important;}_x000D_
+		 .padd-left-right-40 { padding:0 40px 0 40px !important;}_x000D_
+		 .padd-left-right-20 { padding:0 20px 0 20px !important;}_x000D_
+		 .padd-left-right-10 { padding:0 10px 0 10px !important;}_x000D_
+		 .padd-left-right-28 { padding:0 28px 0 28px !important;}_x000D_
+		 .padd-right-26 { padding:0 26px 0 0 !important;}_x000D_
+		 .padd-left-26 { padding:0 0 0 26px !important;}_x000D_
+		 .tile-small-box .btn-block {vertical-align:top}		 _x000D_
+		 .tile-image {padding: 10px 20px 10px 10px;}_x000D_
+		 .reward-tile-card {padding-right: 20px;}_x000D_
+         .lg-tile-image, .lg-tile-headline, .lg-tile-paragraph, .lg-tile-button {padding: 0 40px 0 40px;}_x000D_
+         .tile-headline, .tile-paragraph { padding: 0 20px 0 20px;}_x000D_
+         .small-tile-image { padding: 20px 20px 0px 20px;}_x000D_
+         .tile-button { padding: 0 20px 20px 20px;}		 _x000D_
+         .tile-txt-small {font-family: 'Segoe UI', Helvetica, Arial, sans-serif; font-size: 12px; font-style: normal; color: #505050; line-height: 16px; letter-spacing: -0.01em; text-align: center; padding-left: 5px; padding-right: 5px; word-wrap: break-word; word-break: break-all;}_x000D_
+         .tile-txt-large {font-family: 'Segoe UI', Helvetica, Arial, sans-serif; font-size: 14px; font-style: normal; color: #505050; line-height: 20px; letter-spacing: -0.01em; text-align: center; padding-left: 10px; padding-right: 10px; word-wrap: break-word; word-break: break-all;} _x000D_
+         .boxed-list-wrapper {padding: 20px 30px 0;}_x000D_
+		 .block-padd-top-30 {padding-top: 0px;}_x000D_
+		 .rating-thumbs-up {padding-right: 30px;}_x000D_
+		 .text-card-padding {padding: 0 80px 0px 80px;}_x000D_
+         .rte-spacer-20 p,.rte-spacer-20 ul,.rte-spacer-20 ol {padding-bottom: 20px !important;}_x000D_
+		 .rte-spacer-10 p,.rte-spacer-10 ul,.rte-spacer-10 ol {padding-bottom: 10px !important;}_x000D_
+         .rte-footerspacer-10 p,.rte-footerspacer-10 ul,.rte-footerspacer-10 ol {padding-top: 10px !important;}_x000D_
+		 .semibold{font-weight:600;}_x000D_
+		 .strikethrough { text-decoration: line-through;}_x000D_
+		  /* Tabular Data Start */_x000D_
+		 .spacer-ln-ht-0 {line-height: 0px;font-size: 0px;}_x000D_
+		 .table-ruler-mobile td, .table-ruler-mobile th, .table-zebra-mobile td, .table-zebra-mobile th, .table-hr-icon td, .table-zebra-icon td {_x000D_
+      		height: 30px !important; padding: 20px 0 20px 20px !important; text-align: left !important;	word-wrap: break-word !important;	overflow-wrap: break-word !important; }_x000D_
+_x000D_
+		 .table-ruler th, .table-ruler td { height: 30px !important;	padding: 20px 0 20px 20px !important; text-align: left !important; word-wrap: break-word !important; overflow-wrap: break-word !important; }_x000D_
+_x000D_
+		 .table-zebra th, .table-zebra td { height: 30px !important;	padding: 20px 0 20px 20px !important; text-align: left !important; word-wrap: break-word !important; overflow-wrap: break-word !important; }_x000D_
+_x000D_
+         .table-ruler th, .table-ruler td, .table-ruler-mobile th, .table-ruler-mobile td, .table-hr-icon td { _x000D_
+         border-bottom: 1px solid #E0E0E0 !important;}_x000D_
+         .table-zebra-mobile th, .table-zebra-mobile td {border-bottom : 1px solid #ffffff !important;}_x000D_
+         .table-ruler-mobile, .table-hr-icon {border-top: 1px solid #E0E0E0;}_x000D_
+         .table-ruler-mobile th, .table-zebra-mobile th {font-weight: 600 !important;}_x000D_
+         .table-zebra-icon .odd-row td, .table-zebra .odd-row td, .table-zebra-mobile .odd-row td {background-color: #F6F6F6;}_x000D_
+         .table-zebra th, .table-zebra-mobile th {background-color: #e7e7e7;}_x000D_
+		 .hero-text-center {text-align: center !important;padding: 0 30px !important;}_x000D_
+		 .intro-tile-image { padding:10px 20px 10px 10px !important;}_x000D_
+		 .intro-tile-text  {padding:0 10px 0 0}_x000D_
+		 .intro-tile-text-20 {padding: 0 20px 0 0;}_x000D_
+         .intro-tile-image-20 {padding: 20px 20px 20px 20px !important;}_x000D_
+         .image-tile-10 { padding:10px 0px 0px 10px !important;}_x000D_
+         .image-tile-20 {padding: 20px 0px 0px 20px !important;}_x000D_
+         .email-table th table td { font-weight:600 !important;}_x000D_
+         /* Tabular Data Ends */_x000D_
+         @media only screen and (max-width: 640px) {_x000D_
+         .mobileHide {display:none;line-height:0; mso-hide: all;max-height: 0; max-width: 0; width:0;}_x000D_
+         } _x000D_
+		 /* Responsive classes for mobile starts here */_x000D_
+         @media only screen and (max-width: 480px) {         _x000D_
+		 .wrapper, .table-hr-icon, .table-zebra-icon, .email-table {width: 100%!important;}_x000D_
+         /* Stack */_x000D_
+		 .text-card-padding {padding: 0px 40px 0px 40px !important;}_x000D_
+         img.photo {display:block !important; width:100% !important; height:auto !important;}_x000D_
+         .block, .block-text-align-right, .desktopHidden {width:100% !important; display:block !important;}_x000D_
+         .blockLast {width:100% !important; display:block !important; padding-bottom:20px !important;}_x000D_
+		 .app-download-block th, .btn-block, .btn-block-right {display: block !important; width: auto !important;}_x000D_
+		 .block-max-width, .block-max-width-center{ max-width: none !important; display: block !important; width: auto !important;}_x000D_
+         .addressText {font-size:10px !important;}_x000D_
+		 .mobileHidden, .table-ruler, .table-zebra {display: none !important;}   _x000D_
+		 .mobileBody {width:288px !important;}_x000D_
+         .mobileBodyPadding {padding:10px 20px 35px 20px !important; width:288px !important;}_x000D_
+         .mobileNoPadding {padding:0 !important;}_x000D_
+         .mobileGutter {width:15px !important;}_x000D_
+		 .mobile-block-padd-top-30 {display: block !important;padding-top: 30px;width: 100%;}_x000D_
+         .mobileCTA {width:258px !important;}_x000D_
+         .mobileCTABody {margin:0 auto !important;}_x000D_
+         .mobileHeight {height:auto !important;}_x000D_
+         .mobileOnly, _x000D_
+         .mobileOnly img, _x000D_
+         .mobileOnly, _x000D_
+         .mobileOnly {display:block !important; margin:0 !important; padding:20px 0 0 0 !important; overflow:visible !important; width:auto !important; max-height:inherit !important; height:1px !important; position: relative !important; top: 0px !important; border-bottom:1px solid #1e90ff;}_x000D_
+         .mobileTopPad5 { padding-top: 5px !important; }_x000D_
+         .mobileTopPad10 { padding-top: 10px !important; } _x000D_
+         .mobileWidthAdj { width: 70px !important; } _x000D_
+         .mobileBody { width: 288px !important;}_x000D_
+         .hide{display:none;}_x000D_
+         .show{display:none;}_x000D_
+         .desktophide{display:block!important;}_x000D_
+         .mobileFont{font-size:30px!important;line-height:30px!important;}_x000D_
+         .mobilepadding-right{padding-right:40px;}_x000D_
+         .icon-top-padding{padding-top:40px!important;}_x000D_
+         .w-100p{width:100%!important;}_x000D_
+         .p-0{padding:0!important;}_x000D_
+         .flex{display:block!important;width:100%!important;box-sizing:border-box!important;}_x000D_
+         .thold{display:table!important;width:100%!important;}_x000D_
+         .thead{display:table-header-group!important;width:100%!important;}_x000D_
+         .trow{display:table-row!important;width:100%!important;}_x000D_
+         .tfoot{display:table-footer-group!important;width:100%!important;}_x000D_
+         .pr-24{padding-right:24px!important;}_x000D_
+         .mobile-padding-20{padding-left:20px!important; padding-right:20px!important;}_x000D_
+         .mobile-padding-rght-20{padding-left:0px!important; padding-right:20px!important;}_x000D_
+         .mobile-social-table{text-align:center!important;}_x000D_
+         .mobile-social-padd-btm{padding-bottom:35px!important;}_x000D_
+		 .mobile-social-padd-btm-top{padding-bottom:35px!important;}_x000D_
+         .mobile-social-marg-btm{margin-top:20px!important;}_x000D_
+		 .mobile-social-inline{display:inline-block!important; padding-right:2px!important;}_x000D_
+		 .mobile-social-margin-lft{margin-left:10px!important;}		 _x000D_
+		 .logo-mobile-img{width:85px!important;height:18px!important;}_x000D_
+		 .mobile-monthly-padd-left{padding-left:20px!important;}_x000D_
+		 .secondary-logo-padd-left{ padding-left:0px!important;}_x000D_
+         .secondary-logo-padd-left-20{ padding-left:20px!important;}_x000D_
+         .mobile-txt-center {text-align: center!important;}_x000D_
+         .social-text-pad-rght{padding-right:20px!important;padding-bottom:0px!important;}_x000D_
+		 .followus-pad-top{padding-top:20px!important;}_x000D_
+		 .banner-image-txt-only{max-height: 48.4%!important;}_x000D_
+		 .banner-hero-imghgt-mobile{height: 160px!important;}		 			_x000D_
+		.card-padding {padding-left: 20px!important; padding-right: 20px!important; padding-top: 40px!important; padding-bottom: 40px!important;}_x000D_
+		.thead {display: table-header-group!important; width: 100%!important;}_x000D_
+		.mobile-card-table {width: 100%!important;}_x000D_
+		.mobile-txt-center {text-align: center!important;}_x000D_
+		.mobile-card-img-size {width: 100%!important;}_x000D_
+		.tfoot {display: table-footer-group!important; width: 100%!important;}_x000D_
+		.mobile-card-padding-top-padd {padding-top: 40px!important;}_x000D_
+		.mobile-card-margin-btm40 {margin-bottom: 40px!important;}_x000D_
+		.mobile-card-margin-btm30 {margin-bottom: 40px!important;}_x000D_
+		.mobile-cta-padd-bottom{padding-bottom:40px!important;}_x000D_
+		.tile-pad-large-4 {padding-left: 20px !important; padding-right: 20px !important;}_x000D_
+		.tile-pad-large {padding-left: 60px !important; padding-right: 60px !important;}_x000D_
+		.tile-pad-small-v1 {padding-left: 20px !important; padding-right: 20px !important;}_x000D_
+		.tile-pad-small-v2 {padding-left: 20px !important; padding-right: 20px !important;}_x000D_
+		.tile-pad-small-v3 {padding-left: 20px !important; padding-right: 20px !important;}_x000D_
+		.tile-pad-small-v5 {padding-left: 55px !important; padding-right: 55px !important;}_x000D_
+		.mob-padd-top-zero {padding-top: 0px !important;}_x000D_
+        .boxed-list-wrapper {padding: 20px 20px 0 !important;}_x000D_
+        .gutter {padding:0 20px!important;}_x000D_
+		.mobile-padding-left-20{padding-left:24px;}_x000D_
+		.mobile-text-only-pad{padding-left: 0px !important;}_x000D_
+		.mob-gutter { padding-left: 20px !important; padding-right: 20px !important; }_x000D_
+		.block-padd-top-30 { display: block !important; padding-top: 30px; }_x000D_
+		.mobile-bottom-padding-20 { padding: 0 0 20px 0 !important;}_x000D_
+		.learn-more-img{padding-top:40px; width: 100%;}_x000D_
+		.hero-mobile { width: 100% !important; max-width: 100% !important; height: auto !important;}_x000D_
+        .hero-text-center {padding: 0 20px !important;}		_x000D_
+		/*Tabular Data Starts */_x000D_
+         .spacer-mob-30 {height: 30px !important;}_x000D_
+         .spacer-mob-20 {height: 20px !important;}        _x000D_
+         .table-zebra-mobile, .table-ruler-mobile {display: table !important;}_x000D_
+         .table-ruler-mobile td, .table-zebra-mobile td, .table-ruler-mobile th, .table-zebra-mobile th {padding: 20px !important;}_x000D_
+         .table-hr-icon td, .table-zebra-icon td {min-width: 16px !important; max-width: 150px !important;}_x000D_
+         /*Tabular Data Ends */_x000D_
+		.hero-xl-mobile,.hero-custom,.hero-lg-mobile,.hero-md-mobile,.hero-sm-mobile {width: 100% !important; max-width: 100% !important; height: auto !important;}_x000D_
+		.rtl-template .block-text-align-right { text-align: right !important;}_x000D_
+        .thold { display: table !important; width: 100% !important; }_x000D_
+		.thead { display: table-header-group !important; width: 100% !important; }_x000D_
+		.tfoot { display: table-footer-group !important; width: 100% !important; }_x000D_
+		.email-banner-image { display: block !important; margin-left: auto; margin-right: auto}_x000D_
+        .email-banner-padding { padding-left:20px !important; padding-right:20px !important; }_x000D_
+_x000D_
+         }_x000D_
+		 /* Responsive classes for mobile Ends here */_x000D_
+		 _x000D_
+         ul { margin:0 !important;padding-left:22px !important;text-align: left !important;}_x000D_
+         ol { margin-top:0 !important;margin-bottom:0 !important;padding-left:22px !important;text-align: left !important;}_x000D_
+		 li{padding: 0 0 8px 12px !important;margin: 0 !important;}_x000D_
+		 li a {text-decoration: underline; color: #0067B8;}_x000D_
+         *[class].gmailfix {display:none; display:none!important;}_x000D_
+      _x000D_
+     _x000D_
+		_x000D_
+		p { mso-hyphenate: none;}_x000D_
+        .rtl-template,_x000D_
+        .rtl-template td{_x000D_
+        direction: ltr !important;_x000D_
+        text-align: right !important;_x000D_
+        }_x000D_
+        .rtl-template p {_x000D_
+        direction: rtl !important;_x000D_
+        text-align: right !important;_x000D_
+        }_x000D_
+        .text-rtl-center .list-item-right p {_x000D_
+		text-align: right !important;_x000D_
+		direction: rtl !important;_x000D_
+		}_x000D_
+        .rtl-template .email-header p {_x000D_
+        direction: rtl !important;_x000D_
+        text-align: left !important;_x000D_
+        }_x000D_
+        .email-table th table td {_x000D_
+		font-weight:600 !important;_x000D_
+		}_x000D_
+		.text-rtl-center p,_x000D_
+        .rtl-template .email-table .text-center p,_x000D_
+        .rtl-template .email-table .text-center td {_x000D_
+			direction: rtl !important;_x000D_
+			text-align: center !important;_x000D_
+		}_x000D_
+		.email-table .text-center p,_x000D_
+		.email-table .text-center td {_x000D_
+			text-align:center !important;_x000D_
+		}_x000D_
+        .email-table .text-left p,_x000D_
+        .email-table .text-left td {_x000D_
+         text-align:left !important;_x000D_
+        }_x000D_
+        .footer-address-center td,_x000D_
+		.footer-address-center td p,_x000D_
+		.footer-address-center td p a{_x000D_
+				text-align:center !important;_x000D_
+				direction:ltr !important;_x000D_
+		}_x000D_
+ 		.cta-button{_x000D_
+		font-weight:normal !important;_x000D_
+		}_x000D_
+		li _x000D_
+         {_x000D_
+         margin: 0 0 8px 0 !important;_x000D_
+         text-align: left !important;_x000D_
+         }_x000D_
+         div.list ul li {_x000D_
+         mso-special-format: bullet;_x000D_
+         }_x000D_
+         div.list {_x000D_
+         margin: 0 0 0 -20px;_x000D_
+         }_x000D_
+         div li.list-bottom{_x000D_
+            margin-bottom: 28px !important;_x000D_
+         }_x000D_
+         .rtl-template li _x000D_
+         {_x000D_
+         margin: 0 0 8px 0 !important;_x000D_
+         text-align: right !important;_x000D_
+         direction : rtl !important;_x000D_
+         }_x000D_
+        .rtl-template div.list _x000D_
+         {_x000D_
+         Margin: 0 -20px 0 0;_x000D_
+         }_x000D_
+		 .rtl-template .footeraddressrtl p,_x000D_
+         .rtl-template .footeraddressrtl  {_x000D_
+         direction: ltr !important; _x000D_
+         text-align:right !important;_x000D_
+         }_x000D_
+         .footeraddressrtl {_x000D_
+         mso-padding-alt: 0 30px !important;_x000D_
+         }_x000D_
+         .text-rtl-center .footeraddressrtl p, _x000D_
+         .rtl-template .footeraddressrtl  { _x000D_
+         direction: ltr !important;  _x000D_
+         text-align:center !important; _x000D_
+         }_x000D_
+         .text-rtl-center .txt-align-right td {_x000D_
+		  text-align:right !important;_x000D_
+			}_x000D_
+		 .txt-center ul li,_x000D_
+         .txt-center ol li_x000D_
+         {_x000D_
+            text-align:center !important;_x000D_
+         }_x000D_
+_x000D_
+		 .rte-spacer-20 p _x000D_
+		 {_x000D_
+			mso-margin-bottom-alt: 20px;_x000D_
+		 }_x000D_
+		 .rte-spacer-10 p _x000D_
+		 {_x000D_
+	        mso-margin-bottom-alt: 10px;_x000D_
+         }_x000D_
+         .rte-footerspacer-10 p {_x000D_
+	        mso-margin-top-alt: 10px;_x000D_
+         }_x000D_
+         .rtl-template th.tileimage {_x000D_
+         	direction: ltr !important;_x000D_
+         }		 _x000D_
+		 .table-hr-icon td,_x000D_
+         .table-zebra-icon td,_x000D_
+         .table-zebra td,_x000D_
+         .table-zebra th,_x000D_
+         .table-zebra-mobile td,_x000D_
+         .table-zebra-mobile th,_x000D_
+         .table-ruler td,_x000D_
+         .table-ruler th,_x000D_
+         .table-ruler-mobile td,_x000D_
+         .table-ruler-mobile th_x000D_
+         {_x000D_
+			mso-padding-alt: 20px 0 20px 20px !important;_x000D_
+         }_x000D_
+		 .rtl-template .table-ruler th,_x000D_
+		 .rtl-template .table-zebra th {_x000D_
+			direction: rtl !important;_x000D_
+		 }_x000D_
+		 .rtl-template .rating-thumbs-down {_x000D_
+			padding-left:1px;    _x000D_
+		 }_x000D_
+		 table {_x000D_
+			border-spacing: 0; _x000D_
+			mso-margin-bottom-alt: 0; _x000D_
+			mso-margin-top-alt: 0; _x000D_
+			mso-table-lspace: 0pt; _x000D_
+			mso-table-rspace: 0pt;_x000D_
+		}_x000D_
+		td ,th {_x000D_
+		mso-table-lspace: 0pt !important;_x000D_
+		mso-table-rspace: 0pt !important;_x000D_
+		}_x000D_
+		.mso-line-ht-rule {_x000D_
+		  mso-line-height-rule: exactly;_x000D_
+		}_x000D_
+        .hero-text-center p{_x000D_
+            text-align: center !important;_x000D_
+        }_x000D_
+        _x000D_
+	_x000D_
+_x000D_
+    _x000D_
+   _x000D_
+    _x000D_
+	_x000D_
+_x000D_
+_x000D_
+_x000D_
+      Action requise pour accéder à votre contenu sur tous vos appareils_x000D_
+			_x000D_
+				&amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp;&amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp;&amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp;&amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp;&amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp; &amp;#847; &amp;zwnj; &amp;nbsp;_x000D_
+			_x000D_
+      _x000D_
+      _x000D_
+         &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; _x000D_
+         &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; _x000D_
+         &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp;_x000D_
+      _x000D_
+      _x000D_
+	  _x000D_
+	  		  _x000D_
+	  _x000D_
+	  _x000D_
+         _x000D_
+      		_x000D_
+               _x000D_
+                  _x000D_
+				  _x000D_
+                  _x000D_
+				  _x000D_
+				  _x000D_
+				  _x000D_
+				  _x000D_
+                     _x000D_
+					    _x000D_
+						_x000D_
+						   _x000D_
+								_x000D_
+    _x000D_
+    _x000D_
+    _x000D_
+        _x000D_
+            _x000D_
+                _x000D_
+                    _x000D_
+                        _x000D_
+                        _x000D_
+                            _x000D_
+                                _x000D_
+                                    _x000D_
+                                        _x000D_
+                                            _x000D_
+                                                _x000D_
+                                                    Accédez à votre OneDrive |_x000D_
+                                                _x000D_
+                                                                                                    Afficher dans un navigateur_x000D_
+                                                _x000D_
+                                            _x000D_
+                                        _x000D_
+                                    _x000D_
+                                _x000D_
+                            _x000D_
+                        _x000D_
+                    _x000D_
+                _x000D_
+            _x000D_
+        _x000D_
+    _x000D_
+_x000D_
+							_x000D_
+						_x000D_
+						_x000D_
+					_x000D_
+                     	_x000D_
+                     	_x000D_
+                     		_x000D_
+                     			_x000D_
+	_x000D_
+	_x000D_
+		_x000D_
+	_x000D_
+	_x000D_
+	_x000D_
+		_x000D_
+			_x000D_
+			_x000D_
+				_x000D_
+   _x000D_
+       &amp;#xA0;_x000D_
+   _x000D_
+_x000D_
+				_x000D_
+					_x000D_
+						_x000D_
+							_x000D_
+_x000D_
+							_x000D_
+						_x000D_
+						_x000D_
+					_x000D_
+				_x000D_
+				_x000D_
+   _x000D_
+       &amp;#xA0;_x000D_
+   _x000D_
+_x000D_
+			_x000D_
+			_x000D_
+		_x000D_
+	_x000D_
+_x000D_
+		_x000D_
+		_x000D_
+		_x000D_
+		_x000D_
+		_x000D_
+	_x000D_
+_x000D_
+_x000D_
+                     		_x000D_
+                     	_x000D_
+                     	_x000D_
+						_x000D_
+                     		_x000D_
+                                _x000D_
+_x000D_
+    _x000D_
+   _x000D_
+   _x000D_
+   _x000D_
+      _x000D_
+         _x000D_
+            _x000D_
+               _x000D_
+               _x000D_
+                  _x000D_
+    _x000D_
+    _x000D_
+        _x000D_
+            &amp;#xA0;_x000D_
+        _x000D_
+    _x000D_
+_x000D_
+               _x000D_
+            _x000D_
+            _x000D_
+               _x000D_
+                  _x000D_
+                     _x000D_
+    _x000D_
+_x000D_
+    _x000D_
+        _x000D_
+_x000D_
+        _x000D_
+_x000D_
+        _x000D_
+_x000D_
+        _x000D_
+_x000D_
+        _x000D_
+            _x000D_
+            _x000D_
+                &lt;p style="color:#000000;_x000D_
+                        font-family:Segoe UI, Helvetica, Arial, sans-serif;font-style: normal;font-weight:600; font-size:32px;line-height:40px;letter-spacing:-0.02em;margin:0; padding:0;" role="heading" aria-level="3"&gt; Gérez votre stockage dès maintenant pour ne pas perdre l’accès à vos photos et à vos fichiers _x000D_
+            _x000D_
+        _x000D_
+_x000D_
+        _x000D_
+_x000D_
+        _x000D_
+_x000D_
+        _x000D_
+_x000D_
+        _x000D_
+_x000D_
+        _x000D_
+    _x000D_
+_x000D_
+                  _x000D_
+               _x000D_
+               _x000D_
+    _x000D_
+    _x000D_
+        _x000D_
+            &amp;#xA0;_x000D_
+        _x000D_
+    _x000D_
+_x000D_
+            _x000D_
+            _x000D_
+            _x000D_
+            _x000D_
+               _x000D_
+                  _x000D_
+                     _x000D_
+                        _x000D_
+                           _x000D_
+                              _x000D_
+                                 _x000D_
+                                    _x000D_
+                                       _x000D_
+                                          _x000D_
+                         _x000D_
+                                             _x000D_
+                                                _x000D_
+                                                   _x000D_
+_x000D_
+   _x000D_
+_x000D_
+   _x000D_
+_x000D_
+   _x000D_
+_x000D_
+	   _x000D_
+	_x000D_
+		_x000D_
+		_x000D_
+		_x000D_
+			_x000D_
+				_x000D_
+					_x000D_
+						_x000D_
+_x000D_
+						_x000D_
+					_x000D_
+					_x000D_
+				_x000D_
+			_x000D_
+		_x000D_
+		_x000D_
+		_x000D_
+		_x000D_
+		_x000D_
+		_x000D_
+		_x000D_
+		_x000D_
+		_x000D_
+		_x000D_
+		_x000D_
+		_x000D_
+		_x000D_
+		_x000D_
+		_x000D_
+    _x000D_
+    _x000D_
+        _x000D_
+            &amp;#xA0;_x000D_
+        _x000D_
+    _x000D_
+_x000D_
+		_x000D_
+	_x000D_
+_x000D_
+      _x000D_
+      _x000D_
+      _x000D_
+      _x000D_
+      _x000D_
+      _x000D_
+      _x000D_
+      _x000D_
+      _x000D_
+_x000D_
+   _x000D_
+_x000D_
+_x000D_
+                                                _x000D_
+                                                _x000D_
+                                                _x000D_
+                                                _x000D_
+                                                _x000D_
+                                                _x000D_
+                                                _x000D_
+                                                _x000D_
+                                                _x000D_
+                                                _x000D_
+                                                _x000D_
+                                                _x000D_
+                                                _x000D_
+                                                _x000D_
+                                                _x000D_
+                                                _x000D_
+                                             _x000D_
+                                             _x000D_
+                                          _x000D_
+                                       _x000D_
+                                    _x000D_
+                                 _x000D_
+                              _x000D_
+                           _x000D_
+                        _x000D_
+                     _x000D_
+                  _x000D_
+                  _x000D_
+               _x000D_
+            _x000D_
+            _x000D_
+            _x000D_
+               _x000D_
+                  _x000D_
+    _x000D_
+        _x000D_
+        _x000D_
+    _x000D_
+    _x000D_
+_x000D_
+               _x000D_
+               _x000D_
+            _x000D_
+         _x000D_
+      _x000D_
+   _x000D_
+_x000D_
+_x000D_
+    _x000D_
+	_x000D_
+	_x000D_
+	_x000D_
+		_x000D_
+			_x000D_
+			_x000D_
+			_x000D_
+    _x000D_
+        _x000D_
+        _x000D_
+            _x000D_
+                _x000D_
+                &amp;#xA0;_x000D_
+            _x000D_
+        _x000D_
+    _x000D_
+    _x000D_
+_x000D_
+			_x000D_
+			_x000D_
+			_x000D_
+			_x000D_
+			_x000D_
+			_x000D_
+				_x000D_
+					_x000D_
+						_x000D_
+							_x000D_
+_x000D_
+							_x000D_
+								_x000D_
+    _x000D_
+        _x000D_
+        _x000D_
+            _x000D_
+                _x000D_
+                &amp;#xA0;_x000D_
+            _x000D_
+        _x000D_
+    _x000D_
+    _x000D_
+_x000D_
+							_x000D_
+_x000D_
+							_x000D_
+						_x000D_
+						_x000D_
+						_x000D_
+						_x000D_
+						_x000D_
+							_x000D_
+    _x000D_
+    _x000D_
+        _x000D_
+            &amp;#xA0;_x000D_
+        _x000D_
+    _x000D_
+_x000D_
+								_x000D_
+									_x000D_
+										_x000D_
+										_x000D_
+											_x000D_
+												_x000D_
+												_x000D_
+													_x000D_
+														_x000D_
+														_x000D_
+														_x000D_
+														L’espace yessineht@gmail.com de stockage de votre compte Microsoft a&amp;nbsp;actuellement&amp;nbsp;0&amp;nbsp;bytes&amp;nbsp;dépassé la limite de 5&amp;nbsp;GB.&amp;nbsp;Lorsque votre espace de stockage est plein, vous ne pouvez plus&amp;nbsp;:_x000D_
+_x000D_
+ Enregistrer et sauvegarder de nouveaux fichiers, photos ou vidéos sur OneDrive&amp;nbsp;_x000D_
+ Synchroniser des fichiers sur vos appareils_x000D_
+ Envoyer et recevoir des e-mails depuis Outlook.com_x000D_
+_x000D_
+Pour pouvoir à nouveau utiliser votre espace de stockage et votre messagerie, gérez votre espace de stockage en supprimant les fichiers dont vous n’avez pas besoin. Vous pouvez également mettre à niveau votre abonnement Microsoft&amp;nbsp;365 pour bénéficier de plus d’espace stockage_x000D_
+														_x000D_
+														_x000D_
+														_x000D_
+													_x000D_
+												_x000D_
+											_x000D_
+										_x000D_
+										_x000D_
+									_x000D_
+								_x000D_
+						_x000D_
+						_x000D_
+						_x000D_
+						_x000D_
+							_x000D_
+								_x000D_
+    _x000D_
+        _x000D_
+        _x000D_
+            _x000D_
+                _x000D_
+                &amp;#xA0;_x000D_
+            _x000D_
+        _x000D_
+    _x000D_
+    _x000D_
+_x000D_
+							_x000D_
+							_x000D_
+							_x000D_
+							_x000D_
+						_x000D_
+					_x000D_
+				_x000D_
+			_x000D_
+			_x000D_
+			_x000D_
+			_x000D_
+			_x000D_
+			_x000D_
+			_x000D_
+			_x000D_
+			_x000D_
+		_x000D_
+	_x000D_
+_x000D_
+_x000D_
+    _x000D_
+_x000D_
+   _x000D_
+_x000D_
+   _x000D_
+_x000D_
+   _x000D_
+      _x000D_
+         _x000D_
+            _x000D_
+    _x000D_
+        _x000D_
+        _x000D_
+    _x000D_
+    _x000D_
+_x000D_
+            _x000D_
+               _x000D_
+_x000D_
+                  _x000D_
+                     _x000D_
+   _x000D_
+   _x000D_
+   _x000D_
+   _x000D_
+   _x000D_
+   _x000D_
+   _x000D_
+   _x000D_
+      _x000D_
+         _x000D_
+            _x000D_
+               _x000D_
+			    _x000D_
+                    _x000D_
+                        _x000D_
+                  _x000D_
+                     _x000D_
+                        _x000D_
+                           _x000D_
+                           _x000D_
+                              _x000D_
+                                 _x000D_
+                                    _x000D_
+                                    _x000D_
+                                       							  _x000D_
+                                 _x000D_
+                                 _x000D_
+                                 _x000D_
+                                 _x000D_
+                                 _x000D_
+                                    _x000D_
+                                    _x000D_
+                                       _x000D_
+                                          _x000D_
+                                             _x000D_
+                                                _x000D_
+                                                   _x000D_
+    _x000D_
+    _x000D_
+	_x000D_
+        _x000D_
+        _x000D_
+            _x000D_
+                Obtenir plus d’espace de stockage_x000D_
+                _x000D_
+            _x000D_
+        _x000D_
+	_x000D_
+	_x000D_
+    _x000D_
+_x000D_
+                                                _x000D_
+                                             _x000D_
+                                          _x000D_
+                                       _x000D_
+                                    _x000D_
+                                 _x000D_
+                              _x000D_
+             </t>
+  </si>
+  <si>
+    <t>"Firas via Messenger" &lt;messages@facebookmail.com&gt;
+Hi Yessine,_x000D_
+_x000D_
+[https://facebook.com/email/appredirect/?rid=100004844588432&amp;fallback_uri=https%3A%2F%2Fwww.facebook.com%2Ffiras.hadjtaieb1998&amp;native_uri=fb%3A%2F%2Fprofile%2F100086414921033&amp;email_type=email] _x000D_
+_x000D_
+View message[https://www.facebook.com/messenger/email/?recipient_fbid=100004844588432&amp;sender_fbid=100086414921033&amp;thread_fbid=7876397999072048&amp;is_group_thread=0&amp;source=msg&amp;notif_id=1773950642411370&amp;cta_type=view_message_body&amp;is_fbm_redirect=0&amp;is_e2ee_thread=1] _x000D_
+_x000D_
+Go to profile[https://facebook.com/email/appredirect/?rid=100004844588432&amp;fallback_uri=https%3A%2F%2Fwww.facebook.com%2Ffiras.hadjtaieb1998&amp;native_uri=fb%3A%2F%2Fprofile%2F100086414921033&amp;email_type=email] _x000D_
+_x000D_
+Thanks,_x000D_
+The Facebook team_x000D_
+_x000D_
+_x000D_
+_x000D_
+========================================_x000D_
+This message was sent to yessineht@gmail.com. If you don't want to receive these emails from Meta in the future, please follow the link below to unsubscribe._x000D_
+https://www.facebook.com/o.php?k=AS3zG75gr_Yk47pY3s0&amp;u=100004844588432&amp;mid=64d65c84dd498G5af4313ccd90G64d6611e3d76aG8431&amp;ee=Af88QLM7Ebz3RpXJFgIOTjJsnAviBbVDdeh1m4ppS0gxMNuoHbdFdjAK_AfKlsQqVSwSzSXGrA26e0curw_x000D_
+Meta Platforms, Inc., Attention: Community Support, 1 Meta Way, Menlo Park, CA 94025</t>
+  </si>
+  <si>
+    <t>GitHub &lt;noreply@github.com&gt;
+A GitHub App, Vercel, installed on your account is requesting updated permissions._x000D_
+_x000D_
+Visit https://github.com/settings/installations/96614029/permissions/update to review and accept these permissions._x000D_
+_x000D_
+You may choose to ignore this request, in which case Vercel will retain its current permissions._x000D_
+_x000D_
+You can view pending requests directly by visiting your account’s settings page and clicking on Applications. If you run into problems, please contact support by visiting https://support.github.com/contact?tags=dotcom-integrations._x000D_
+_x000D_
+Thanks,_x000D_
+Your friends at GitHub</t>
+  </si>
+  <si>
+    <t>noreply@codeforces.com
+Hello ToNy_IV,_x000D_
+_x000D_
+I'm glad to invite you to take part in Codeforces Round 1087. It starts on Saturday, March, 21, 2026 14:35 (UTC). The contest duration is 2 hours. The allowed programming languages are C/C++, Python, Java, Kotlin, Rust, Go, C#, F#, Pascal/Delphi, JavaScript, D, Haskell, OCaml, Perl, PHP, Ruby, Scala._x000D_
+_x000D_
+Register Now →  The round writers are OtterZ, __baozii__. Don't miss the round!_x000D_
+_x000D_
+It will be for newbies and participants from the second division (non-rated users or those whose rating is below 2100). The round will be held on the rules of Codeforces, so read the rules (here and here) beforehand. Want to compete? Do not forget to register for the contest and check your handle on the registration page. The registration will be closed 5 minutes before the contest._x000D_
+_x000D_
+If you have any questions, please feel free to ask me on the pages of Codeforces. If you no longer wish to receive these emails, click https://codeforces.com/unsubscribe/contests/d51b03ab8bc362dd4f31ca9111e5b0937d3fe9c1/ to unsubscribe._x000D_
+_x000D_
+Wish you high rating, Mike Mirzayanov and Codeforces team</t>
+  </si>
+  <si>
+    <t>daily.dev &lt;informer@daily.dev&gt;
+We picked posts from your topics based on what the community found useful  _x000D_
+_x000D_
+*******_x000D_
+For you_x000D_
+*******_x000D_
+_x000D_
+​Mar 20, 2026_x000D_
+_x000D_
+Logo ( https://app.daily.dev/ )_x000D_
+_x000D_
+daily.dev Changelog ( https://app.daily.dev/posts/USrnh71PU?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+daily.dev skills are here ( https://app.daily.dev/posts/USrnh71PU?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+--------------------------------------------------------------------------------------------------------------------------------_x000D_
+_x000D_
+Read_x000D_
+article → ( https://app.daily.dev/posts/USrnh71PU?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+Addy Osmani ( https://app.daily.dev/posts/kthBgt6Kn?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+14 More Lessons from 14 years at Google ( https://app.daily.dev/posts/kthBgt6Kn?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+----------------------------------------------------------------------------------------------------------------------------------------------_x000D_
+_x000D_
+Read_x000D_
+article → ( https://app.daily.dev/posts/kthBgt6Kn?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+( https://api.daily.dev/v2/c?id=eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJPYmplY3QiOnsiaSI6ImYwMDM0Nzk2LTMxMTktNGRjOS04YTEzLTJhYzMyYjk1ZTE0NiIsInUiOiJodHRwczovL2NvZGVyYWJiaXQubGluay9kYWlseSIsImFpIjoiNTMwOTMxMWEtYWFhZi00NjdiLTg2MzQtNzA5OTk3OTI4ODI2IiwiYyI6IjQ2NjE2ZWU1LWFhZDktNDk3Yi1hZjJlLTU5MmI0NjlhYmU2YSIsImEiOiJiYzNmMmFjZi05MDQxLTQzNDAtOTY4OC1hYWQ3ZDAyMGRmM2YiLCJ0aWQiOiJhMTJmYTg4Ny03ZWU5LTQzM2ItYTkxYy1lZDAxN2FlZDVmOTkiLCJ0aWRzIjpbImExMmZhODg3LTdlZTktNDMzYi1hOTFjLWVkMDE3YWVkNWY5OSJdLCJjciI6ImI5ZTI5YTg1LWJmY2YtNGJmYy05MTBlLTI4YTA3Nzc2MjE3MSIsInVzIjoiNHM1YldiZUZzUjB5aDJhbDVreUFQIiwidCI6MTc3Mzk4Mjk2MX19.T9ggwYCslcPZooiW960CTFYqaZBMQDxaTMVgM20um4M )_x000D_
+_x000D_
+CodeRabbit_x000D_
+· Ad ( https://api.daily.dev/v2/c?id=eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJPYmplY3QiOnsiaSI6ImYwMDM0Nzk2LTMxMTktNGRjOS04YTEzLTJhYzMyYjk1ZTE0NiIsInUiOiJodHRwczovL2NvZGVyYWJiaXQubGluay9kYWlseSIsImFpIjoiNTMwOTMxMWEtYWFhZi00NjdiLTg2MzQtNzA5OTk3OTI4ODI2IiwiYyI6IjQ2NjE2ZWU1LWFhZDktNDk3Yi1hZjJlLTU5MmI0NjlhYmU2YSIsImEiOiJiYzNmMmFjZi05MDQxLTQzNDAtOTY4OC1hYWQ3ZDAyMGRmM2YiLCJ0aWQiOiJhMTJmYTg4Ny03ZWU5LTQzM2ItYTkxYy1lZDAxN2FlZDVmOTkiLCJ0aWRzIjpbImExMmZhODg3LTdlZTktNDMzYi1hOTFjLWVkMDE3YWVkNWY5OSJdLCJjciI6ImI5ZTI5YTg1LWJmY2YtNGJmYy05MTBlLTI4YTA3Nzc2MjE3MSIsInVzIjoiNHM1YldiZUZzUjB5aDJhbDVreUFQIiwidCI6MTc3Mzk4Mjk2MX19.T9ggwYCslcPZooiW960CTFYqaZBMQDxaTMVgM20um4M )_x000D_
+_x000D_
+AI code reviews for teams that move fast (but don't break things) ( https://api.daily.dev/v2/c?id=eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJPYmplY3QiOnsiaSI6ImYwMDM0Nzk2LTMxMTktNGRjOS04YTEzLTJhYzMyYjk1ZTE0NiIsInUiOiJodHRwczovL2NvZGVyYWJiaXQubGluay9kYWlseSIsImFpIjoiNTMwOTMxMWEtYWFhZi00NjdiLTg2MzQtNzA5OTk3OTI4ODI2IiwiYyI6IjQ2NjE2ZWU1LWFhZDktNDk3Yi1hZjJlLTU5MmI0NjlhYmU2YSIsImEiOiJiYzNmMmFjZi05MDQxLTQzNDAtOTY4OC1hYWQ3ZDAyMGRmM2YiLCJ0aWQiOiJhMTJmYTg4Ny03ZWU5LTQzM2ItYTkxYy1lZDAxN2FlZDVmOTkiLCJ0aWRzIjpbImExMmZhODg3LTdlZTktNDMzYi1hOTFjLWVkMDE3YWVkNWY5OSJdLCJjciI6ImI5ZTI5YTg1LWJmY2YtNGJmYy05MTBlLTI4YTA3Nzc2MjE3MSIsInVzIjoiNHM1YldiZUZzUjB5aDJhbDVreUFQIiwidCI6MTc3Mzk4Mjk2MX19.T9ggwYCslcPZooiW960CTFYqaZBMQDxaTMVgM20um4M )_x000D_
+---------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------_x000D_
+_x000D_
+Get Started Today ( https://api.daily.dev/v2/c?id=eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJPYmplY3QiOnsiaSI6ImYwMDM0Nzk2LTMxMTktNGRjOS04YTEzLTJhYzMyYjk1ZTE0NiIsInUiOiJodHRwczovL2NvZGVyYWJiaXQubGluay9kYWlseSIsImFpIjoiNTMwOTMxMWEtYWFhZi00NjdiLTg2MzQtNzA5OTk3OTI4ODI2IiwiYyI6IjQ2NjE2ZWU1LWFhZDktNDk3Yi1hZjJlLTU5MmI0NjlhYmU2YSIsImEiOiJiYzNmMmFjZi05MDQxLTQzNDAtOTY4OC1hYWQ3ZDAyMGRmM2YiLCJ0aWQiOiJhMTJmYTg4Ny03ZWU5LTQzM2ItYTkxYy1lZDAxN2FlZDVmOTkiLCJ0aWRzIjpbImExMmZhODg3LTdlZTktNDMzYi1hOTFjLWVkMDE3YWVkNWY5OSJdLCJjciI6ImI5ZTI5YTg1LWJmY2YtNGJmYy05MTBlLTI4YTA3Nzc2MjE3MSIsInVzIjoiNHM1YldiZUZzUjB5aDJhbDVreUFQIiwidCI6MTc3Mzk4Mjk2MX19.T9ggwYCslcPZooiW960CTFYqaZBMQDxaTMVgM20um4M )_x000D_
+_x000D_
+( https://api.daily.dev/v2/c?id=eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJPYmplY3QiOnsiaSI6ImYwMDM0Nzk2LTMxMTktNGRjOS04YTEzLTJhYzMyYjk1ZTE0NiIsInUiOiJodHRwczovL2NvZGVyYWJiaXQubGluay9kYWlseSIsImFpIjoiNTMwOTMxMWEtYWFhZi00NjdiLTg2MzQtNzA5OTk3OTI4ODI2IiwiYyI6IjQ2NjE2ZWU1LWFhZDktNDk3Yi1hZjJlLTU5MmI0NjlhYmU2YSIsImEiOiJiYzNmMmFjZi05MDQxLTQzNDAtOTY4OC1hYWQ3ZDAyMGRmM2YiLCJ0aWQiOiJhMTJmYTg4Ny03ZWU5LTQzM2ItYTkxYy1lZDAxN2FlZDVmOTkiLCJ0aWRzIjpbImExMmZhODg3LTdlZTktNDMzYi1hOTFjLWVkMDE3YWVkNWY5OSJdLCJjciI6ImI5ZTI5YTg1LWJmY2YtNGJmYy05MTBlLTI4YTA3Nzc2MjE3MSIsInVzIjoiNHM1YldiZUZzUjB5aDJhbDVreUFQIiwidCI6MTc3Mzk4Mjk2MX19.T9ggwYCslcPZooiW960CTFYqaZBMQDxaTMVgM20um4M )_x000D_
+_x000D_
+Tech World With Milan ( https://app.daily.dev/posts/V90BEtMZY?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+You're Not Paid to Write Code ( https://app.daily.dev/posts/V90BEtMZY?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+------------------------------------------------------------------------------------------------------------------------------------_x000D_
+_x000D_
+Read_x000D_
+article → ( https://app.daily.dev/posts/V90BEtMZY?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+Yegor's Blog ( https://app.daily.dev/posts/bTPRCiz9N?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+Fast Software: More Programmers, Not Fewer ( https://app.daily.dev/posts/bTPRCiz9N?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+-------------------------------------------------------------------------------------------------------------------------------------------------_x000D_
+_x000D_
+Read_x000D_
+article → ( https://app.daily.dev/posts/bTPRCiz9N?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+Atomic Spin ( https://app.daily.dev/posts/aeJGGwMeD?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+Upgrade Your Note-Taking Skills ( https://app.daily.dev/posts/aeJGGwMeD?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+--------------------------------------------------------------------------------------------------------------------------------------_x000D_
+_x000D_
+Read_x000D_
+article → ( https://app.daily.dev/posts/aeJGGwMeD?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+Fast-track your growth. Upgrade to plus ( https://app.daily.dev/plus )_x000D_
+_x000D_
+Try daily.dev on mobile (if you haven’t yet)_x000D_
+_x000D_
+( https://apps.apple.com/app/daily-dev/id6740634400 )_x000D_
+daily.dev for iOS ( https://apps.apple.com/app/daily-dev/id6740634400 )_x000D_
+_x000D_
+( https://play.google.com/store/apps/details?id=dev.daily )_x000D_
+daily.dev for Android ( https://play.google.com/store/apps/details?id=dev.daily )_x000D_
+_x000D_
+Explore ( https://app.daily.dev/posts )   |   Discussions ( https://app.daily.dev/discussed )   |   Tags ( https://app.daily.dev/tags )   |   Sources ( https://app.daily.dev/sources )   |   Leaderboard ( https://app.daily.dev/users )_x000D_
+_x000D_
+X ( https://twitter.com/dailydotdev ) Yt ( https://www.youtube.com/c/dailydev )_x000D_
+Inst ( https://www.instagram.com/dailydotdev/ ) Tt ( https://www.tiktok.com/@dailydotdev )_x000D_
+GitHub ( https://github.com/dailydotdev/daily )_x000D_
+This email was intended for Yessine Ht (yessineht@gmail.com)_x000D_
+Settings notifications ( https://app.daily.dev/account/notifications ), account details ( https://app.daily.dev/account/profile ) or unsubscribe ( https://track.customer.io/manage_subscription_preferences/RLnCCQUAAZ0Jn9NU7KOvVPjWI6M53A== ) _x000D_
+_x000D_
+( https://app.daily.dev )Daily Dev Ltd., 9 Derech HaTikva Ganei Tikva, Israel_x000D_
+5591252</t>
+  </si>
+  <si>
+    <t>Ollama &lt;hello@ollama.com&gt;
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+_x000D_
+ _x000D_
+Ollama and NVIDIA have teamed up to make OpenClaw faster and safer:_x000D_
+ * Nemotron 3 Super is available to run with Ollama – a new open model from NVIDIA that ranks #1 on PinchBench (the benchmark_x000D_
+   measuring OpenClaw effectiveness), with 5x more throughput than previous models._x000D_
+_x000D_
+ * NemoClaw is now available with built-in Ollama support to provide a safe environment for your OpenClaw assistant with privacy_x000D_
+   and security guardrails._x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+OpenClaw with Nemotron 3 Super_x000D_
+_x000D_
+Start by downloading Ollama:_x000D_
+ _x000D_
+_x000D_
+Download Ollama [https://ollama.com/download]_x000D_
+_x000D_
+ _x000D_
+Next, run OpenClaw with Nemotron 3 Super via Ollama's cloud:_x000D_
+ _x000D_
+ollama launch openclaw --model nemotron-3-super:cloud_x000D_
+ _x000D_
+Nemotron 3 Super can be used on Ollama's cloud for free._x000D_
+ _x000D_
+For challenging tasks, Ollama's Pro and Max plans [https://ollama.com/pricing] enable your OpenClaw assistant to run multiple_x000D_
+sub-agents and background tasks at the same time._x000D_
+ _x000D_
+On machines with 96GB of VRAM or more, Nemotron 3 Super can also be run locally using Ollama. See the model page_x000D_
+[https://ollama.com/library/nemotron-3-super]._x000D_
+ _x000D_
+_x000D_
+_x000D_
+NemoClaw: run OpenClaw more safely_x000D_
+_x000D_
+NVIDIA's NemoClaw is an open source stack that installs OpenClaw with added privacy and security controls, including_x000D_
+pre-configured support for Ollama._x000D_
+_x000D_
+_x000D_
+curl -fsSL https://nvidia.com/nemoclaw.sh | bash_x000D_
+ _x000D_
+This will install NemoClaw and run its Installer. Enter 2 to select Ollama when prompted:_x000D_
+ _x000D_
+_x000D_
+_x000D_
+_x000D_
+ _x000D_
+When prompted for a model, select nemotron-3-super:cloud (or choose another model you may wish to run)._x000D_
+ _x000D_
+Once OpenClaw is running, connect to it:_x000D_
+ _x000D_
+nemoclaw my-assistant connect_x000D_
+ _x000D_
+For more information on NemoClaw, see NVIDIA's documentation [https://docs.nvidia.com/nemoclaw/latest/index.html]._x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+OpenShell: a safe runtime for other agents_x000D_
+_x000D_
+NVIDIA's OpenShell [https://github.com/NVIDIA/OpenShell] is a private runtime for agents and assistants that brings the safety of_x000D_
+NemoClaw to other agents such as Claude Code, Codex, OpenCode and more._x000D_
+ _x000D_
+To get started with OpenShell, first download and install it [https://github.com/NVIDIA/OpenShell?tab=readme-ov-file#install]._x000D_
+ _x000D_
+Next, create a new sandbox with Ollama:_x000D_
+ _x000D_
+openshell sandbox create --from ollama_x000D_
+ _x000D_
+Finally, run Ollama to launch an agent:_x000D_
+ _x000D_
+ollama_x000D_
+ _x000D_
+ _x000D_
+If you have any feedback, reply directly to this email or join Ollama's Discord channel [https://discord.gg/ollama]._x000D_
+ _x000D_
+❤️ Ollama_x000D_
+ _x000D_
+You are receiving this email because you opted-in to receive updates from Ollama_x000D_
+Ollama, 744 High Street, Palo Alto, CA 94301_x000D_
+Unsubscribe [https://app.loops.so/unsubscribe/cmmywaughhpu30170gmjl1xqo/e46ef131f1546eb91f38c3a58cea945b413506cceae01ec46b0134c91cb943ef8f97d09dece0254cf31a21c30369ba975c1261af57daf79552a78c71]</t>
+  </si>
+  <si>
+    <t>"The Batch @ DeepLearning.AI" &lt;thebatch@deeplearning.ai&gt;
+I’ve been hearing from people at all levels of seniority about a feeling of job insecurity._x000D_
+_x000D_
+View in browser (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX785m_5PW8wM7ks6lZ3n8W8thYnb1Td80JW8jDcX23_b8MMN97rb4hRVw7SW51TLGG7syP_MW6Mfp3R83mP2-W8HPMc0772y5jW6L78lg3ZL1_jW6x-2xk2z5MwCW4d97Q06l_HkMW6YfY0X5mxZ4RN2wP6P6hnLSqW5gPSQk1byP8xW2dBBN46pkF1vW6vQlZ81rp78LW7VMxLz1mclYBW9887m95X-x-nW4d_Nwr2_xm64W8Pvfps1qqYWrW4zlrRN38hZ2lW43XGhg6R2BVPW4F4jS-3k2bsrW5K0CVv3R7YL5W91R7Fj4kBWdKW5ncvcQ5hkKf8W2bzM9d68jB4lW5bDxSR7h_L0xW5B39813JMdzwW3VXsVS8vDghsW2T65Rg3-t1VzW2nkP5B8zDb30W6zQ0lv22pYscW8kY7-Q7ZB_LJW1kNHwX964Vq5W5m_c2F55X2lyW7JP_WP5GCcNcW6dKGyB3BsRHgW7_DPkb136pm7W76pjZ42VCXqfW1bfNR055sPZkW4qJmZj76Q9MHW86F3-q4Vty_vW4fF-hr6xs9qGW5HYrhT466fvBN3Tfqvdc2WCRf8VbJ3b04 )_x000D_
+_x000D_
+The Batch top banner - March 20, 2026 (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX6g3prCCW6N1vHY6lZ3mZW2v7yzh47b9ZvN89KGD_W3skCW4_d5cM3ksKCPN2hmkjzGqtjZW4ybgbv4ysXQmW8FdHN27gzr30N8v1kfHwLCwhN93BHqlvj7MZW23wG-75rycn4W4W_RXT1nFfcfW8Wng3P2DgV11W5CgKzY7Gxkf6W5HtjcZ2clySjW5P00K82sCgj3W6CStLz2YHxvhW6-rN7-488jK5Vp2bmn1yhHN5W7vS5YQ1nmHJ8V8MXvC5Jy_dyW6NrmsY2NB7G_W1Sm9XP6z8jJXW4DjG9s7k04j6f4kBkTW04 )_x000D_
+_x000D_
+Subscribe (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX6g3l5QzW6N1vHY6lZ3p3W3pTx3j2Lw_5gW47M55G33gJ_mW7vJ7jF68PbhXW1s4Bck8ZqsSgN27zmhd9Xf54W6KRVFy3lPHmZW8pjhdJ1G1VLrW8PXnl747PsPCW63Sk5V453L1PV459-p8n6lpdW3qT8TW7Pbx71W5ns5sQ8dMMm0VyJVtB5p0KJ1W1wWV0T3rd42MW2Xv4Rf53h6WpW5pT_gH5tKTtwW5RYFQ-80HV8sW7KCS7P7c8J2NW5T-tQq1y3yHTW4hwp2X8jLKdQVL8Rl54H2XF0W6gds9v5sTpN7f9gS9Vv04 )   Submit a tip (mailto:thebatch@deeplearning.ai?subject=RE%3A%20Tips%20and%20News)_x000D_
+_x000D_
+Dear friends,_x000D_
+_x000D_
+I’ve been hearing from people at all levels of seniority about feelings of job insecurity. High-school students wonder if there will be a job for them, engineers worry about keeping up, C-level officers wonder if they’ll manage to help their businesses transform with AI, and many more. Amid the frenetic pace of AI advances and multiple sources of geopolitical uncertainty, the future feels less certain at this moment than at any other I recall. In moments like this, I think about what we can build to take advantage of the exciting possibilities ahead. But I also think about what is stable that I can count on, such as community and skills. To those of you who are navigating an uncertain environment, I hope this will bring some comfort._x000D_
+_x000D_
+The frenetic pace of AI advancement makes the future of jobs and of many businesses uncertain. On the business front, the venture investor Chamath Palihapitiya wrote a thoughtful article (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX6z3prCCW7lCdLW6lZ3pwW3Zq38x5x2fD4W9b4ZdW64KlTKW9fh3Jz6Qb3m3W4-TZ_-4flzFkW1ZQ--j67zVjkN4tyPS2Hq8qhN9cDm4DDHKsqW4gnHxm9k6ZKsV9jgJG1WmM3_W7GQtdt3f_NNcW82w0cq1J8wWWW5PbfP420bxBMW8lmtvF8ySxfnN2n4LlKGcLnzV1Yk336KPc7rW6H526P1XH3M7W1jdpvP27cF15W8LKGYK1MD2WhN86hS32brq3lW1-hgG-2Ldg37W7dL3Yd4W2bSrW2tNYm67FKr3VMZdRsYvPBMWW6wXdZd6Q0KkGf3gJ8nW04 ) on how share prices are affected as businesses face disruption from AI. tl;dr: The value of many companies is in the cash flows they are expected to generate in the long term, and if their cash flows might be impaired due to disruption by AI,  they become much less valuable._x000D_
+_x000D_
+Further, even though representatives from frontier AI labs often make confident-sounding predictions about the future, when I’ve spoken privately with some of them, they share that they really don’t know what will really happen in a few years. In software, some trends are clear: Highly agentic coding systems will continue to get better; the Product Management bottleneck, which is already acute, will get worse; many more people will be coding. But despite these trends, exactly what software engineering will look like and how software engineering teams will be organized in the future is only slowly coming into focus._x000D_
+_x000D_
+Separately from the pace of AI advancement, many flash points add risk to the future. The war in Iran, which is leading to tragic civilian deaths as well as the Strait of Hormuz blockade; uncertainty over the future of peace in Taiwan and the impact on semiconductor supplies; potential overinvestment in AI infrastructure; China’s control over rare-earth metals, and more. Because of our interconnected world, any of these can significantly impact people anywhere, thus enhancing risk for everyone._x000D_
+_x000D_
+Jeff Bezos famously said that knowing what’s not going to change in the next 10 years creates a stable foundation on which to build businesses. Many many things in the world will still be the same in 10 years as now. But for individuals who are worried about job security, I would put forward two things that I think will be stable in that timeframe: Community and skills._x000D_
+_x000D_
+First, 10 years from now, I know that my friends and family will still be there for me. Just as I know that no matter what, I will still be there for them. Relationships can be incredibly durable. During Covid, many communities bonded and supported each other. In moments of uncertainty, having communities — networks of relationships — helps everyone. That’s why opportunities to build relationships are so valuable and help us both get more done and protect ourselves against downside risks._x000D_
+_x000D_
+I find in-person gatherings, where we can make new friends and refresh existing relationships, especially helpful. If you would like to attend a high-quality AI event, please come to AI Dev (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX6g3prCCW6N1vHY6lZ3pQN3s1Zjq79B0_N3Q70jSH_2QYW1RKw_Y6cSS_3W2kJ1lx8YNLFyW90bFj03ZKSvrW4FmNdz3LJz9fW4xqqdn8rbmBzW6LvpJ83-4SttW19QLqc3p7rymW1FybzV1DQP2TVpBfRz8MjnDcW3mGtFh19ddgpW8hmM5S4jp-4hW2lhHt77hGqBhW6vb15W2RqH6BW69mxHq5ls8rCW5BBmPF1PWFf3W70dbxt5cJdSqW8KbDB66_NfK6W6CTZqX2306NTW5k_6gC92WkcwW5YbXZL7y0TytdhF_yg04 ) , which will be held on April 28-29 in San Francisco. I’ve really enjoyed meeting people there — in fact, AI Aspire, an advisory firm I co-lead, started from a meeting at a previous AI Dev! — and I’m confident that you will, too._x000D_
+_x000D_
+Finally, a particular business may or may not do well, but many skills will continue to be valuable. Your skills are something that you can always take with you, and no one can ever make you lose a skill you’ve earned. Exactly what skills are valuable will change, so it’s worth investing in a range of them to give yourself more options, and perhaps even learn some skills that might not be immediately applicable. Further, skills stack on top of each other (e.g., understanding prompting is important for using coding agents, and understanding AI building blocks is important for understanding how to architect certain applications). So building skills makes it easier to gain additional knowledge, and investing now in building a range of skills means that come what may, you can still accomplish a wide variety of valuable things._x000D_
+_x000D_
+I’m optimistic that many of the risks we’re seeing will work out well, and our collective AI future will be far brighter than it is today. You can count on me to be here to support you, and to support the AI community. As we navigate this fast-moving and uncertain world, let’s help each other out, build community, and keep helping each other gain valuable skills._x000D_
+_x000D_
+Keep building!_x000D_
+_x000D_
+Andrew_x000D_
+_x000D_
+A MESSAGE FROM DEEPLEARNING.AI (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX5-3prCCW69sMD-6lZ3m0W1JvznX6hHdX3N3DCFQvzgv05W1Fv8YG5p4mQkW4htkQk78vGxhV8q6K7803Z4ZW26wwy32HWlztW1B9HNx24HWC3VhJtW38H5CRgVcX3PK8QkPs1W7q_c5y18TFF1W497nWb3ggMjqW3L4tFg3FZyTvN544_fjfMkN7W5sRXNy2Bf_B_W7Wn3tx8_FY8PW88hwwV7pP9rJW2z2nqP8cmB27W4-FD7R4jJTXQW8k0kHk6QmxQ9V6f0Mr4-WmPgf8z9JZl04 )_x000D_
+_x000D_
+Promo banner for: "Agent Memory: Building Memory-Aware Agents" (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX783prCCW8wLKSR6lZ3pxW2zr1nd2RPr3mW1t-g5N3qrN7cW8B8hCt5vNMBhV1Cqf61RKFy7W6432PH500ph7W17wh625KpSySW2blN-72B8TjZV8zL946k4HZbW2pVgd54X4qzjW1G0L-x3K2bZ3W2VgmdT2zX-gyW3nDKwg2fxWSXW6VVpXd6XBGTvW2hHkmy7GCLKXW33RDLF1x8MKVW3dSC7T8J5NPJW3TKkS13qF8W1W6tnK5D46-N-BW74Sxrc1J3PKkW6FdS1x3lCdFmW7kW4XV7wc0KdW5ycGb15Tc6dqN93GHDy7CYDrW31Rgn118wnyGW3hmp152hpsMRW4Yfh0r3ZyYRKW5jkq1q5GggqlW7F2C616qfVCcf5q8HCW04 )_x000D_
+_x000D_
+In our latest course, made in collaboration with Oracle, you’ll build a complete agent memory system that lets an LLM store, retrieve, and refine knowledge across sessions, turning a stateless agent into one that learns and improves over time. Sign up here (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX783prCCW8wLKSR6lZ3pxW2zr1nd2RPr3mW1t-g5N3qrN7cW8B8hCt5vNMBhV1Cqf61RKFy7W6432PH500ph7W17wh625KpSySW2blN-72B8TjZV8zL946k4HZbW2pVgd54X4qzjW1G0L-x3K2bZ3W2VgmdT2zX-gyW3nDKwg2fxWSXW6VVpXd6XBGTvW2hHkmy7GCLKXW33RDLF1x8MKVW3dSC7T8J5NPJW3TKkS13qF8W1W6tnK5D46-N-BW74Sxrc1J3PKkW6FdS1x3lCdFmW7kW4XV7wc0KdW5ycGb15Tc6dqN93GHDy7CYDrW31Rgn118wnyGW3hmp152hpsMRW4Yfh0r3ZyYRKW5jkq1q5GggqlW7F2C616qfVCcf5q8HCW04 )_x000D_
+_x000D_
+News_x000D_
+_x000D_
+Drones Hit Persian Gulf Data Centers_x000D_
+_x000D_
+Iran hit at least three Amazon data centers in the Middle East, an indicator of AI’s critical role in the United States’ war against Iran and possibly the first time such facilities have been targeted during warfare._x000D_
+_x000D_
+What happened: Iranian drones damaged (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX6g5m_5PW6N1X8z6lZ3n_W2Z1YZY7QQLb7W8lZLGQ86z7VbVJvqfJ4vTXPcW5XqxXW61bd8KW86VDJg1WJnZ1VPGhKh7-C-mYW1V-3w663kB4rW2-nPnx3l96pHW4xYXp92Hz8lxW5rlghz7kp9WRN2d3LVDCGrqgW5QMwL93BpxVyF8MJ_xZ1Yw0W53Q01T6rNnvTW1RXzCP5PvK09W4mtbQY4njQ0fW8z-f8T16_8Y1W4GZ9Tt3vBdJVW1MN_6j6MVMmQW2_fsRc9h_qKWW8c2ng01KLj_nN8fX5_N8P7tSVVW5s_6mYPLNW5T1r094HpWbhN6ZxdVRWRDqyW3CdZwd51YNvdW6DBZmm2Fnh3XW3Wv_p-2s9YjzW7FxRDz1NVMRPW60dkFZ5JCjJZMPzpNCC3HGvW7KZDHp4jP4r9W4LTT4B3MGD70W2-ySX27C5yj8W4jSXCy4v-726W1X5Cbw4bSp6ZW2L0dHC6GPs-tW2KbGZ81StMsMf1S4zNl04 )  an Amazon Web Services (AWS) facility in Bahrain and two in the United Arab Emirates (UAE), disrupting online services including banking, payments, ride sharing, food delivery, and business software. The U.S. military uses AWS to run the unclassified version of Anthropic Claude and possibly other computing systems, but it didn’t disclose whether the attacks affected its operations._x000D_
+_x000D_
+Drone attacks: Early on March 1, drones struck two AWS data centers in the UAE, and the Bahrain data center suffered damage shortly afterward. Amazon said the Bahrain attack was “a drone strike in close proximity to one of our facilities,” while Iran said it had targeted the facility “to identify the role of these centers in supporting the enemy’s military and intelligence activities,” according to (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX5-3prCCW69sMD-6lZ3lfW67VFZ_8k-xj-W2tmPB079NT93W1LJrJ44VT_r8W3_yX3J4StcblW746y-r7ZB4pSW8vLpV25NxFLLW5qJ9jq8L-1GmW76n3Mk7QzhLJW6v1c0q8gMXL8V8-Fn38gVDxcVsQdwH5X4_3KW3g02Mx6RyVrqW6qMtKm3W6-_SW66-Fl56ttfDXW3j1d2r16Gr8tW6W8R_C3m6FVFW2GDy267Sn1pcW3XrPV06DYKwpW3mfBbl3FbJZYW3_HhzD1J33-ff68JbZz04 ) to Iran’s state-controlled Fars News Agency via the messaging service Telegram._x000D_
+_x000D_
+- The data centers suffered structural damage, power disruptions, and water damage caused by firefighters, which resulted in service outages and higher-than-normal error rates. As of March 3, Amazon recommended (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX6g3prCCW6N1vHY6lZ3mrW2gH68v5RNBT5W4SFK6q515m-zW2ypmMG7ZXJ2tW2p_hfT5pm1thN201xykclKBGW74NvBd7d4G5yW1Xvtlj7JDjcDW7tNhkB44S4qFW78Ptpn7f3k8rW3tyRj-8hhXjMMR0ZCHLB803V9QFtz2hFBjKW4By-sR3_2KMqW86_sTr5k7Fv9W1JMbyg81Gm9FW6fh5C27kk_vyW3jc9Nq1z9yw1N6vhhcWJYhfbW7G5Hq67JVlHLN7MffjBpgl32N4vGN0Tbn5njW3PJJ3z73Fz_ff3Jw42d04 ) that its cloud-computing customers back up data and move workloads from AWS Middle East Region to the U.S., Europe, or Asia Pacific._x000D_
+- The attacks put at risk trillions of dollars of investments to build AI hubs in the Persian Gulf region, The New York Times reported (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX783prCCW8wLKSR6lZ3mZN1QK1PsXyVM6N3Wh9-Jw5p0qVw9Dhp7DLFSGW8wq00l5ZGtMhW2G07vh5s9y0_W4xKlgj2JR5zmW5L16tY8J1pN8W99-fPx357X0cVfDzVx8pSGTkW5w2ghH8fdtPXW89znxj5m6BtXW1ngtSm8YLNfMW6zRGX23B3S0xW2-ZKMk7VsfkYN2VmLZZRV_HPW76FHS98X3y00W1qd1dm7TYt4GW8ndvRc7MbjGMW1t1XMp5DXyfgW9jlgX03XhwF5N80hf9wq72PMW7X45026CpCDGW6kzFlq83QCLdW63PqXq31H0qBW2X8bqZ8jXjD9N91wKByc5Y33W4dfr-s7sT5dWW3s-kcT5dJMdZf7j7SmF04 ) . Amazon, Google, OpenAI, Microsoft, and xAI each have announced multibillion-dollar commitments in the region._x000D_
+- Member nations of the Gulf Cooperation Council, an economic union and military alliance that includes Bahrain, Kuwait, Oman, Qatar, Saudi Arabia, and the United Arab Emirates, host 2.0 gigawatts of data center capacity, with an additional 0.4 gigawatts planned, Business Insider reported (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX7s3prCCW95jsWP6lZ3lcW71DXp45-VW2hW75ZpMy7vscWDW7Dcjnk2YdyWgW270spC2cx_PMW8W0NcP7qtJTwW7YRP8J8-n_5YN7c01-S6Rs0rW3Ffyw288-Z25W8kXVZp5yxb13W4KgVNT3FV-5sW6QCfq87NVQGMW4BWCwD4mdsfTW4HdXQM6CxVS4W61WnGF5KjKmYW3sWrYC1QKh8DVjg4w17Brd2FW8nw3gQ6Q9HJcW19t5M-3BKKmdW18Hw9w5hTtCsW1WM6j36RtsJ4W1gQRY04fW1ZFW1Syc_21FDWJGVTtvvb1hkc_7W6PBr254_rzMGW9b4M6x2_m_d6W534w8p6Py1c1N7XxL_8t0bwMW9ght065jQBY3W84b6Ts3KHtDzN8Kk8YMFpTwxf8VXtHx04 ) ._x000D_
+_x000D_
+Behind the news: The risk to data centers mirrors a rise in AI’s role in warfare. Despite the U.S. military’s recent decision to ban (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX5n5m_5PW50kH_H6lZ3ptW8Q7bq56qMyZGW4BQjNt6_-2d9W2tpWD95pD2jFW39sgk03BxtVsW4VZLfQ43s11cN5zRX_Ctj145N4-5VQgrj7f-S9vK25lPyTW4WcGVb6chQk5W6Ttbj26dKw31VMC4hx2K-x0hW8HMl-350dcFRW18w1SZ8jr9KPW1hm1FB4xh6K9W24Dlq-2rrN_DN5kT5GhHPldbW7Xp19F1K5LSCN6CGR_9_Hzx4W6JQC2B709zFCF4VVRr4rwWrW285YYz7wqkk6W4HppSs5_ZbnjW12Vw_94pRr5NW1NJ0zf5z2TQXW7YbpPK2kscYmW25s2LN5BTbZ5W7-YK3D8gwNpmW505nz268G-JLN2JSJ6cMkkwfW19RtqQ3L3ykBW2cgw8Z7XBG29N8G53v_g-Hstf3MSjlx04 ) defense uses of Anthropic’s Claude large language model, U.S. forces routinely use Claude and other systems for a variety of purposes in Iran and elsewhere. For its part, Iran uses weaponized drones that have some degree of autonomy._x000D_
+_x000D_
+- Claude was part of a system that helped select more than 1,000 targets during the initial 24 hours of the U.S.-Israel war on Iran, enabling U.S. forces to vastly accelerate the pace of strikes, The Washington Post reported (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX783prCCW8wLKSR6lZ3l9W8_RB2m2Srdn1W40LCX-1Z9LYnW3VyWc54Q9z4MW57dV-g20gWsYW4ZSgvq16ZFRXW7QbFSx3Bb3HkN16gM3wZdMhfW1b4DFN31G0pcW2JQZ_D8zRBZ7W8pfZXZ64WJRPW1tX1ts84l7S4W4S2ZNj2N5RKQW7L1TSN7LNzJ3W56xvkN4060KxN6464GbYsrmXW6tBqLx1sng2cW6jk_qx6WGk_kN4_8tx7kmgTzVQFJWg1-Nl0RW1Hs_bs59MZhFN3fQdTrYXDbbMDRsvbNr89lW65WSq94WG3kPW8Xz8Dg1pZL7VN56vzyM14zpdW5b5hzM8jxSGzW4jpm1m6N2Sj3VqTK3778YyZRf6Jj-7K04 ) . Claude is integrated with Maven Smart System (MSS), a system for targeting and logistics built by Palantir. To avoid errors, human analysts check the system’s output in life-and-death situations. In exercises, MSS reduced the targeting process from 12 hours to less than 1 minute and achieved results with a staff of 20 that previously required 2,000, Army Times reported (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX5n5m_5PW50kH_H6lZ3mrW4bD16c6BnNrCV4jgHT67ZrNZW7-BDQw38BXccN93c-WZwvSQzW7v8gC02MbPF3W5zh0g63d0DfnW6ksycy5CFQKMW442TjZ2y7TYrW7wVvpp49hpD3W8k2xx85h_xD_VfHqTZ4d1sQwW8DWTPq2ZXs60W2c7qWB7t9Pg-W54ch1W1G_vSmF8c0_Mcr3njW2_jfh-7zxxdkW8Vb6LJ7ZyCtvW5pcShV1lzjzlN2QZV6B3qzj8W3nCfws7d3PZ9Mc9tBB9cBDZW90LPd359MGlsN194qGP5JhMBW7PX8Dw9cWTXPN17Q02lhRj_cN2td5P_VLzmPW1mYTKx429BvTW1Pw8pX5fV88DVG-ZQN59ZLWqW6_Djhh6V556jW3ScQ3V3hpQL-N3h_P8qrT36Jf8GlhWH04 ) . Claude/MSS played a role in the January operation that captured Venezuelan president Nicolás Maduro, but the actions in Iran are its first use in “major war operations.”_x000D_
+- The use of inexpensive drones has become a defining feature of the recent U.S.-Iran war. Iran responded (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX6g5m_5PW6N1X8z6lZ3pMW8Zn7mC8Xg4GlN86zXVj8HpfjW5_5y1t3CcQc-W4STGLh8Hcw61W4YXS_M7VDqqfW1c-GFQ7ngY_BW6vvP5s4PgRxBW3rx54y5BLGtbW7z0wyS5GdYYLW4T4ccn7mLwk6N69H3YPB7D3nVk2jPl6TxBN0W6FX7f-7DP98qN4RHsVJ2wGTPW7SxNXB5_PdCgW8sbs_F43kbbvW7JmDGf4vhc0_W30BKb28X9phWN6tpkfYH-HkvVCt3B03GkCVgW7zdrhp5PzYMqW6D8Myh3crK2WW3n3nYg92j3cjW6y1v1j6Dqt3_W4QsPWC5XB3XvN160vF_P3JtCN2Nd5XLy_t1PW1TMVCL4s0l51N4_Z4hgfYY0wW4-fhQz2jRlgkVsSgWd7Zfv6KW5n5zQ-30wWFTW6wtjLN580wjNN2bS4HLJkxGjW1NM1MW8M3MpWN85kbgyT5tckW9k06Qk8BN_1qN5Fs-mS3lltNds8lT404 ) to the initial U.S. bombing campaign with large waves of attack drones — many of them low-cost designs that navigate autonomously and attack on command — aimed at regional infrastructure, military sites, and U.S. assets. The U.S., in turn, unleashed its own one-way attack drones, including the LUCAS system modeled on Iran’s Shahed-136. This style of warfare draws heavily on Ukraine’s innovations developed during the Russia-Ukraine war, where swarms of drones — often coordinated with software and AI — have destroyed tanks, artillery, and logistics targets._x000D_
+_x000D_
+Yes, but: As AI raises the pace of military decision-making, it also raises the risk of deadly mistakes. For example, during the initial wave of air strikes on Iran, a bomb destroyed a school, killing more than 170 people, mostly children. In a subsequent investigation, preliminary findings indicate (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX7s3prCCW95jsWP6lZ3pcW5Sz26V4yBByQW7tRWxq7bZjrVW5svhW11dQb7YW8CRxgV4TNqsvW5Nr0Nc94z-7yW4ZFrgR9dBYbQW4trXQg9hVlVxW7rf7ky3wl__tW1Q-d9475Kft-W24M29s6cxsFJW4xbQNz8wQts4W1rXHK110Wj80V_S46H6d9GbjW8hht925pc9L_W6qGp0l4TXK0gN1VnWNmLkPwdN1tJhxR9ZcgsW6_m2Gr30YMMdW4_hzbs6b4WWlW7LFzRb3TG8VqW5T1R1150fdW4V-mFnd5RpKDQW102L7t2m-QslW6C5Zmz3q6kvdW1dB0lm1HSPDCW3Gg7Vp4rMLlpVbZ8T21hByrbW2H4j646ZB8byW4ZmF5y7SDQy2W1tbvp67VbBDNdg6WCj04 ) that U.S. forces likely dropped the bomb. Out-of-date target data may have played a role in targeting the building, since the school was part of a nearby naval base roughly 15 years ago._x000D_
+_x000D_
+Why it matters: The sharp rise of AI-enabled warfare signals a shift in the pace of combat from human to machine speed. AI makes it practical to plan missions by running vast numbers of simulations to identify actions most likely to lead to success. It accelerates battlefield decisions and actions while potentially reducing the so-called fog of war that can obscure realities on the battlefield. Missions become viable that previously were constrained by lack of human attention to analyze the flood of battlefield communications, imagery, and other information. The acceleration could shorten some phases of conflict, yet it adds pressure to make snap decisions that could have catastrophic consequences._x000D_
+_x000D_
+We’re thinking: AI-generated recommendations don’t remove the need to verify intelligence, question assumptions, and weigh the moral and strategic consequences of using force._x000D_
+_x000D_
+Qwen3.5 Outperforms Bigger Models, Leads Vision Benchmarks_x000D_
+_x000D_
+The Qwen3.5 family of open-weights vision-language models includes impressive larger models as well as a smaller one that outperforms an OpenAI open-weights model 10 times its size._x000D_
+_x000D_
+What’s new: Alibaba released the Qwen3.5 (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX6g3prCCW6N1vHY6lZ3pvVRmvrF2lxClvW6kGGg_54XW0FVKzjm26LJ9NFW96wRsL8CYBF2V_1gP98VBHpKW7637JS2RhJd7W2b1CR91mW39sN68SG9HbJFRvW8w9KkB7-cLTPW6PD8YF9bDlmgW990TdX3PyGz7W3wj2xP5QWRDrW4SZ01D3pf5cXW3FKpYw59L2zsW60dXjN4pB8RJW4KXskY4pq09DW3ccyJZ8P-gS3W1S8tRT2xfP76W9d-MRc302c7ZW2Rkzjg3Rp15qW7x1ZnG1J-7SYW790gJ_1S__6qf1qr4pv04 ) family of eight open weights vision-language models._x000D_
+_x000D_
+-_x000D_
+_x000D_
+The largest are Qwen3.5-397B-A17B (397 billion parameters, 17 billion active per token), which offers open weights, and Qwen3.5-Plus, a hosted version of Qwen3.5-397B-A17B that supports agentic applications by providing a larger input context and built-in tools that it can select autonomously._x000D_
+_x000D_
+-_x000D_
+_x000D_
+Four medium-size models include the open-weights Qwen3.5-122B-A10B, Qwen3.5-35B-A3B, and Qwen3.5-27B, plus Qwen3.5-Flash, a hosted version of Qwen3.5-53B-A3B that’s outfitted for agentic applications._x000D_
+_x000D_
+-_x000D_
+_x000D_
+Among the smaller Qwen3.5 members of the family — Qwen3.5-9B, Qwen3.5-4B, Qwen3.5-2B, and Qwen3.5-0.8B — the 9 and 4 billion-parameter variations rival the performance of much larger models._x000D_
+_x000D_
+Qwen 3.5 specs: The new models offer tool use, web search, and chain-of-thought reasoning in more than 200 natural languages._x000D_
+_x000D_
+- Input/output: Text, image, video in (open-weights models 254,000 tokens extensible to 1 million tokens, hosted models up to 1 million tokens by default), text out (up to 64,000 tokens)_x000D_
+- Architecture: Mixture-of-experts or dense transformer with mixed attention and Gated DeltaNet layers, unspecified vision encoder_x000D_
+- Performance: Excellent vision performance overall; Qwen3.5-9B (9 billion parameters) outperforms gpt-oss-120B (120 billion parameters) on many language tasks_x000D_
+- Availability: Open weights freely available (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX6z3prCCW7lCdLW6lZ3nCW5Cm0lW6LfH2gW74pJKR3TQhScW5Sfhv96YxW6WN8b0D6RxtD96W1q1c2w4L_sb5W83hTWT5CX_krW33DKqs4zYKtnW7-wS0L3Zrgx0W3hwjc14lHpm6W5fPNgv7RcWqcN1Zq4DckmsV2W7x4r5v38gpTmW8VRF1d4twLP9W6hlmYr2yC2xHW1wgG4G4VnRGpW7y-bDs6fKFTdW5r5trs9jL_VBN8drzVnFvJ6VW6F9_Lh2dxpXnW6jrNvK3jDszMW3GXyGy4pSZfxN2D3NRJWg02yW6ySPgR6v41wZW83zqQK1fwYCNf7kqy4n04 ) under Apache 2.0 license; API for hosted open-weights models via Alibaba Cloud Model Studio $0.20-$0.60/$2-$3.6 per 1 million input/output tokens (prices vary according to the specific model); API for Qwen3.5-Plus $0.4/$0.04/$2.4; API for Qwen3.5-Flash $0.1/$0.01/$0.4 per 1 million input/cached/output tokens_x000D_
+- Undisclosed: Vision encoder, training data and methods_x000D_
+_x000D_
+How it works: Alibaba shared little information about how it built the Qwen3.5 family._x000D_
+_x000D_
+- Qwen3.5 is built on the Qwen3-Next architecture (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX5-5m_5PW69t95C6lZ3nhVH8Zgn2pMsC7W4qnZwq2JVf9bW7tlJlX33NckhW90j0cq15rvXcW8NJ3y65CLKl9N8PVqCDBVHnfW8mpfyX8-M9f1W7ShwSb2H5-qRW5GJZzx6-pY4cVYK4V51WxkRCW1Qk9z47L2vWsW7V5Gk776t3pvN171XFCS6Qf3W2CRl3D6jWmnlW5zPgv27tydz_W7L5HdR6WYPZxW4GhfDR6QYhbwW1MwMJW3RbQwrW8NyWWN2yF4MgN7pMPJ8HPg-MW3QCjqP7GqpfjW3NdtYz4b_GxSW7--x_v93_jyVW9c3_R3419HkNW3ZZ27N67HStzW3Y5plr3Tt50VW7pjXM07l229vN5_p-4BbXXRVW3JVRgB4Mhd3jW1h2lPy3Dkdf5W8MHffJ69zvcmW1fn_z57pMtp_W2CBVt690D61GW4RSCdM4mVBwBW62BsNp6s4m8XW9bXQDL5QqRMyf5DbtFW04 ) , a variation on the Qwen3-30B-A3B architecture and training method that’s modified to increase training efficiency and stability._x000D_
+- Qwen3.5 was trained on a “significantly larger scale of visual-text tokens” than Qwen3._x000D_
+_x000D_
+Results: Tested by Alibaba, all Qwen3.5 models excelled at vision tasks, outperforming much larger models, and some turned in competitive results in language tasks as well. Qwen3.5-9B and Qwen3.5-4B showed the most impressive performance overall, shining in both vision and language tasks, even compared to much larger models. The two smallest variations lack comparative metrics._x000D_
+_x000D_
+- On 28 of 44 vision benchmarks, Qwen3.5-397B-A17B outperformed GPT-5.2, Claude 4.5 Opus, and Gemini-3 Pro, whose parameter counts are undisclosed but almost certainly much larger. In a variety of language tasks, Qwen3.5-397B-A17B outperformed either GPT-5.2, Claude 4.5 Opus, or Gemini-3 Pro, but generally it did not outperform all three._x000D_
+- On most language and vision benchmarks tested, Qwen3.5-122B-A10B and Qwen3.5-27B exceeded GPT-5-mini (parameter count undisclosed). Generally, Qwen3.5-122B-A10B, a mixture-of-experts architecture that activates 10 billion parameters per token, outperformed Qwen3.5-27B, a dense architecture of 27 billion parameters. Qwen3.5-35B-A3B generally underperformed the smaller Qwen3.5-27B and Qwen3.5-122B-A10B, but nonetheless it outperformed GPT-5-mini in 58 of 74 benchmarks tested._x000D_
+- Qwen3.5-9B outdistanced OpenAI’s language model gpt-oss-120b — more than 10 times bigger — on most of the language benchmarks tested except reasoning and coding tasks. Similarly, Qwen3.5-4B outperformed OpenAI’s language model gpt-oss-20b on most language benchmarks tested except reasoning and coding tasks. On most of the vision benchmarks tested, both Qwen3.5-9B and Qwen3.5-4B outperformed the vision-language models GPT-5-nano and Gemini-2.5-Flash-Lite._x000D_
+_x000D_
+Behind the news: Shortly after rolling out the Qwen3 family, Lin Junyang, the team’s technical lead and a key architect of the models, abruptly resigned with a post (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX6z3prCCW7lCdLW6lZ3nnW3mBp0H4Nbky9VWsgV-69kGxQW4-0my78bgMPpN8sv4s-MPPp-W70HZ7k8X4HPkW8Qrkwy40ZH2JW9kVGjY5gSTp8W6lvmJP7F7CHBN540VkW3jCfVW2X3LVw5fkM2YW2rr28D79-4LbW3Swrmp8V72fRW7GGRmh4Cy9gRW3cjVwt1kthwrW843XFm1zgnG5W7WrDPM6JrpJSW2WmkSP51YMH_W6R9_H58Tx4S_N45mts2365KYW7Jys2X7_x8GBN1319c6wq3f2VpjYy890t5dQW28Cd7S8Smm9VW6Zzht_7mbkqkf7mKbqn04 ) on the X social network that read, “Bye my beloved qwen.” The Chinese tech-news outlet 36kr.com subsequently reported (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX6g3prCCW6N1vHY6lZ3ksW7zVLTV8-4tvtW8DZ2Z_4yJ6k6W44V-6K4qDlDxW3Lg3bb2d8Y3hW65X9VK7d-JrwW6W1Dpn4_rGXQW2SghMk20RyZ2W5Py0v27QF_bGW22QPbx8vWbsnN4HPgSKK2XM0W1wzMNk3z3MV5N58-MKvj1HhrW5QX2MV1t3FsNW8TdMV15Q9gJNVrpBH36kyCP_W7s0VVl8Z5t6vW3GSLXy1jtG7FW7KM2MS5MwTk2W3w_Bc_71qM1_W2w3xhQ3h3ZQ9W61BQyJ3VzFjyVtjqTD5x8s-wf1Wx_R404 ) that four other members of the team resigned in his wake. In a January public appearance, Lin had said, “We are stretched thin — just meeting delivery demands consumes most of our resources,” Bloomberg reported (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX7s3prCCW95jsWP6lZ3lBN2pWmh_Sf8bdMDQkv4sJX72VDmqj95lnqS2T6rbm1j5XDLW77MwnB52zzLYW5mPyMZ6jN3C_W3WMt9-4dlXgCN5-jrN9J-NlzW8z2mq-3s4NQ0W3_BzlP35jX14W5xQKhh9ff5dHM3RD6mhjSrVW5svCTY7Q-8x_W7yG3WK3331VgW55bQRD87frYfW5Llkhm7qfn6FW93Xq4v6ll6LVN8kncwsy1NffMGdx4WmztnHMPBXDc88139W8rbYZq838vdhW98gv6b20Qcg5N7-cWfClbDF0W1h6G5G7txr9lN85BgfTlLnNyN8vqYDgzl4CTW7qQzh37rddllN2sMk2W6W37-W5B_YhR8QCV3VN1PjvHM3-FFjf1H9NGF04 ) . Alibaba responded by putting the Qwen project under tighter supervision by senior leadership and promising to invest further in AI development._x000D_
+_x000D_
+Why it matters: All Qwen3.5 models deliver stellar vision performance for their sizes, but the smaller models — especially Qwen3.5-9B — are small enough to run on consumer laptops while delivering performance that previously required an 80 gigabyte GPU like the Nvidia H100._x000D_
+_x000D_
+We’re thinking: Vision-language models with reasoning capability that are small enough to run locally means reduced cost, better privacy, and new vistas for vision-language applications._x000D_
+_x000D_
+A snake crosses a busy tech startup walkway; people with scooters react in surprise. (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX5H9bqx4W5BXf_W6lZ3kvW92P3jY517VBmW1HMMKn6t3f5DN5Hjyz4f7WbLW5pBQMr41p9nSW3k6t2M8bRDBWW4p6xly20fyFkW3pR9qC6NT1-pW3PjMtK6MJwyyW14dwNp7t_4xDW5BxmvQ9cfcnLW3P2hRn5520T5W370bnd7j0bhCVb7l0d7vHVzfW3G3DB085BZWWVK7NSr1ndXThN2GDsv3wf6nNW1-V0cK7-9ZVCVksXbg72P7R9W3FYylk7PlrFsW6PQDbh7hFLlKW6HV5mC7bm1C7W1F1Rx95r346SV6Y0Dg1GTgQQW3npDP41685lVW6xSJsn8dmG41W3bGnRw7p_DrNW7t_G7q1SbqLNW1RSJjn3DdGQqW6y_-zW8d6m4pW4VgGl955gQbXW3tP9VX3MPLfJMSx3yHzr-hnW6mbT2q850tg9W2lkgWy2nwgmYW5NxWlJ1tnB20W1QZdJP5fjbT2Mbc1V5bqfgNW8bVHt17YFMbcW8CPmjg5Gy-FgW7yWc3N40_dL5W3b5DBt53dvKCV2PYVT2qCrr4VvBpmr4dNF8rW28NlTB2tJ_5YW7kPfNT7t1Q91W9cMxxh3TYJhKN1NVyPpM9-7ZVZr85y5CJ55wW7Wwt4P5BWMZlW59Lm0t6b3-84W4lq-Lh6YGjh1W3k5H552KPQMrW6NK9Wk1f4--4W6RHMtp8Y5CJ1W3yrX8l1QKCFlW77DGq_2bJJYrVPZKq-5c3bjQW1sFRwx2CFfc7N4KyvCRqz_ZBW2p3szM4p0szvW45b4KH8JFzgYW7q6p7V65TLK-N1_fX6sYYlpRW5Tyn9N4r0GBrW59T7Pg8DhyrcW6y3BLf870BGXf2G6SPj04 )_x000D_
+_x000D_
+Learn More About AI With Data Points!_x000D_
+_x000D_
+AI is moving faster than ever. Data Points helps you make sense of it just as fast. Data Points arrives in your inbox twice a week with six brief news stories. This week, we covered Perplexity’s expansion into autonomous AI agents across desktop and enterprise tools and Nvidia’s secure infrastructure for deploying AI agents in production. Subscribe today (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX5H9bqx4W5BXf_W6lZ3kvW92P3jY517VBmW1HMMKn6t3f5DN5Hjyz4f7WbLW5pBQMr41p9nSW3k6t2M8bRDBWW4p6xly20fyFkW3pR9qC6NT1-pW3PjMtK6MJwyyW14dwNp7t_4xDW5BxmvQ9cfcnLW3P2hRn5520T5W370bnd7j0bhCVb7l0d7vHVzfW3G3DB085BZWWVK7NSr1ndXThN2GDsv3wf6nNW1-V0cK7-9ZVCVksXbg72P7R9W3FYylk7PlrFsW6PQDbh7hFLlKW6HV5mC7bm1C7W1F1Rx95r346SV6Y0Dg1GTgQQW3npDP41685lVW6xSJsn8dmG41W3bGnRw7p_DrNW7t_G7q1SbqLNW1RSJjn3DdGQqW6y_-zW8d6m4pW4VgGl955gQbXW3tP9VX3MPLfJMSx3yHzr-hnW6mbT2q850tg9W2lkgWy2nwgmYW5NxWlJ1tnB20W1QZdJP5fjbT2Mbc1V5bqfgNW8bVHt17YFMbcW8CPmjg5Gy-FgW7yWc3N40_dL5W3b5DBt53dvKCV2PYVT2qCrr4VvBpmr4dNF8rW28NlTB2tJ_5YW7kPfNT7t1Q91W9cMxxh3TYJhKN1NVyPpM9-7ZVZr85y5CJ55wW7Wwt4P5BWMZlW59Lm0t6b3-84W4lq-Lh6YGjh1W3k5H552KPQMrW6NK9Wk1f4--4W6RHMtp8Y5CJ1W3yrX8l1QKCFlW77DGq_2bJJYrVPZKq-5c3bjQW1sFRwx2CFfc7N4KyvCRqz_ZBW2p3szM4p0szvW45b4KH8JFzgYW7q6p7V65TLK-N1_fX6sYYlpRW5Tyn9N4r0GBrW59T7Pg8DhyrcW6y3BLf870BGXf2G6SPj04 ) !_x000D_
+_x000D_
+DeepSeek Snubs Nvidia for Huawei_x000D_
+_x000D_
+DeepSeek, the Chinese developer of outstanding open-weights models, has withheld an upcoming update of its flagship model from U.S. chip makers, a move that intensifies the AI rivalry between the U.S. and China._x000D_
+_x000D_
+What’s new: DeepSeek has not yet given Nvidia and AMD an opportunity to make sure its upcoming DeepSeek-V4, which is in the final stages of development, will run smoothly on their chips — a departure from the typical practice prior to major model updates. However, it did share a prerelease version of the model with Huawei, giving the Chinese chip maker several weeks to optimize the software for its hardware, Reuters reported (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX5n5m_5PW50kH_H6lZ3nqW4j-mw66TgP08W8k4LkL2DBWrDW2pFlLT1ZjZJnW7yh2nd76Bdt8W2YkrcL5RqgfXW48GRxy7S73wkW2_YlzD4bDxn4W4q178d35SByjW1SkNQ88kwrqPW1PN9N35lWWBjW9b64tS5Bt9DXW8nBWfc1J1WXxW4dqty43S76jHW977DFM4TqRCWW2-YlYc6nx1vBW50MJ_r7-Dc_pW6DqT3z2LRDX5W6d_P6M3fzQYLW88vC7s8Gdf-DW8_GvyH2KrG2rV8dtw73NSKpHW39Jnp3825yc_W7W622m1tkXS7VY5hT660FrSpW7bJc1b8lhCmrW3VDww71Kjy0TVyNk7190xGxRW6F1bNx7ct95NW6Yn-d923J5Q8W4MHf881xck1MM4rgK2F4HhQW3spYVN1D6wRyf4BPFX204 ) . It did not report DeepSeek’s reasoning for the decision._x000D_
+_x000D_
+How it works: Chip makers typically examine new models ahead of their release to make sure inference runs efficiently on their hardware. In the past, DeepSeek has worked closely with Nvidia to train its models._x000D_
+_x000D_
+- An unnamed senior Trump administration official said DeepSeek-V4 was trained in China using Nvidia’s most advanced chips despite U.S. export controls on such products, Reuters reported (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX5H5m_5PW5BWr2F6lZ3nzW7P3_NZ7wcDwnW43VzcQ56GkHPW1SBSGR1yMHwYW11Xf8b7ZKy3wW7wj1118TrCrkW2vRXgs53JlX1W7wlTC81SkLQbW6TDs-v6WRpBwW4sG6_r37mYShVZZ0Cb79TCYnW2LDJmT84K2l5W5xrsww1T75V2N8KFVMXqPtwgW6BrgNs4HNnPKW7NwZss56fCClV5JB0-56Y_hJW7djBYn1rJ2jJN5dSHxvPPQn4W8pmCXj5vvZWPW8Xc6G94dtpdmW8M7ks47JkT2TW943_7N7PBDPJVY34561pRP0NW5Xhg8n64q0GGW1z_CxJ5hwlJ3N6SHqk6vC8cdW6GZTmv645d-_W3v10R255sQ4bW1009cz7PG9QpN8KKMPKQKY0WW5GDtrb6xvc0kMYZct5Br1clW61zzZr6gJhhSVw-LxF7B9Xzvf5V3ngH04 ) , although it was not able to learn how the official obtained this information._x000D_
+- Nvidia supplied extensive technical assistance to DeepSeek when it trained DeepSeek-V3, achieving “major training efficiency gains,” the chairman of the U.S. House of Representatives Select Committee on China said (https://info.deeplearning.ai/e3t/Ctc/LX+113/cJhC404/VWk4q_4xDjYyW60VRtK1DSyKkW2ZRfP15LV2hnN8GDX5n5m_5PW50kH_H6lZ3p3V2M4vq11cxn5W4-Cnxm8_9h3HW26bx2s7342FQW227wwL3H4FRmW35Nvrd5NW4JZW51q</t>
+  </si>
+  <si>
+    <t>"Firas via Messenger" &lt;messages@facebookmail.com&gt;
+Hi Yessine,_x000D_
+_x000D_
+[https://facebook.com/email/appredirect/?rid=100004844588432&amp;fallback_uri=https%3A%2F%2Fwww.facebook.com%2Ffiras.hadjtaieb1998&amp;native_uri=fb%3A%2F%2Fprofile%2F100086414921033&amp;email_type=email] _x000D_
+_x000D_
+View message[https://www.facebook.com/messenger/email/?recipient_fbid=100004844588432&amp;sender_fbid=100086414921033&amp;thread_fbid=7876397999072048&amp;is_group_thread=0&amp;source=msg&amp;notif_id=1774040367158696&amp;cta_type=view_message_body&amp;is_fbm_redirect=0&amp;is_e2ee_thread=1] _x000D_
+_x000D_
+Go to profile[https://facebook.com/email/appredirect/?rid=100004844588432&amp;fallback_uri=https%3A%2F%2Fwww.facebook.com%2Ffiras.hadjtaieb1998&amp;native_uri=fb%3A%2F%2Fprofile%2F100086414921033&amp;email_type=email] _x000D_
+_x000D_
+Thanks,_x000D_
+The Facebook team_x000D_
+_x000D_
+_x000D_
+_x000D_
+========================================_x000D_
+This message was sent to yessineht@gmail.com. If you don't want to receive these emails from Meta in the future, please follow the link below to unsubscribe._x000D_
+https://www.facebook.com/o.php?k=AS1DaNPBne0njyqJZX0&amp;u=100004844588432&amp;mid=64d7aac50d2d6G5af4313ccd90G64d7af5e6d5a8G8431&amp;ee=Af9JGtduP3SgVb0YWb_Jjb4bBQ-0x4mXLagxUgcdNlPyLmE2vjERLWVBtB7dHjadL6qBNd30tczfehz8XQ_x000D_
+Meta Platforms, Inc., Attention: Community Support, 1 Meta Way, Menlo Park, CA 94025</t>
+  </si>
+  <si>
+    <t>Epic Games &lt;store@email.epicgames.com&gt;
+It looks like your email client might not support HTML formatted email._x000D_
+_x000D_
+Try opening this email in another email client._x000D_
+_x000D_
+Or, open the following link to view this email in a browser:_x000D_
+https://e.email.epicgames.com/click?EeWVzc2luZWh0QGdtYWlsLmNvbQ/CeyJtaWQiOiIxNzc0MDQwNzc5MTQwNDQwOGE0ZTliOTcxIiwiY3QiOiJlcGljLWdhbWVzLXN0b3JlLXByb2QtOWUwNDZhY2JiMzExOTQ3Y2JlOTA5ZWQ5ZDlmOTg4ZmYtMSIsInJkIjoiZ21haWwuY29tIn0/UaHR0cHM6Ly92aWV3LmVtYWlsLmVwaWNnYW1lcy5jb20vbWVzc2FnZXMvMTc3NDA0MDc3OTE0MDQ0MDhhNGU5Yjk3MS9yYXc/SWkhfZXBpY19OTlRBTjAzMjAyMDI2YzIwMDQ2Nzg/LZW4x/gab3CJw/JMDMyMDIwMjZDMjAwNDY3OA/sel4edc6159_x000D_
+_x000D_
+-------------------------------------------------------------------------------_x000D_
+_x000D_
+We respect your privacy, if this e-mail has been sent to you by error or you no longer wish to receive email, open the following link in a browser to unsubscribe:_x000D_
+https://e.email.epicgames.com/click?EeWVzc2luZWh0QGdtYWlsLmNvbQ/CeyJtaWQiOiIxNzc0MDQwNzc5MTQwNDQwOGE0ZTliOTcxIiwiY3QiOiJlcGljLWdhbWVzLXN0b3JlLXByb2QtOWUwNDZhY2JiMzExOTQ3Y2JlOTA5ZWQ5ZDlmOTg4ZmYtMSIsInJkIjoiZ21haWwuY29tIn0/UaHR0cHM6Ly9wcmVmZXJlbmNlcy5lbWFpbC5lcGljZ2FtZXMuY29tL2VwaWNTdG9yZV91bnN1YnNjcmliZQ/SWkhfZXBpY19OTlRBTjAzMjAyMDI2YzIwMDQ2Nzg/LZW4x/qP2VuY2J1PU1qWmlNVGMwTURkalpUSmxORGt6T0dFNE1qRmtObUV3T0RZMVpUY3dZVFk9JmVuY2U9ZVdWemMybHVaV2gwUUdkdFlXbHNMbU52YlE9PSZtZXNzYWdlX3VpZD0xNzc0MDQwNzc5MTQwNDQwOGE0ZTliOTcx/gab3CJw/JMDMyMDIwMjZDMjAwNDY3OA/s4q1805549f</t>
+  </si>
+  <si>
+    <t>LinkedIn &lt;updates-noreply@linkedin.com&gt;
+Jobs.tn shared a post: le bureau C4I Training à la recherche d'un formateur safe certifié_x000D_
+vous pouvez envoyer vos dossier de candidature via email_x000D_
+contact@C4I.tn_x000D_
+_x000D_
+Read more: https://www.linkedin.com/comm/feed/update/urn:li:activity:7439637911030935552?origin=NETWORK_CONVERSATIONS&amp;lipi=urn%3Ali%3Apage%3Aemail_email_network_conversations_01%3B7GVHKadESGmx%2BUl56XOwPA%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=0GjwOFmgscasc1&amp;trk=eml-email_network_conversations_01-network~post~cta~text-0-read~more&amp;trkEmail=eml-email_network_conversations_01-network~post~cta~text-0-read~more-null-m8w88x~mmz9ejq6~m9-null-null&amp;eid=m8w88x-mmz9ejq6-m9&amp;otpToken=MTMwNjFhZTUxMzI3Y2ZjMGJjMmYwZmViNDExOWUzYjQ4Y2NhZDY0ODlkYTg4YTZlN2JjZTAxNjg0OTVkNThmYmYyZDJkMGU5NzBlMmZiODc3ZTkwZjZjYTNhMWRmODMyNjNjNzhjYmViMmExNjU2MjMzZWJhMzJjLDEsMQ%3D%3D_x000D_
+        _x000D_
+_x000D_
+_x000D_
+_x000D_
+    _x000D_
+          _x000D_
+Radhwane Harres reacted to this_x000D_
+        _x000D_
+_x000D_
+          _x000D_
+Joshua Adesoye LIKE PRAISE EMPATHY 51, 16 Comments_x000D_
+_x000D_
+_x000D_
+_x000D_
+Radhwane Harrescommented a post: In my professional journey, I’ve found that learning while doing yields better results than striving for…LIKE 1, 2 Replies_x000D_
+  _x000D_
+        _x000D_
+_x000D_
+          _x000D_
+    _x000D_
+    Read more:  https://www.linkedin.com/comm/feed/update/urn:li:activity:7438903304572674048?origin=NETWORK_CONVERSATIONS&amp;lipi=urn%3Ali%3Apage%3Aemail_email_network_conversations_01%3B7GVHKadESGmx%2BUl56XOwPA%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=0GjwOFmgscasc1&amp;trk=eml-email_network_conversations_01-network~post~cta~text-0-read~more&amp;trkEmail=eml-email_network_conversations_01-network~post~cta~text-0-read~more-null-m8w88x~mmz9ejq6~m9-null-null&amp;eid=m8w88x-mmz9ejq6-m9&amp;otpToken=MTMwNjFhZTUxMzI3Y2ZjMGJjMmYwZmViNDExOWUzYjQ4Y2NhZDY0ODlkYTg4YTZlN2JjZTAxNjg0OTVkNThmYmYyZDJkMGU5NzBlMmZiODc3ZTkwZjZjYTNhMWRmODMyNjNjNzhjYmViMmExNjU2MjMzZWJhMzJjLDEsMQ%3D%3D_x000D_
+_x000D_
+        _x000D_
+_x000D_
+See more on LinkedIn: https://www.linkedin.com/comm/feed/?lipi=urn%3Ali%3Apage%3Aemail_email_network_conversations_01%3B7GVHKadESGmx%2BUl56XOwPA%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=0GjwOFmgscasc1&amp;trk=eml-email_network_conversations_01-footer_promo-0-footer_see_all&amp;trkEmail=eml-email_network_conversations_01-footer_promo-0-footer_see_all-null-m8w88x~mmz9ejq6~m9-null-null&amp;eid=m8w88x-mmz9ejq6-m9&amp;otpToken=MTMwNjFhZTUxMzI3Y2ZjMGJjMmYwZmViNDExOWUzYjQ4Y2NhZDY0ODlkYTg4YTZlN2JjZTAxNjg0OTVkNThmYmYyZDJkMGU5NzBlMmZiODc3ZTkwZjZjYTNhMWRmODMyNjNjNzhjYmViMmExNjU2MjMzZWJhMzJjLDEsMQ%3D%3D_x000D_
+_x000D_
+----------------------------------------_x000D_
+_x000D_
+This email was intended for Yessine Hadj Taieb (IT Student)_x000D_
+Learn why we included this: https://www.linkedin.com/help/linkedin/answer/4788?lang=en&amp;lipi=urn%3Ali%3Apage%3Aemail_email_network_conversations_01%3B7GVHKadESGmx%2BUl56XOwPA%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=0GjwOFmgscasc1&amp;trk=eml-email_network_conversations_01-SecurityHelp-0-textfooterglimmer&amp;trkEmail=eml-email_network_conversations_01-SecurityHelp-0-textfooterglimmer-null-m8w88x~mmz9ejq6~m9-null-null&amp;eid=m8w88x-mmz9ejq6-m9&amp;otpToken=MTMwNjFhZTUxMzI3Y2ZjMGJjMmYwZmViNDExOWUzYjQ4Y2NhZDY0ODlkYTg4YTZlN2JjZTAxNjg0OTVkNThmYmYyZDJkMGU5NzBlMmZiODc3ZTkwZjZjYTNhMWRmODMyNjNjNzhjYmViMmExNjU2MjMzZWJhMzJjLDEsMQ%3D%3D_x000D_
+You are receiving Network Conversations emails. Some content may be automatically translated based on_x000D_
+      &lt;a href="https://www.linkedin.com/mypreferences/d/language-for-translation" target="_blank" class="link-no-visited-state" data-tracking-will-navigate data-tracking-control-name="email_network_conversations_content_settings_link" style="cursor: pointer; display: inline-block; text-decoration: none; -webkit-text-size-adjust: 100%; -ms-text-size-adjust: 100%; font-weight: 600; color: #0a66c2;"&gt;your settings&lt;/a&gt;._x000D_
+_x000D_
+_x000D_
+Unsubscribe: https://www.linkedin.com/comm/mypreferences/u/emailunsub?action=updateEmailSubscription&amp;lipi=urn%3Ali%3Apage%3Aemail_email_network_conversations_01%3B7GVHKadESGmx%2BUl56XOwPA%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=0GjwOFmgscasc1&amp;trk=eml-email_network_conversations_01-unsubscribe-0-textfooterglimmer&amp;trkEmail=eml-email_network_conversations_01-unsubscribe-0-textfooterglimmer-null-m8w88x~mmz9ejq6~m9-null-null&amp;eid=m8w88x-mmz9ejq6-m9&amp;loid=AQHwfGOi9oAYPwAAAZ0MtTHoioZ1l1F4xGczqbGzTJUTQbqF815rcl4lYDU9uXLijpDtWVmMZg-nnIafbGy401qIrzBFFCRgY6lRJjRwVDlS0nXoXx9wVXsL4Q_x000D_
+Help: https://www.linkedin.com/help/linkedin/answer/67?lang=en&amp;lipi=urn%3Ali%3Apage%3Aemail_email_network_conversations_01%3B7GVHKadESGmx%2BUl56XOwPA%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=0GjwOFmgscasc1&amp;trk=eml-email_network_conversations_01-help-0-textfooterglimmer&amp;trkEmail=eml-email_network_conversations_01-help-0-textfooterglimmer-null-m8w88x~mmz9ejq6~m9-null-null&amp;eid=m8w88x-mmz9ejq6-m9&amp;otpToken=MTMwNjFhZTUxMzI3Y2ZjMGJjMmYwZmViNDExOWUzYjQ4Y2NhZDY0ODlkYTg4YTZlN2JjZTAxNjg0OTVkNThmYmYyZDJkMGU5NzBlMmZiODc3ZTkwZjZjYTNhMWRmODMyNjNjNzhjYmViMmExNjU2MjMzZWJhMzJjLDEsMQ%3D%3D_x000D_
+_x000D_
+© 2026 LinkedIn Corporation, 1zwnj000 West Maude Avenue, Sunnyvale, CA 94085._x000D_
+LinkedIn and the LinkedIn logo are registered trademarks of LinkedIn.</t>
+  </si>
+  <si>
+    <t>"Nihel via Messenger" &lt;messages@facebookmail.com&gt;
+Hi Yessine,_x000D_
+_x000D_
+[https://facebook.com/email/appredirect/?rid=100004844588432&amp;fallback_uri=https%3A%2F%2Fwww.facebook.com%2Faloulou.nihel.3&amp;native_uri=fb%3A%2F%2Fprofile%2F100011764560621&amp;email_type=email] _x000D_
+_x000D_
+View message[https://www.facebook.com/messenger/email/?recipient_fbid=100004844588432&amp;sender_fbid=100011764560621&amp;thread_fbid=7371965359591542&amp;is_group_thread=0&amp;source=msg&amp;notif_id=1774121018850867&amp;cta_type=view_message_body&amp;is_fbm_redirect=0&amp;is_e2ee_thread=1] _x000D_
+_x000D_
+Go to profile[https://facebook.com/email/appredirect/?rid=100004844588432&amp;fallback_uri=https%3A%2F%2Fwww.facebook.com%2Faloulou.nihel.3&amp;native_uri=fb%3A%2F%2Fprofile%2F100011764560621&amp;email_type=email] _x000D_
+_x000D_
+Thanks,_x000D_
+The Facebook team_x000D_
+_x000D_
+_x000D_
+_x000D_
+========================================_x000D_
+This message was sent to yessineht@gmail.com. If you don't want to receive these emails from Meta in the future, please follow the link below to unsubscribe._x000D_
+https://www.facebook.com/o.php?k=AS2jx6n7PqN30aDOM28&amp;u=100004844588432&amp;mid=64d8d7387fb61G5af4313ccd90G64d8dbd1dfe33G8431&amp;ee=Af8r4DD-JKewGOE0L1ls7Aqm3si6XGukCtCwzwY1eCnopxGsKasEG9GEf5u2s7-mqXctLSoIEycxGFB1pw_x000D_
+Meta Platforms, Inc., Attention: Community Support, 1 Meta Way, Menlo Park, CA 94025</t>
+  </si>
+  <si>
+    <t>Patreon &lt;no-reply@updates.patreon.com&gt;
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+#outlook a{padding: 0;}_x000D_
+.ReadMsgBody{width: 100%;}_x000D_
+.ExternalClass{width: 100%;}_x000D_
+.ExternalClass *{line-height: 100%;}_x000D_
+body{margin: 0; padding: 0; -webkit-text-size-adjust: 100%; -ms-text-size-adjust: 100%;}_x000D_
+table, td{border-collapse: collapse; mso-table-lspace: 0pt; mso-table-rspace: 0pt;}_x000D_
+img{border: 0; height: auto; line-height: 100%; outline: none; text-decoration: none; -ms-interpolation-mode: bicubic;}_x000D_
+p{display: block; margin: 13px 0;}_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+96_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+.outlook-group-fix{width:100% !important;}_x000D_
+_x000D_
+_x000D_
+ _x000D_
+@media only screen and (max-width: 480px) {_x000D_
+.dys-desktop { display: none !important; }_x000D_
+div.dys-mobile { display: block !important; }_x000D_
+tr.dys-mobile { display: table-row !important; } _x000D_
+}_x000D_
+_x000D_
+ _x000D_
+@media only screen and (min-width:480px) {_x000D_
+.dys-column-per-100 {_x000D_
+width: 100.000000% !important;_x000D_
+max-width: 100.000000%;_x000D_
+}_x000D_
+}_x000D_
+_x000D_
+_x000D_
+@media only screen and (max-width:480px) {_x000D_
+ table.full-width-mobile { width: 100% !important; }_x000D_
+td.full-width-mobile { width: auto !important; }_x000D_
+}_x000D_
+u + #body a {color: #000000;text-decoration: underline;font-size: inherit; font-family: inherit; font-weight: inherit; line-height: inherit; }_x000D_
+ a {color: #000000;text-decoration: underline;}_x000D_
+ @font-face {_x000D_
+ font-family: "Oracle";_x000D_
+ src: url("https://c5.patreon.com/external/fonts/oracle/PatreonOracle-Light.woff2")_x000D_
+ format("woff2"),_x000D_
+ url("https://c5.patreon.com/external/fonts/oracle/PatreonOracle-Light.woff")_x000D_
+ format("woff");_x000D_
+ font-weight: 200;_x000D_
+ font-style: normal;_x000D_
+ }_x000D_
+ @font-face {_x000D_
+ font-family: "Oracle";_x000D_
+ src: url("https://c5.patreon.com/external/fonts/oracle/PatreonOracle-Book.woff2")_x000D_
+ format("woff2"),_x000D_
+ url("https://c5.patreon.com/external/fonts/oracle/PatreonOracle-Book.woff")_x000D_
+ format("woff");_x000D_
+ font-weight: 400;_x000D_
+ font-style: normal;_x000D_
+ }_x000D_
+ @font-face {_x000D_
+ font-family: "Oracle";_x000D_
+ src: url("https://c5.patreon.com/external/fonts/oracle/PatreonOracle-Medium.woff2")_x000D_
+ format("woff2"),_x000D_
+ url("https://c5.patreon.com/external/fonts/oracle/PatreonOracle-Medium.woff")_x000D_
+ format("woff");_x000D_
+ font-weight: 700;_x000D_
+ font-style: normal;_x000D_
+ }_x000D_
+ @font-face {_x000D_
+ font-family: "OracleLight";_x000D_
+ src: url("https://c5.patreon.com/external/fonts/oracle/PatreonOracle-Light.woff2")_x000D_
+ format("woff2"),_x000D_
+ url("https://c5.patreon.com/external/fonts/oracle/PatreonOracle-Light.woff")_x000D_
+ format("woff");_x000D_
+ font-weight: 400;_x000D_
+ font-style: normal;_x000D_
+ }_x000D_
+ @font-face {_x000D_
+ font-family: "OracleLight";_x000D_
+ src: url("https://c5.patreon.com/external/fonts/oracle/PatreonOracle-Book.woff2")_x000D_
+ format("woff2"),_x000D_
+ url("https://c5.patreon.com/external/fonts/oracle/PatreonOracle-Book.woff")_x000D_
+ format("woff");_x000D_
+ font-weight: 700;_x000D_
+ font-style: normal;_x000D_
+ }_x000D_
+ @font-face {_x000D_
+ font-family: "OracleTriple";_x000D_
+ src: url("https://c5.patreon.com/external/fonts/oracle/PatreonOracleTriple-Regular.woff2")_x000D_
+ format("woff2"),_x000D_
+ url("https://c5.patreon.com/external/fonts/oracle/PatreonOracleTriple-Regular.woff")_x000D_
+ format("woff");_x000D_
+ font-weight: 400;_x000D_
+ font-style: normal;_x000D_
+ }_x000D_
+ /* darkmode button support */_x000D_
+ .dm-pbtn table tbody tr td{_x000D_
+ background-image:linear-gradient(#ffffff,#ffffff) !important;_x000D_
+background: transparent !important; _x000D_
+ }_x000D_
+ .dm-sbtn table tbody tr td{_x000D_
+ background-image:linear-gradient(#ffffff,#ffffff) !important;_x000D_
+ box-shadow: 0 0px 3px #fff;_x000D_
+ }_x000D_
+ /* darkmode button support targets outlook.com */_x000D_
+ [data-ogsb] .dm-sbtn table tbody tr td{_x000D_
+ border: 1px solid #feffff;_x000D_
+ outline: 1px solid #feffff; _x000D_
+ } _x000D_
+ img {_x000D_
+ max-width:570px; _x000D_
+ }_x000D_
+ _x000D_
+ .preserve-white-space { _x000D_
+ white-space: pre-wrap;_x000D_
+ }_x000D_
+ @media only screen and (min-width:440px) {_x000D_
+ .icon-text &gt; div {_x000D_
+ padding-top:8px !important;_x000D_
+ }_x000D_
+ }_x000D_
+ @media only screen and (max-width:440px) {_x000D_
+ .icon-col {_x000D_
+ vertical-align: top !important;_x000D_
+ }_x000D_
+ .icon-text {_x000D_
+ padding-top: 0px !important;_x000D_
+ }_x000D_
+ .icon-img {_x000D_
+ padding-top: 5px !important;_x000D_
+ }_x000D_
+ }_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+Last day to claim your exclusive offer for Makarus. ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏ _x000D_
+ ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏ _x000D_
+ ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏ _x000D_
+ ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏ _x000D_
+ ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏ _x000D_
+ ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏ _x000D_
+ ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏ _x000D_
+ ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏ _x000D_
+ ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏ _x000D_
+ ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏  ͏ _x000D_
+ ­ ­ ­ ­ ­ ­ ­ ­ ­ ­ _x000D_
+­ ­ ­ ­ ­ ­ ­ ­ ­ ­ _x000D_
+­ ­ ­ ­ ­ ­ ­ ­ ­ ­ _x000D_
+­ ­ ­ ­ ­ ­ ­ ­ ­ ­ _x000D_
+­ ­ ­ ­ ­ ­ ­ ­ ­ ­ _x000D_
+­ ­ ­ ­ ­ ­ ­ ­ ­ ­ _x000D_
+­ ­ ­ ­ ­ ­ ­ ­ ­ ­ _x000D_
+­ ­ ­ ­ ­ ­ ­ ­ ­ ­ _x000D_
+­ ­ ­ ­ ­ ­ ­ ­ ­ ­ _x000D_
+­ ­ ­ ­ ­ ­ ­ ­ ­ ­ _x000D_
+ &amp;nbsp;_x000D_
+ _x000D_
+ _x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+ _x000D_
+ _x000D_
+ _x000D_
+ _x000D_
+ _x000D_
+ _x000D_
+ _x000D_
+ _x000D_
+ _x000D_
+ Makarus_x000D_
+ _x000D_
+ _x000D_
+ _x000D_
+ _x000D_
+ _x000D_
+ _x000D_
+ _x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+ _x000D_
+ _x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+ 50% off membership to Makarus ends today_x000D_
+ _x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+ Don’t miss out. Claim your offer below and get 50% off your first month. You’ll get access to exclusive benefits, posts and so much more.​Offer expires at 23:59 GMT-7 22 March 2026._x000D_
+ _x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+_x000D_
+ _x000D_
+ Claim your offer_x000D_
+ _x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+ Offer applies to the first month of paid membership for Makarus only. Offer cannot be combined with other offers or transferred. If the discounted price is less than US$0.50, a partial discount will be applied to adjust the price to US$0.50. Offer valid until 23:59 GMT-7 22 March 2026._x000D_
+ _x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+ _x000D_
+ _x000D_
+ _x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+ _x000D_
+ _x000D_
+ _x000D_
+ _x000D_
+ _x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+ _x000D_
+ 600 Townsend Street Suite 500_x000D_
+ San Francisco, CA 94103_x000D_
+ _x000D_
+ This email was sent to yessineht@gmail.comManage your email settings</t>
+  </si>
+  <si>
+    <t>LinkedIn &lt;messages-noreply@linkedin.com&gt;
+Do you know Omar Safi?3 mutual connections_x000D_
+_x000D_
+Yes, connect: https://www.linkedin.com/comm/mynetwork/send-invite/omarsafi3/?lipi=urn%3Ali%3Apage%3Aemail_email_pymk_02%3B0gs%2B0zpXTruEI6RX%2FNM4OQ%3D%3D&amp;midSig=2qX34DDPr7cIc1&amp;midToken=AQFDdUEz6WQ9Uw&amp;trkEmail=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A1159817139-null-m8w88x%7Emn1rfb23%7E53-null-null&amp;trk=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A1159817139&amp;_sig=2b5lRg9OH7cIc1_x000D_
+_x000D_
+_x000D_
+More people you may know_x000D_
+            _x000D_
+    Iadh ZALLOUZ_x000D_
+Développeur WordPress &amp; PHP | Création de sites web sur mesure | Optimisation SEO &amp; performance_x000D_
+https://www.linkedin.com/comm/mynetwork/send-invite/iyadh-zallouz/?lipi=urn%3Ali%3Apage%3Aemail_email_pymk_02%3B0gs%2B0zpXTruEI6RX%2FNM4OQ%3D%3D&amp;midSig=2qX34DDPr7cIc1&amp;midToken=AQFDdUEz6WQ9Uw&amp;trkEmail=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A461258324-null-m8w88x%7Emn1rfb23%7E53-null-null&amp;trk=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A461258324&amp;_sig=0u83IFglD7cIc13 mutual connections_x000D_
+            _x000D_
+    Walid Ellouze_x000D_
+Software Engineer | Java, Spring Boot, JavaScript, React.js_x000D_
+https://www.linkedin.com/comm/mynetwork/send-invite/walid-ellouze/?lipi=urn%3Ali%3Apage%3Aemail_email_pymk_02%3B0gs%2B0zpXTruEI6RX%2FNM4OQ%3D%3D&amp;midSig=2qX34DDPr7cIc1&amp;midToken=AQFDdUEz6WQ9Uw&amp;trkEmail=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A901693708-null-m8w88x%7Emn1rfb23%7E53-null-null&amp;trk=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A901693708&amp;_sig=1enkzDgE37cIc12 mutual connections_x000D_
+            _x000D_
+    Bilel Elloumi_x000D_
+Ingénieur R&amp;D web (PHP, Drupal(8,9,10),Magento,symfony,next.js)_x000D_
+https://www.linkedin.com/comm/mynetwork/send-invite/bilel-elloumi-98137b264/?lipi=urn%3Ali%3Apage%3Aemail_email_pymk_02%3B0gs%2B0zpXTruEI6RX%2FNM4OQ%3D%3D&amp;midSig=2qX34DDPr7cIc1&amp;midToken=AQFDdUEz6WQ9Uw&amp;trkEmail=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A1087810225-null-m8w88x%7Emn1rfb23%7E53-null-null&amp;trk=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A1087810225&amp;_sig=30U7VQ4w77cIc13 mutual connections_x000D_
+            _x000D_
+    Yassin Omri_x000D_
+Junior Engineer | Embedded Linux Software | C | Qt | Electrical Engineering Graduate_x000D_
+https://www.linkedin.com/comm/mynetwork/send-invite/yassinomri/?lipi=urn%3Ali%3Apage%3Aemail_email_pymk_02%3B0gs%2B0zpXTruEI6RX%2FNM4OQ%3D%3D&amp;midSig=2qX34DDPr7cIc1&amp;midToken=AQFDdUEz6WQ9Uw&amp;trkEmail=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A839127883-null-m8w88x%7Emn1rfb23%7E53-null-null&amp;trk=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A839127883&amp;_sig=1ikmIax_b7cIc11 mutual connection_x000D_
+            _x000D_
+    eya ben moallem_x000D_
+Ingénieure en Génie Logiciel | IA, Computer Vision &amp; Développement Full-Stack_x000D_
+https://www.linkedin.com/comm/mynetwork/send-invite/eya-ben-moallem-a906011b8/?lipi=urn%3Ali%3Apage%3Aemail_email_pymk_02%3B0gs%2B0zpXTruEI6RX%2FNM4OQ%3D%3D&amp;midSig=2qX34DDPr7cIc1&amp;midToken=AQFDdUEz6WQ9Uw&amp;trkEmail=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A849515724-null-m8w88x%7Emn1rfb23%7E53-null-null&amp;trk=eml-email_pymk_02-pymkCard-0-pymk_cta%3A+urn%3Ali%3Amember%3A849515724&amp;_sig=3LjvQGpWL7cIc12 mutual connections_x000D_
+_x000D_
+See more people you might know:https://www.linkedin.com/comm/mynetwork/add-connections/?lipi=urn%3Ali%3Apage%3Aemail_email_pymk_02%3B0gs%2B0zpXTruEI6RX%2FNM4OQ%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=2qX34DDPr7cIc1&amp;trk=eml-email_pymk_02-see_more-0-cta~text&amp;trkEmail=eml-email_pymk_02-see_more-0-cta~text-null-m8w88x~mn1rfb23~53-null-null&amp;eid=m8w88x-mn1rfb23-53&amp;otpToken=MTMwNjFhZTUxMzI3Y2ZjMGJjMmYwZmViNDExOWUzYjU4N2NhZDE0NTk4YWI4ODZlN2JjZTAxNjg0OTVkNThmYmYyZDJkMGU5NzFiNmVkZDg1Y2IyZDU5NmZkY2FlY2RmY2UxZGM4OTRmN2YwMWY3NDU3NjExZTc5LDEsMQ%3D%3D_x000D_
+      _x000D_
+_x000D_
+----------------------------------------_x000D_
+_x000D_
+This email was intended for Yessine Hadj Taieb (IT Student)_x000D_
+Learn why we included this: https://www.linkedin.com/help/linkedin/answer/4788?lang=en&amp;lipi=urn%3Ali%3Apage%3Aemail_email_pymk_02%3B0gs%2B0zpXTruEI6RX%2FNM4OQ%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=2qX34DDPr7cIc1&amp;trk=eml-email_pymk_02-SecurityHelp-0-textfooterglimmer&amp;trkEmail=eml-email_pymk_02-SecurityHelp-0-textfooterglimmer-null-m8w88x~mn1rfb23~53-null-null&amp;eid=m8w88x-mn1rfb23-53&amp;otpToken=MTMwNjFhZTUxMzI3Y2ZjMGJjMmYwZmViNDExOWUzYjU4N2NhZDE0NTk4YWI4ODZlN2JjZTAxNjg0OTVkNThmYmYyZDJkMGU5NzFiNmVkZDg1Y2IyZDU5NmZkY2FlY2RmY2UxZGM4OTRmN2YwMWY3NDU3NjExZTc5LDEsMQ%3D%3D_x000D_
+You are receiving People You May Know notification emails._x000D_
+_x000D_
+_x000D_
+Unsubscribe: https://www.linkedin.com/comm/psettings/email-unsubscribe?lipi=urn%3Ali%3Apage%3Aemail_email_pymk_02%3B0gs%2B0zpXTruEI6RX%2FNM4OQ%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=2qX34DDPr7cIc1&amp;trk=eml-email_pymk_02-unsubscribe-0-textfooterglimmer&amp;trkEmail=eml-email_pymk_02-unsubscribe-0-textfooterglimmer-null-m8w88x~mn1rfb23~53-null-null&amp;eid=m8w88x-mn1rfb23-53&amp;loid=AQEBKx9e-8HUYgAAAZ0VnZL2xDn2eVxzkR4uo3sb8xifysvvSvStmY43wGmxEmtNx95aYJyLSsMPyC-1Sc8JEYnjspXVFyCxfViq5HM-1Q_x000D_
+Help: https://www.linkedin.com/help/linkedin/answer/67?lang=en&amp;lipi=urn%3Ali%3Apage%3Aemail_email_pymk_02%3B0gs%2B0zpXTruEI6RX%2FNM4OQ%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=2qX34DDPr7cIc1&amp;trk=eml-email_pymk_02-help-0-textfooterglimmer&amp;trkEmail=eml-email_pymk_02-help-0-textfooterglimmer-null-m8w88x~mn1rfb23~53-null-null&amp;eid=m8w88x-mn1rfb23-53&amp;otpToken=MTMwNjFhZTUxMzI3Y2ZjMGJjMmYwZmViNDExOWUzYjU4N2NhZDE0NTk4YWI4ODZlN2JjZTAxNjg0OTVkNThmYmYyZDJkMGU5NzFiNmVkZDg1Y2IyZDU5NmZkY2FlY2RmY2UxZGM4OTRmN2YwMWY3NDU3NjExZTc5LDEsMQ%3D%3D_x000D_
+_x000D_
+© 2026 LinkedIn Corporation, 1zwnj000 West Maude Avenue, Sunnyvale, CA 94085._x000D_
+LinkedIn and the LinkedIn logo are registered trademarks of LinkedIn.</t>
+  </si>
+  <si>
+    <t>Spotify &lt;no-reply@spotify.com&gt;
+فرصتك للاشتراك في Spotify Premium. https://www.spotify.com/purchase/offer/2026-q1-global-campaign-intro?splot=wqM2qvqAT0igMzConUU52A_x000D_
+موسيقى تطرب آذانك مجاناً لمدة 3 أشهر_x000D_
+_x000D_
+_x000D_
+يمكنك الاستماع إلى مقاطعك المفضَّلة مراراً وتكراراً بالترتيب الذي يعجبك. يتيح لك اشتراك Spotify Premium تنسيق أغانيك بنفسك — أو حتى سيكون هو الدي جي الخاص بك._x000D_
+_x000D_
+_x000D_
+الآن 3 أشهر مقابل 0 TND ( https://www.spotify.com/purchase/offer/2026-q1-global-campaign-intro?splot=wqM2qvqAT0igMzConUU52A )_x000D_
+_x000D_
+_x000D_
+العرض سارٍ على باقة &amp;quot;Premium للأفراد&amp;quot; فقط. وينتهي في 31 مارس 2026. بعد ذلك، ستكون قيمة الاشتراك 12,50 TND شهرياً. &lt;a href="https://www.spotify.com/legal/premium-promotional-offer-terms/"&gt;تُطبَّق الشروط والأحكام.&lt;/a&gt; هذا العرض متاح للمستخدمين الذين لم تسبق لهم تجربة اشتراك Premium فقط. بالنقر على الزر، سيتم تسجيل الدخول إلى حسابك على Spotify، حيث يمكنك قبول هذا العرض. يجب عدم إعادة توجيه هذه الرسالة الإلكترونية إلى أي شخص غير مصرَّح له بالدخول إلى حسابك._x000D_
+_x000D_
+_x000D_
+-------------_x000D_
+_x000D_
+اشترك في Spotify ديال:_x000D_
+  * iPhone (https://itunes.apple.com/app/spotify-music/id324684580)_x000D_
+  * iPad (https://itunes.apple.com/app/spotify-music/id324684580)_x000D_
+  * Android (https://play.google.com/store/apps/details?id=com.spotify.music)_x000D_
+  * شي حاجة أخرى (https://www.spotify.com/download/)_x000D_
+_x000D_
+الرسالة تصيفطات للبريد الإلكتروني yessineht@gmail.com._x000D_
+إذا ما تبي تجيك الرسائل الإلكترونية ذي من Spotify بعد كذا، تقدر_x000D_
+تعدّل صفحتك الشخصية_x000D_
+(https://www.spotify.com/account/notifications)_x000D_
+أو_x000D_
+تلغي اشتراكك_x000D_
+(https://www.spotify.com/account/unsubscribe?t=JcVBDoQgDADAr%2FgBDgWl%2BJyW0shGqVnWEH%2Bvyc5lAvgx27ZxpWOYoPVoA89PqXhNzX5Vb9fP%2F6Zavt1RE8dXk730yWf0gRKEmGHJxLSiMARWnNcSk1B6gfID&amp;a=unsubscribe)_x000D_
+_x000D_
+_x000D_
+  * شروط الاستخدام https://www.spotify.com/legal/end-user-agreement/_x000D_
+  * سياسة الخصوصية https://www.spotify.com/legal/privacy-policy/_x000D_
+  * تواصل معانا https://www.spotify.com/about-us/contact/_x000D_
+_x000D_
+_x000D_
+Spotify AB, Regeringsgatan 19, 111 53, Stockholm, Sweden</t>
+  </si>
+  <si>
+    <t>daily.dev &lt;informer@daily.dev&gt;
+We picked posts from your topics based on what the community found useful  _x000D_
+_x000D_
+*******_x000D_
+For you_x000D_
+*******_x000D_
+_x000D_
+​Mar 23, 2026_x000D_
+_x000D_
+Logo ( https://app.daily.dev/ )_x000D_
+_x000D_
+Tech World With Milan ( https://app.daily.dev/posts/V90BEtMZY?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+You're Not Paid to Write Code ( https://app.daily.dev/posts/V90BEtMZY?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+------------------------------------------------------------------------------------------------------------------------------------_x000D_
+_x000D_
+Read_x000D_
+article → ( https://app.daily.dev/posts/V90BEtMZY?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+Addy Osmani ( https://app.daily.dev/posts/kthBgt6Kn?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+14 More Lessons from 14 years at Google ( https://app.daily.dev/posts/kthBgt6Kn?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+----------------------------------------------------------------------------------------------------------------------------------------------_x000D_
+_x000D_
+Read_x000D_
+article → ( https://app.daily.dev/posts/kthBgt6Kn?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+Atomic Spin ( https://app.daily.dev/posts/aeJGGwMeD?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+Upgrade Your Note-Taking Skills ( https://app.daily.dev/posts/aeJGGwMeD?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+--------------------------------------------------------------------------------------------------------------------------------------_x000D_
+_x000D_
+Read_x000D_
+article → ( https://app.daily.dev/posts/aeJGGwMeD?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+Code Like A Girl ( https://app.daily.dev/posts/AeOi33le7?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+You Don’t Suck at Coding. You’re Just Meeting a Real Codebase. ( https://app.daily.dev/posts/AeOi33le7?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+-------------------------------------------------------------------------------------------------------------------------------------------------------------------------_x000D_
+_x000D_
+Read_x000D_
+article → ( https://app.daily.dev/posts/AeOi33le7?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+Engineering Enablement ( https://app.daily.dev/posts/MCzNO6zN8?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+AI productivity gains are 10%, not 10x ( https://app.daily.dev/posts/MCzNO6zN8?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+---------------------------------------------------------------------------------------------------------------------------------------------_x000D_
+_x000D_
+Read_x000D_
+article → ( https://app.daily.dev/posts/MCzNO6zN8?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+Fast-track your growth. Upgrade to plus ( https://app.daily.dev/plus )_x000D_
+_x000D_
+Try daily.dev on mobile (if you haven’t yet)_x000D_
+_x000D_
+( https://apps.apple.com/app/daily-dev/id6740634400 )_x000D_
+daily.dev for iOS ( https://apps.apple.com/app/daily-dev/id6740634400 )_x000D_
+_x000D_
+( https://play.google.com/store/apps/details?id=dev.daily )_x000D_
+daily.dev for Android ( https://play.google.com/store/apps/details?id=dev.daily )_x000D_
+_x000D_
+Explore ( https://app.daily.dev/posts )   |   Discussions ( https://app.daily.dev/discussed )   |   Tags ( https://app.daily.dev/tags )   |   Sources ( https://app.daily.dev/sources )   |   Leaderboard ( https://app.daily.dev/users )_x000D_
+_x000D_
+X ( https://twitter.com/dailydotdev ) Yt ( https://www.youtube.com/c/dailydev )_x000D_
+Inst ( https://www.instagram.com/dailydotdev/ ) Tt ( https://www.tiktok.com/@dailydotdev )_x000D_
+GitHub ( https://github.com/dailydotdev/daily )_x000D_
+This email was intended for Yessine Ht (yessineht@gmail.com)_x000D_
+Settings notifications ( https://app.daily.dev/account/notifications ), account details ( https://app.daily.dev/account/profile ) or unsubscribe ( https://track.customer.io/manage_subscription_preferences/RLnCCQUAAZ0ZEzpvfu1zYMb-xjnEnw== ) _x000D_
+_x000D_
+( https://app.daily.dev )Daily Dev Ltd., 9 Derech HaTikva Ganei Tikva, Israel_x000D_
+5591252</t>
+  </si>
+  <si>
+    <t>MongoDB &lt;mongodbteam@messages.mongodb.com&gt;
+To view this email as a web page, go to the following address: https://info.mongodb.com/index.php/email/emailWebview?mkt_tok=MTQ5LUNCSi0xMzYAAAGguYwlXakzx6ur_uwPwzmDXyUfclttn3FumR7HAdDtj67TjhbrB9uKZiNLA1s_dtRBR4mcLKN0YpF5GykRlcPBHIIffgL8MALhhnyZjgEGBqkxwg _x000D_
+_x000D_
+_x000D_
+Bonjour Yessine,_x000D_
+_x000D_
+_x000D_
+Que vous souhaitiez développer vos compétences ou mieux comprendre tout le potentiel des solutions MongoDB, notre Programme de Certification vous accompagne avec une certification officielle à la clé._x000D_
+_x000D_
+Conçue par les experts MongoDB, cette formation vous permettra d’approfondir vos connaissances, de développer vos compétences et de valoriser votre expertise._x000D_
+_x000D_
+En vous inscrivant, vous bénéficierez de :_x000D_
+_x000D_
+_x000D_
+	- 9 sessions en direct animées par des experts MongoDB_x000D_
+	- Un contenu exclusif, avec des cas d’usage avancés_x000D_
+	- Un examen de certification officiel gratuit_x000D_
+_x000D_
+_x000D_
+_x000D_
+Que vous soyez développeur, architecte ou responsable data, ce programme vous aidera à mieux exploiter les opportunités offertes par les architectures de données modernes MongoDB._x000D_
+Inscrivez-vous  &lt;https://em.mongodb.com/MTQ5LUNCSi0xMzYAAAGguYwlXTuCIKP6_LoBDLdFIsmZKyH45iQ6nDGf-UFAtSTG3VC72eDm9R1cwzlFDJWZw66Qw1Q=&gt;_x000D_
+Think Big. Go Far,_x000D_
+The MongoDB Team_x000D_
+_x000D_
+This email was sent to yessineht@gmail.com. If you no longer wish to receive these emails you may unsubscribe here: https://info.mongodb.com/UnsubscribePage.html?mkt_unsubscribe=1&amp;mkt_tok=MTQ5LUNCSi0xMzYAAAGguYwlXakzx6ur_uwPwzmDXyUfclttn3FumR7HAdDtj67TjhbrB9uKZiNLA1s_dtRBR4mcLKN0YpF5GykRlcPBHIIffgL8MALhhnyZjgEGBqkxwg.</t>
+  </si>
+  <si>
+    <t>AliExpress &lt;promotion@aliexpress.com&gt;
+         #outlook a { padding:0; } body { margin:0;padding:0;-webkit-text-size-adjust:100%;-ms-text-size-adjust:100%; } table, td { border-collapse:collapse;mso-table-lspace:0pt;mso-table-rspace:0pt; } img { border:0;height:auto;line-height:100%; outline:none;text-decoration:none;-ms-interpolation-mode:bicubic; } p { display:block;margin:13px 0; }      96      .mj-outlook-group-fix { width:100% !important; }     x @import url(https://fonts.googleapis.com/css?family=Open+Sans:300,400,500,700);      @import url(https://fonts.googleapis.com/css?family=Open+Sans:300,400,500,700);        @import url(https://fonts.googleapis.com/css?family=Roboto:300,400,500,700);        @import url(https://fonts.googleapis.com/css?family=Roboto:300,400,500,700);        @import url(https://fonts.googleapis.com/css?family=Roboto:300,400,500,700);        @import url(https://fonts.googleapis.com/css?family=Open+Sans:300,400,500,700);      @media screen and (min-width: 480px) { .list-one-two-left-item-card .list-one-two-product-name { font-size: 18px !important; line-height: 22px !important; } .list-one-two-left-item-card .list-one-two-item-card-text { padding: 16px 24px 0px; } .list-one-two-left-item-card .list-one-two-price { padding-top: 1px !important; font-size: 24px !important; line-height: 32px !important; } .list-one-two-left-item-card .list-one-two-split { height: 16px !important; font-size: 15px !important; line-height: 15px !important; } .list-one-two-left-item-card .list-one-two-ori-price { font-size: 15px !important; line-height: 19px !important; } .list-one-two-left-item-card .list-one-two-product-price-off { font-size: 15px !important; line-height: 19px !important; } .list-one-two-right-item-card .list-one-two-product-name { font-size: 15px !important; line-height: 19px !important; } .list-one-two-right-item-card .list-one-two-price { font-size: 20px !important; line-height: 24px !important; } .list-one-two-right-item-card .list-one-two-ori-price { font-size: 15px !important; line-height: 19px !important; } .list-one-two-module-title { font-size: 20px !important; font-weight: 700 !important; line-height: 24px !important; } .free-shipping-icon { width: 20px !important; height: 20px !important; } .free-shipping-text { font-weight: 400 !important; font-size: 15px !important; line-height: 19px !important; color: #009966 !important; } .logistics-timeliness-icon { width: 14px !important; height: 14px !important; } .logistics-timeliness-text { font-weight: 400 !important; font-size: 15px !important; line-height: 19px !important; color: #009966 !important; } .reverse-return-text { font-size: 15px !important; line-height: 19px !important; color: #009966 !important; } .selling-point-text { font-size: 12px !important; line-height: 16px !important; } .sales-text { font-size: 15px !important; line-height: 19px !important; color: #191919 !important; } .product-rating-icon { width: 15px !important; height: 15px !important; } .product-rating-text { font-size: 15px !important; line-height: 19px !important; color: #191919 !important; } @media screen and (min-width: 480px) { .EDM-COLUMNS-THREE-discount div { margin-bottom: 0px !important; } } .bottomNavigation-v1-title div { font-size: 20px !important; line-height: 24px !important; font-weight: 700 !important; } }                                         Découvrez vos offres de rêves &amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;                                                                                        Redécouvrez votre chez vous              2,96€ 5,91€ | -50%         &amp;nbsp;           131,20€ 262,40€          .              141,55€ 410,97€          &amp;nbsp;                   &amp;nbsp;      Explorer plus      &amp;nbsp;                 .          .     .          .      -67%  321,49€      .          .      -32%  32,81€      .          .      -66%  162,54€      .    .     .          .      .  69,23€      .          .      -50%  169,36€      .          .      -50%  60,80€      .    .     .          .      .  26,92€      .          .      -53%  63,89€      .          .      -50%  21,90€      .    .     .          .      -40%  10,64€      .          .      -50%  21,82€      .          .      -65%  1,25€      .    .     .          .      .  32,29€      .          .      -72%  19,48€      .          .      -50%  3,22€      .    .     .          .      -50%  141,31€      .          .      -66%  44,23€      .          .      -30%  25,08€      .    .     .          .      -67%  122,45€      .          .      -50%  89,46€      .          .      -50%  12,38€      .    .      .                  &amp;nbsp;      Voir plus      &amp;nbsp;                  Populaire         Art  Articles ménagers  Cuisine         Outils  Amélioration de l'habitat  Éclairage d'intérieur                    Les prix, offres et disponibilités affichés dans cet email sont valables à l'heure de l'envoi et peuvent changer. Veuillez noter que les frais d'envoi ne sont pas inclus. Rendez-vous sur la page de l'article pour voir les informations à jour.                  Téléchargez l'application pour profiter d'offres exclusives                                                 Cet email a été envoyé à yessi****@gmail.com     Vous recevez cet email car vous êtes un membre de www.AliExpress.com.    Pour ne plus recevoir nos emails promotionnels, Cliquez ici    Lisez notre Politique de confidentialité et conditions d'utilisation si vous avez des questions.    Centre de service clientèle AliExpress    Alibaba.com Singapore E-Commerce Private Limited,     c/o 26/F Tower One, Times Square, 1 Matheson Street, Causeway Bay, Hong Kong</t>
+  </si>
+  <si>
+    <t>sirine &lt;sirine@lunflow.com&gt;
+Bonsoir , ok merci_x000D_
+_x000D_
+On 3/23/2026 7:56 PM, Yessine Ht wrote:_x000D_
+&gt; Bonjour,_x000D_
+&gt;_x000D_
+&gt; Je vous envoie ce mail pour vous informer que nous avons essayé de _x000D_
+&gt; contacter notre encadrant académique par téléphone, mais nous n’avons _x000D_
+&gt; pas réussi à le joindre.</t>
+  </si>
+  <si>
+    <t>sirine &lt;sirine@lunflow.com&gt;
+ok_x000D_
+_x000D_
+On 3/23/2026 8:03 PM, Yessine Ht wrote:_x000D_
+&gt; Bonsoir_x000D_
+&gt;_x000D_
+&gt; Je m’excuse pour le message précédent. Notre encadrant académique _x000D_
+&gt; vient de nous rappeler et a confirmé qu’il est d’accord pour la _x000D_
+&gt; réunion. Il sera disponible entre 10h et 11h._x000D_
+&gt;_x000D_
+&gt; On Mon, Mar 23, 2026, 19:58 sirine &lt;sirine@lunflow.com&gt; wrote:_x000D_
+&gt;_x000D_
+&gt;     Bonsoir , ok merci_x000D_
+&gt;_x000D_
+&gt;     On 3/23/2026 7:56 PM, Yessine Ht wrote:_x000D_
+&gt;     &gt; Bonjour,_x000D_
+&gt;     &gt;_x000D_
+&gt;     &gt; Je vous envoie ce mail pour vous informer que nous avons essayé de_x000D_
+&gt;     &gt; contacter notre encadrant académique par téléphone, mais nous_x000D_
+&gt;     n’avons_x000D_
+&gt;     &gt; pas réussi à le joindre._x000D_
+&gt;</t>
+  </si>
+  <si>
+    <t>daily.dev &lt;informer@daily.dev&gt;
+We picked posts from your topics based on what the community found useful  _x000D_
+_x000D_
+*******_x000D_
+For you_x000D_
+*******_x000D_
+_x000D_
+​Mar 24, 2026_x000D_
+_x000D_
+Logo ( https://app.daily.dev/ )_x000D_
+_x000D_
+daily.dev ( https://app.daily.dev/posts/kaAWQy79n?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+How we built a Linear coding agent: the hard parts ( https://app.daily.dev/posts/kaAWQy79n?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+---------------------------------------------------------------------------------------------------------------------------------------------------------_x000D_
+_x000D_
+Read_x000D_
+article → ( https://app.daily.dev/posts/kaAWQy79n?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+Josh W Comeau ( https://app.daily.dev/posts/4AgbREn59?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+Sneaky Header Blocker Trick • Josh W. Comeau ( https://app.daily.dev/posts/4AgbREn59?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+-----------------------------------------------------------------------------------------------------------------------------------------------------_x000D_
+_x000D_
+Read_x000D_
+article → ( https://app.daily.dev/posts/4AgbREn59?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+TkDodo ( https://app.daily.dev/posts/wSju3VMXu?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+Test IDs are an a11y smell ( https://app.daily.dev/posts/wSju3VMXu?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+---------------------------------------------------------------------------------------------------------------------------------_x000D_
+_x000D_
+Read_x000D_
+article → ( https://app.daily.dev/posts/wSju3VMXu?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+Tech World With Milan ( https://app.daily.dev/posts/V90BEtMZY?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+You're Not Paid to Write Code ( https://app.daily.dev/posts/V90BEtMZY?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+------------------------------------------------------------------------------------------------------------------------------------_x000D_
+_x000D_
+Read_x000D_
+article → ( https://app.daily.dev/posts/V90BEtMZY?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+Engineering Enablement ( https://app.daily.dev/posts/MCzNO6zN8?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+AI productivity gains are 10%, not 10x ( https://app.daily.dev/posts/MCzNO6zN8?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+---------------------------------------------------------------------------------------------------------------------------------------------_x000D_
+_x000D_
+Read_x000D_
+article → ( https://app.daily.dev/posts/MCzNO6zN8?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
+_x000D_
+Fast-track your growth. Upgrade to plus ( https://app.daily.dev/plus )_x000D_
+_x000D_
+Try daily.dev on mobile (if you haven’t yet)_x000D_
+_x000D_
+( https://apps.apple.com/app/daily-dev/id6740634400 )_x000D_
+daily.dev for iOS ( https://apps.apple.com/app/daily-dev/id6740634400 )_x000D_
+_x000D_
+( https://play.google.com/store/apps/details?id=dev.daily )_x000D_
+daily.dev for Android ( https://play.google.com/store/apps/details?id=dev.daily )_x000D_
+_x000D_
+Explore ( https://app.daily.dev/posts )   |   Discussions ( https://app.daily.dev/discussed )   |   Tags ( https://app.daily.dev/tags )   |   Sources ( https://app.daily.dev/sources )   |   Leaderboard ( https://app.daily.dev/users )_x000D_
+_x000D_
+X ( https://twitter.com/dailydotdev ) Yt ( https://www.youtube.com/c/dailydev )_x000D_
+Inst ( https://www.instagram.com/dailydotdev/ ) Tt ( https://www.tiktok.com/@dailydotdev )_x000D_
+GitHub ( https://github.com/dailydotdev/daily )_x000D_
+This email was intended for Yessine Ht (yessineht@gmail.com)_x000D_
+Settings notifications ( https://app.daily.dev/account/notifications ), account details ( https://app.daily.dev/account/profile ) or unsubscribe ( https://track.customer.io/manage_subscription_preferences/RLnCCQUAAZ0eOxYRP82OWI9PHu-BzQ== ) _x000D_
+_x000D_
+( https://app.daily.dev )Daily Dev Ltd., 9 Derech HaTikva Ganei Tikva, Israel_x000D_
+5591252</t>
   </si>
   <si>
     <t>IMG_20231029_104613_104.webp</t>
@@ -432,7 +3180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -451,10 +3199,10 @@
         <v>9834</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -462,23 +3210,289 @@
         <v>9868</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>3</v>
+      <c r="A4">
+        <v>9871</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" t="s">
+      <c r="A5">
+        <v>9872</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <f>?UTF-8?B?4oCcR29vZ2xlIEFJIFN0dWRpb+KAnQ==?= &lt;googleaistudio-noreply@google.com&gt;
+Review your usage to better manage your billing.
+Hello Yessine,
+We're writing to notify you of updates to Google AI Studio Usage Tiers and  
+the introduction of enforced billing account tier caps for the Gemini API  
+starting April 1, 2026.
+Review these changes and how they may impact your API usage.
+Key changes:
+Starting March 16, 2026:
+New Project Spend Caps: You can now configure optional, project-level spend  
+limits. If a project exceeds your defined target, the system will pause  
+requests for that specific project within approximately 10 minutes. Please  
+note that you are responsible for any overages incurred during this brief  
+window.
+Paused projects will resume as soon as the limits reset on the first day of  
+the following month, or you update/remove the cap.
+Starting April 1, 2026:
+Enforced billing account tier caps: Each Usage Tier will enforce a maximum  
+monthly spend limit at the billing account level. If your aggregate spend  
+reaches this cap, Gemini API requests tied to that billing account will be  
+paused until the next month.
+Automated Usage Tier upgrades: Tier upgrades will be automated. Your  
+account will systematically graduate to higher tiers with higher rate  
+limits as you meet specified spend and tenure thresholds.
+What you need to do
+Manually verify and review your current usage to plan ahead and prevent  
+service disruption when the new caps take effect:
+Check your tier: Log in to Google AI Studio to view your current Usage Tier  
+and applicable limits.
+Review your billing account spend: Evaluate your historical monthly  
+spending to determine if the new Billing Account Tier Cap will impact your  
+ongoing projects. More details here.
+If you determine that your billing account requires a higher cap:
+Request an override: If you require a cap higher than the automatically  
+assigned tier, please fill out this form.
+If you have any questions or need help, please check our product  
+documentation or visit the Gemini AI community.
+Thanks for choosing Google AI Studio and Gemini API.
+– The Gemini API Team
+© 2026 Google LLC 1600 Amphitheatre Parkway, Mountain View, CA 94043, USA
+This email was sent to Yessineht@gmail.com because you signed up to try the  
+Gemini API and Google AI Studio.</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
         <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
